--- a/Luban/Config/Datas/#BattleSkillConfig.xlsx
+++ b/Luban/Config/Datas/#BattleSkillConfig.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28827"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28925"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Project\Return0\Luban\Config\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{49A9DA66-FCB8-44AB-A393-685D4D6AE8F2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{635C6BC6-261C-4306-9694-B4CCF462DF0D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3630" yWindow="4950" windowWidth="28800" windowHeight="15345" xr2:uid="{53B3FBB6-B116-408D-BCC0-737AAAC6C9D0}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{53B3FBB6-B116-408D-BCC0-737AAAC6C9D0}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="59">
   <si>
     <t>##var</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -107,14 +107,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>1,1,2,3,4</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>2,3,1,4</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>技能需要的键</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -147,18 +139,10 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>UnderHitMoment</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>AfterActionMoment</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>命中后扳机</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>交锋前扳机</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -167,31 +151,115 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>行动后</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>DoDesitionMoment</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>被作为目标时扳机</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>StartActionWheelMoment</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>息开始扳机</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>AsTargetActionMoment</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>ReleaseSkillActionMoment</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>float</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SkillEndMoment</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>行动后扳机</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>XuanQiCost</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>玄炁消耗</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>GangQiCost</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>刚炁消耗</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SkillType</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>技能类型</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>DamageType</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>伤害类型</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>BeforeActionMoment</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>BeforeUnderActionMoment</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>AfterUnderActionMoment</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>RoundEndMoment</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>行动前</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>受到行动前调用</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>受到行动后调用扳机</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>回合结束扳机</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>技能结束扳机</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>技能3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>AniName</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>动画名称</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Attack1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Attack2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Attack3</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -556,20 +624,25 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8D4CF470-E9E0-44FF-BA6C-71B5C42FB7B2}">
-  <dimension ref="A1:P5"/>
+  <dimension ref="A1:W6"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="6" max="6" width="17.5" customWidth="1"/>
-    <col min="7" max="7" width="14.125" customWidth="1"/>
-    <col min="9" max="11" width="22.75" customWidth="1"/>
-    <col min="12" max="12" width="32.5" customWidth="1"/>
-    <col min="13" max="13" width="27.375" customWidth="1"/>
-    <col min="14" max="14" width="22.375" customWidth="1"/>
-    <col min="15" max="15" width="17" customWidth="1"/>
-    <col min="16" max="16" width="18.125" customWidth="1"/>
+    <col min="6" max="9" width="17.5" customWidth="1"/>
+    <col min="10" max="10" width="14.125" customWidth="1"/>
+    <col min="12" max="12" width="14.125" customWidth="1"/>
+    <col min="13" max="13" width="17.5" customWidth="1"/>
+    <col min="14" max="14" width="41.25" customWidth="1"/>
+    <col min="15" max="15" width="24.125" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="22.375" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="17.75" customWidth="1"/>
+    <col min="18" max="18" width="17.5" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="22.25" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="27.5" customWidth="1"/>
+    <col min="21" max="21" width="18.625" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="17.75" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -589,37 +662,58 @@
         <v>12</v>
       </c>
       <c r="G1" t="s">
-        <v>23</v>
+        <v>54</v>
       </c>
       <c r="H1" t="s">
-        <v>24</v>
+        <v>40</v>
       </c>
       <c r="I1" t="s">
+        <v>42</v>
+      </c>
+      <c r="J1" t="s">
+        <v>21</v>
+      </c>
+      <c r="K1" t="s">
+        <v>38</v>
+      </c>
+      <c r="L1" t="s">
         <v>36</v>
       </c>
-      <c r="J1" t="s">
-        <v>38</v>
-      </c>
-      <c r="K1" t="s">
-        <v>40</v>
-      </c>
-      <c r="L1" t="s">
-        <v>41</v>
-      </c>
       <c r="M1" t="s">
+        <v>22</v>
+      </c>
+      <c r="N1" t="s">
+        <v>31</v>
+      </c>
+      <c r="O1" t="s">
+        <v>44</v>
+      </c>
+      <c r="P1" t="s">
+        <v>45</v>
+      </c>
+      <c r="Q1" t="s">
+        <v>26</v>
+      </c>
+      <c r="R1" t="s">
+        <v>27</v>
+      </c>
+      <c r="S1" t="s">
+        <v>32</v>
+      </c>
+      <c r="T1" t="s">
+        <v>46</v>
+      </c>
+      <c r="U1" t="s">
         <v>28</v>
       </c>
-      <c r="N1" t="s">
-        <v>30</v>
-      </c>
-      <c r="O1" t="s">
-        <v>29</v>
-      </c>
-      <c r="P1" t="s">
-        <v>31</v>
+      <c r="V1" t="s">
+        <v>47</v>
+      </c>
+      <c r="W1" t="s">
+        <v>34</v>
       </c>
     </row>
-    <row r="2" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>5</v>
       </c>
@@ -639,7 +733,7 @@
         <v>14</v>
       </c>
       <c r="G2" t="s">
-        <v>19</v>
+        <v>7</v>
       </c>
       <c r="H2" t="s">
         <v>6</v>
@@ -648,28 +742,49 @@
         <v>6</v>
       </c>
       <c r="J2" t="s">
-        <v>6</v>
+        <v>19</v>
       </c>
       <c r="K2" t="s">
-        <v>6</v>
+        <v>33</v>
       </c>
       <c r="L2" t="s">
-        <v>6</v>
+        <v>33</v>
       </c>
       <c r="M2" t="s">
-        <v>6</v>
+        <v>33</v>
       </c>
       <c r="N2" t="s">
-        <v>6</v>
+        <v>19</v>
       </c>
       <c r="O2" t="s">
-        <v>6</v>
+        <v>19</v>
       </c>
       <c r="P2" t="s">
-        <v>6</v>
+        <v>19</v>
+      </c>
+      <c r="Q2" t="s">
+        <v>19</v>
+      </c>
+      <c r="R2" t="s">
+        <v>19</v>
+      </c>
+      <c r="S2" t="s">
+        <v>19</v>
+      </c>
+      <c r="T2" t="s">
+        <v>19</v>
+      </c>
+      <c r="U2" t="s">
+        <v>19</v>
+      </c>
+      <c r="V2" t="s">
+        <v>19</v>
+      </c>
+      <c r="W2" t="s">
+        <v>19</v>
       </c>
     </row>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>8</v>
       </c>
@@ -689,37 +804,58 @@
         <v>13</v>
       </c>
       <c r="G3" t="s">
-        <v>22</v>
+        <v>55</v>
       </c>
       <c r="H3" t="s">
+        <v>41</v>
+      </c>
+      <c r="I3" t="s">
+        <v>43</v>
+      </c>
+      <c r="J3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K3" t="s">
+        <v>39</v>
+      </c>
+      <c r="L3" t="s">
+        <v>37</v>
+      </c>
+      <c r="M3" t="s">
+        <v>23</v>
+      </c>
+      <c r="N3" t="s">
+        <v>24</v>
+      </c>
+      <c r="O3" t="s">
+        <v>48</v>
+      </c>
+      <c r="P3" t="s">
+        <v>49</v>
+      </c>
+      <c r="Q3" t="s">
+        <v>29</v>
+      </c>
+      <c r="R3" t="s">
+        <v>30</v>
+      </c>
+      <c r="S3" t="s">
         <v>25</v>
       </c>
-      <c r="I3" t="s">
-        <v>26</v>
-      </c>
-      <c r="J3" t="s">
-        <v>39</v>
-      </c>
-      <c r="K3" t="s">
-        <v>37</v>
-      </c>
-      <c r="L3" t="s">
-        <v>27</v>
-      </c>
-      <c r="M3" t="s">
-        <v>33</v>
-      </c>
-      <c r="N3" t="s">
-        <v>32</v>
-      </c>
-      <c r="O3" t="s">
-        <v>34</v>
-      </c>
-      <c r="P3" t="s">
+      <c r="T3" t="s">
+        <v>50</v>
+      </c>
+      <c r="U3" t="s">
         <v>35</v>
       </c>
+      <c r="V3" t="s">
+        <v>51</v>
+      </c>
+      <c r="W3" t="s">
+        <v>52</v>
+      </c>
     </row>
-    <row r="4" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:23" x14ac:dyDescent="0.2">
       <c r="B4">
         <v>1</v>
       </c>
@@ -736,26 +872,26 @@
         <v>16</v>
       </c>
       <c r="G4" t="s">
-        <v>20</v>
+        <v>56</v>
       </c>
       <c r="H4">
+        <v>1</v>
+      </c>
+      <c r="I4">
+        <v>1</v>
+      </c>
+      <c r="J4">
+        <v>1</v>
+      </c>
+      <c r="K4">
+        <v>50</v>
+      </c>
+      <c r="L4">
+        <v>50</v>
+      </c>
+      <c r="M4">
         <v>130</v>
       </c>
-      <c r="I4">
-        <v>1</v>
-      </c>
-      <c r="J4">
-        <v>1</v>
-      </c>
-      <c r="K4">
-        <v>1</v>
-      </c>
-      <c r="L4">
-        <v>1</v>
-      </c>
-      <c r="M4">
-        <v>1</v>
-      </c>
       <c r="N4">
         <v>1</v>
       </c>
@@ -765,8 +901,29 @@
       <c r="P4">
         <v>1</v>
       </c>
+      <c r="Q4">
+        <v>1</v>
+      </c>
+      <c r="R4">
+        <v>1</v>
+      </c>
+      <c r="S4">
+        <v>1</v>
+      </c>
+      <c r="T4">
+        <v>1</v>
+      </c>
+      <c r="U4">
+        <v>1</v>
+      </c>
+      <c r="V4">
+        <v>1</v>
+      </c>
+      <c r="W4">
+        <v>1</v>
+      </c>
     </row>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:23" x14ac:dyDescent="0.2">
       <c r="B5">
         <v>2</v>
       </c>
@@ -783,26 +940,26 @@
         <v>15</v>
       </c>
       <c r="G5" t="s">
-        <v>21</v>
+        <v>57</v>
       </c>
       <c r="H5">
+        <v>2</v>
+      </c>
+      <c r="I5">
+        <v>2</v>
+      </c>
+      <c r="J5">
+        <v>1</v>
+      </c>
+      <c r="K5">
+        <v>50</v>
+      </c>
+      <c r="L5">
+        <v>50</v>
+      </c>
+      <c r="M5">
         <v>120</v>
       </c>
-      <c r="I5">
-        <v>1</v>
-      </c>
-      <c r="J5">
-        <v>1</v>
-      </c>
-      <c r="K5">
-        <v>1</v>
-      </c>
-      <c r="L5">
-        <v>1</v>
-      </c>
-      <c r="M5">
-        <v>1</v>
-      </c>
       <c r="N5">
         <v>1</v>
       </c>
@@ -810,6 +967,95 @@
         <v>1</v>
       </c>
       <c r="P5">
+        <v>1</v>
+      </c>
+      <c r="Q5">
+        <v>1</v>
+      </c>
+      <c r="R5">
+        <v>1</v>
+      </c>
+      <c r="S5">
+        <v>1</v>
+      </c>
+      <c r="T5">
+        <v>1</v>
+      </c>
+      <c r="U5">
+        <v>1</v>
+      </c>
+      <c r="V5">
+        <v>1</v>
+      </c>
+      <c r="W5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="B6">
+        <v>3</v>
+      </c>
+      <c r="C6" t="s">
+        <v>53</v>
+      </c>
+      <c r="D6" t="s">
+        <v>53</v>
+      </c>
+      <c r="E6">
+        <v>100</v>
+      </c>
+      <c r="F6" t="s">
+        <v>15</v>
+      </c>
+      <c r="G6" t="s">
+        <v>58</v>
+      </c>
+      <c r="H6">
+        <v>2</v>
+      </c>
+      <c r="I6">
+        <v>2</v>
+      </c>
+      <c r="J6">
+        <v>1</v>
+      </c>
+      <c r="K6">
+        <v>50</v>
+      </c>
+      <c r="L6">
+        <v>50</v>
+      </c>
+      <c r="M6">
+        <v>120</v>
+      </c>
+      <c r="N6">
+        <v>1</v>
+      </c>
+      <c r="O6">
+        <v>1</v>
+      </c>
+      <c r="P6">
+        <v>1</v>
+      </c>
+      <c r="Q6">
+        <v>1</v>
+      </c>
+      <c r="R6">
+        <v>1</v>
+      </c>
+      <c r="S6">
+        <v>1</v>
+      </c>
+      <c r="T6">
+        <v>1</v>
+      </c>
+      <c r="U6">
+        <v>1</v>
+      </c>
+      <c r="V6">
+        <v>1</v>
+      </c>
+      <c r="W6">
         <v>1</v>
       </c>
     </row>

--- a/Luban/Config/Datas/#BattleSkillConfig.xlsx
+++ b/Luban/Config/Datas/#BattleSkillConfig.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28925"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Project\Return0\Luban\Config\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{635C6BC6-261C-4306-9694-B4CCF462DF0D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{961F1470-0222-4BB8-9089-93C04206B5FC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{53B3FBB6-B116-408D-BCC0-737AAAC6C9D0}"/>
+    <workbookView xWindow="4995" yWindow="4455" windowWidth="28800" windowHeight="15345" xr2:uid="{53B3FBB6-B116-408D-BCC0-737AAAC6C9D0}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -267,7 +267,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -282,6 +282,13 @@
       <family val="2"/>
       <charset val="134"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="微软雅黑"/>
+      <family val="2"/>
+      <charset val="134"/>
     </font>
   </fonts>
   <fills count="2">
@@ -306,9 +313,12 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -625,437 +635,440 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8D4CF470-E9E0-44FF-BA6C-71B5C42FB7B2}">
   <dimension ref="A1:W6"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="6" max="9" width="17.5" customWidth="1"/>
-    <col min="10" max="10" width="14.125" customWidth="1"/>
-    <col min="12" max="12" width="14.125" customWidth="1"/>
-    <col min="13" max="13" width="17.5" customWidth="1"/>
-    <col min="14" max="14" width="41.25" customWidth="1"/>
-    <col min="15" max="15" width="24.125" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="22.375" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="17.75" customWidth="1"/>
-    <col min="18" max="18" width="17.5" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="22.25" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="27.5" customWidth="1"/>
-    <col min="21" max="21" width="18.625" bestFit="1" customWidth="1"/>
-    <col min="22" max="23" width="17.75" bestFit="1" customWidth="1"/>
+    <col min="1" max="5" width="9" style="1"/>
+    <col min="6" max="9" width="17.5" style="1" customWidth="1"/>
+    <col min="10" max="10" width="14.125" style="1" customWidth="1"/>
+    <col min="11" max="11" width="9" style="1"/>
+    <col min="12" max="12" width="14.125" style="1" customWidth="1"/>
+    <col min="13" max="13" width="17.5" style="1" customWidth="1"/>
+    <col min="14" max="14" width="41.25" style="1" customWidth="1"/>
+    <col min="15" max="15" width="24.125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="22.375" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="17.75" style="1" customWidth="1"/>
+    <col min="18" max="18" width="17.5" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="22.25" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="27.5" style="1" customWidth="1"/>
+    <col min="21" max="21" width="18.625" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="17.75" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:23" x14ac:dyDescent="0.2">
-      <c r="A1" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" t="s">
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" t="s">
+      <c r="F1" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="G1" t="s">
+      <c r="G1" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="H1" t="s">
+      <c r="H1" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="I1" t="s">
+      <c r="I1" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="J1" t="s">
+      <c r="J1" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="K1" t="s">
+      <c r="K1" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="L1" t="s">
+      <c r="L1" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="M1" t="s">
+      <c r="M1" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="N1" t="s">
+      <c r="N1" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="O1" t="s">
+      <c r="O1" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="P1" t="s">
+      <c r="P1" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="Q1" t="s">
+      <c r="Q1" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="R1" t="s">
+      <c r="R1" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="S1" t="s">
+      <c r="S1" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="T1" t="s">
+      <c r="T1" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="U1" t="s">
+      <c r="U1" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="V1" t="s">
+      <c r="V1" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="W1" t="s">
+      <c r="W1" s="1" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="2" spans="1:23" x14ac:dyDescent="0.2">
-      <c r="A2" t="s">
+      <c r="A2" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C2" t="s">
+      <c r="C2" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="D2" t="s">
+      <c r="D2" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="E2" t="s">
+      <c r="E2" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="F2" t="s">
+      <c r="F2" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="G2" t="s">
+      <c r="G2" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="H2" t="s">
+      <c r="H2" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="I2" t="s">
+      <c r="I2" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="J2" t="s">
+      <c r="J2" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="K2" t="s">
+      <c r="K2" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="L2" t="s">
+      <c r="L2" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="M2" t="s">
+      <c r="M2" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="N2" t="s">
+      <c r="N2" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="O2" t="s">
+      <c r="O2" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="P2" t="s">
+      <c r="P2" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="Q2" t="s">
+      <c r="Q2" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="R2" t="s">
+      <c r="R2" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="S2" t="s">
+      <c r="S2" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="T2" t="s">
+      <c r="T2" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="U2" t="s">
+      <c r="U2" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="V2" t="s">
+      <c r="V2" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="W2" t="s">
+      <c r="W2" s="1" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="3" spans="1:23" x14ac:dyDescent="0.2">
-      <c r="A3" t="s">
+      <c r="A3" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="B3" t="s">
-        <v>1</v>
-      </c>
-      <c r="C3" t="s">
+      <c r="B3" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C3" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="D3" t="s">
+      <c r="D3" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="E3" t="s">
+      <c r="E3" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="F3" t="s">
+      <c r="F3" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="G3" t="s">
+      <c r="G3" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="H3" t="s">
+      <c r="H3" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="I3" t="s">
+      <c r="I3" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="J3" t="s">
+      <c r="J3" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="K3" t="s">
+      <c r="K3" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="L3" t="s">
+      <c r="L3" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="M3" t="s">
+      <c r="M3" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="N3" t="s">
+      <c r="N3" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="O3" t="s">
+      <c r="O3" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="P3" t="s">
+      <c r="P3" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="Q3" t="s">
+      <c r="Q3" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="R3" t="s">
+      <c r="R3" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="S3" t="s">
+      <c r="S3" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="T3" t="s">
+      <c r="T3" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="U3" t="s">
+      <c r="U3" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="V3" t="s">
+      <c r="V3" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="W3" t="s">
+      <c r="W3" s="1" t="s">
         <v>52</v>
       </c>
     </row>
     <row r="4" spans="1:23" x14ac:dyDescent="0.2">
-      <c r="B4">
-        <v>1</v>
-      </c>
-      <c r="C4" t="s">
+      <c r="B4" s="1">
+        <v>1</v>
+      </c>
+      <c r="C4" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="D4" t="s">
+      <c r="D4" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="E4">
+      <c r="E4" s="1">
         <v>10</v>
       </c>
-      <c r="F4" t="s">
+      <c r="F4" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="G4" t="s">
+      <c r="G4" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="H4">
-        <v>1</v>
-      </c>
-      <c r="I4">
-        <v>1</v>
-      </c>
-      <c r="J4">
-        <v>1</v>
-      </c>
-      <c r="K4">
+      <c r="H4" s="1">
+        <v>1</v>
+      </c>
+      <c r="I4" s="1">
+        <v>1</v>
+      </c>
+      <c r="J4" s="1">
+        <v>1</v>
+      </c>
+      <c r="K4" s="1">
         <v>50</v>
       </c>
-      <c r="L4">
+      <c r="L4" s="1">
         <v>50</v>
       </c>
-      <c r="M4">
+      <c r="M4" s="1">
         <v>130</v>
       </c>
-      <c r="N4">
-        <v>1</v>
-      </c>
-      <c r="O4">
-        <v>1</v>
-      </c>
-      <c r="P4">
-        <v>1</v>
-      </c>
-      <c r="Q4">
-        <v>1</v>
-      </c>
-      <c r="R4">
-        <v>1</v>
-      </c>
-      <c r="S4">
-        <v>1</v>
-      </c>
-      <c r="T4">
-        <v>1</v>
-      </c>
-      <c r="U4">
-        <v>1</v>
-      </c>
-      <c r="V4">
-        <v>1</v>
-      </c>
-      <c r="W4">
+      <c r="N4" s="1">
+        <v>1</v>
+      </c>
+      <c r="O4" s="1">
+        <v>1</v>
+      </c>
+      <c r="P4" s="1">
+        <v>1</v>
+      </c>
+      <c r="Q4" s="1">
+        <v>1</v>
+      </c>
+      <c r="R4" s="1">
+        <v>1</v>
+      </c>
+      <c r="S4" s="1">
+        <v>1</v>
+      </c>
+      <c r="T4" s="1">
+        <v>1</v>
+      </c>
+      <c r="U4" s="1">
+        <v>1</v>
+      </c>
+      <c r="V4" s="1">
+        <v>1</v>
+      </c>
+      <c r="W4" s="1">
         <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:23" x14ac:dyDescent="0.2">
-      <c r="B5">
+      <c r="B5" s="1">
         <v>2</v>
       </c>
-      <c r="C5" t="s">
+      <c r="C5" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="D5" t="s">
+      <c r="D5" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="E5">
+      <c r="E5" s="1">
         <v>100</v>
       </c>
-      <c r="F5" t="s">
+      <c r="F5" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="G5" t="s">
+      <c r="G5" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="H5">
+      <c r="H5" s="1">
         <v>2</v>
       </c>
-      <c r="I5">
+      <c r="I5" s="1">
         <v>2</v>
       </c>
-      <c r="J5">
-        <v>1</v>
-      </c>
-      <c r="K5">
+      <c r="J5" s="1">
+        <v>1</v>
+      </c>
+      <c r="K5" s="1">
         <v>50</v>
       </c>
-      <c r="L5">
+      <c r="L5" s="1">
         <v>50</v>
       </c>
-      <c r="M5">
+      <c r="M5" s="1">
         <v>120</v>
       </c>
-      <c r="N5">
-        <v>1</v>
-      </c>
-      <c r="O5">
-        <v>1</v>
-      </c>
-      <c r="P5">
-        <v>1</v>
-      </c>
-      <c r="Q5">
-        <v>1</v>
-      </c>
-      <c r="R5">
-        <v>1</v>
-      </c>
-      <c r="S5">
-        <v>1</v>
-      </c>
-      <c r="T5">
-        <v>1</v>
-      </c>
-      <c r="U5">
-        <v>1</v>
-      </c>
-      <c r="V5">
-        <v>1</v>
-      </c>
-      <c r="W5">
+      <c r="N5" s="1">
+        <v>1</v>
+      </c>
+      <c r="O5" s="1">
+        <v>1</v>
+      </c>
+      <c r="P5" s="1">
+        <v>1</v>
+      </c>
+      <c r="Q5" s="1">
+        <v>1</v>
+      </c>
+      <c r="R5" s="1">
+        <v>1</v>
+      </c>
+      <c r="S5" s="1">
+        <v>1</v>
+      </c>
+      <c r="T5" s="1">
+        <v>1</v>
+      </c>
+      <c r="U5" s="1">
+        <v>1</v>
+      </c>
+      <c r="V5" s="1">
+        <v>1</v>
+      </c>
+      <c r="W5" s="1">
         <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:23" x14ac:dyDescent="0.2">
-      <c r="B6">
+      <c r="B6" s="1">
         <v>3</v>
       </c>
-      <c r="C6" t="s">
+      <c r="C6" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="D6" t="s">
+      <c r="D6" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="E6">
+      <c r="E6" s="1">
         <v>100</v>
       </c>
-      <c r="F6" t="s">
+      <c r="F6" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="G6" t="s">
+      <c r="G6" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="H6">
+      <c r="H6" s="1">
         <v>2</v>
       </c>
-      <c r="I6">
+      <c r="I6" s="1">
         <v>2</v>
       </c>
-      <c r="J6">
-        <v>1</v>
-      </c>
-      <c r="K6">
+      <c r="J6" s="1">
+        <v>1</v>
+      </c>
+      <c r="K6" s="1">
         <v>50</v>
       </c>
-      <c r="L6">
+      <c r="L6" s="1">
         <v>50</v>
       </c>
-      <c r="M6">
+      <c r="M6" s="1">
         <v>120</v>
       </c>
-      <c r="N6">
-        <v>1</v>
-      </c>
-      <c r="O6">
-        <v>1</v>
-      </c>
-      <c r="P6">
-        <v>1</v>
-      </c>
-      <c r="Q6">
-        <v>1</v>
-      </c>
-      <c r="R6">
-        <v>1</v>
-      </c>
-      <c r="S6">
-        <v>1</v>
-      </c>
-      <c r="T6">
-        <v>1</v>
-      </c>
-      <c r="U6">
-        <v>1</v>
-      </c>
-      <c r="V6">
-        <v>1</v>
-      </c>
-      <c r="W6">
+      <c r="N6" s="1">
+        <v>1</v>
+      </c>
+      <c r="O6" s="1">
+        <v>1</v>
+      </c>
+      <c r="P6" s="1">
+        <v>1</v>
+      </c>
+      <c r="Q6" s="1">
+        <v>1</v>
+      </c>
+      <c r="R6" s="1">
+        <v>1</v>
+      </c>
+      <c r="S6" s="1">
+        <v>1</v>
+      </c>
+      <c r="T6" s="1">
+        <v>1</v>
+      </c>
+      <c r="U6" s="1">
+        <v>1</v>
+      </c>
+      <c r="V6" s="1">
+        <v>1</v>
+      </c>
+      <c r="W6" s="1">
         <v>1</v>
       </c>
     </row>

--- a/Luban/Config/Datas/#BattleSkillConfig.xlsx
+++ b/Luban/Config/Datas/#BattleSkillConfig.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Project\Return0\Luban\Config\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{961F1470-0222-4BB8-9089-93C04206B5FC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AE2A94E8-608C-4D5B-8595-E189235FF622}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4995" yWindow="4455" windowWidth="28800" windowHeight="15345" xr2:uid="{53B3FBB6-B116-408D-BCC0-737AAAC6C9D0}"/>
+    <workbookView xWindow="-105" yWindow="0" windowWidth="19410" windowHeight="10545" xr2:uid="{53B3FBB6-B116-408D-BCC0-737AAAC6C9D0}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="90" uniqueCount="66">
   <si>
     <t>##var</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -43,10 +43,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>count</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>##type</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -71,34 +67,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>个数</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>list</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>null</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>(list#sep=,),string</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>qq,12</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>"aa","ss","ddff","asd"</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>技能1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>技能2</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -260,6 +228,66 @@
   </si>
   <si>
     <t>Attack3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>5</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>快速防守</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2,2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.0</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.9</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1002</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1003</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1001001,1001007</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1001008</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1001006</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1001009,1001010</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -634,28 +662,28 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8D4CF470-E9E0-44FF-BA6C-71B5C42FB7B2}">
-  <dimension ref="A1:W6"/>
+  <dimension ref="A1:U6"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="5" width="9" style="1"/>
-    <col min="6" max="9" width="17.5" style="1" customWidth="1"/>
+    <col min="1" max="4" width="9" style="1"/>
+    <col min="5" max="7" width="17.5" style="1" customWidth="1"/>
+    <col min="8" max="8" width="15.375" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="9" style="1"/>
     <col min="10" max="10" width="14.125" style="1" customWidth="1"/>
-    <col min="11" max="11" width="9" style="1"/>
-    <col min="12" max="12" width="14.125" style="1" customWidth="1"/>
-    <col min="13" max="13" width="17.5" style="1" customWidth="1"/>
-    <col min="14" max="14" width="41.25" style="1" customWidth="1"/>
-    <col min="15" max="15" width="24.125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="22.375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="17.75" style="1" customWidth="1"/>
-    <col min="18" max="18" width="17.5" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="22.25" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="27.5" style="1" customWidth="1"/>
-    <col min="21" max="21" width="18.625" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="23" width="17.75" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="16384" width="9" style="1"/>
+    <col min="11" max="11" width="17.5" style="1" customWidth="1"/>
+    <col min="12" max="12" width="41.25" style="1" customWidth="1"/>
+    <col min="13" max="13" width="24.125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="22.375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="17.75" style="1" customWidth="1"/>
+    <col min="16" max="16" width="17.5" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="22.25" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="27.5" style="1" customWidth="1"/>
+    <col min="19" max="19" width="18.625" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="17.75" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -669,407 +697,293 @@
         <v>3</v>
       </c>
       <c r="E1" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="Q1" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="R1" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="S1" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="T1" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="U1" s="1" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="2" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="A2" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="L1" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="M1" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="N1" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="O1" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="P1" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="Q1" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="R1" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="S1" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="T1" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="U1" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="V1" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="W1" s="1" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="2" spans="1:23" x14ac:dyDescent="0.2">
-      <c r="A2" s="1" t="s">
+      <c r="B2" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="C2" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C2" s="1" t="s">
-        <v>7</v>
-      </c>
       <c r="D2" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E2" s="1" t="s">
         <v>6</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="G2" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="J2" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="L2" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M2" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="N2" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="T2" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="U2" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="3" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="A3" s="1" t="s">
         <v>7</v>
-      </c>
-      <c r="H2" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="I2" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="J2" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="K2" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="L2" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="M2" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="N2" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="O2" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="P2" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="Q2" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="R2" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="S2" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="T2" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="U2" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="V2" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="W2" s="1" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="3" spans="1:23" x14ac:dyDescent="0.2">
-      <c r="A3" s="1" t="s">
-        <v>8</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C3" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D3" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="D3" s="1" t="s">
+      <c r="E3" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="H3" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="I3" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="J3" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="K3" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="L3" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="M3" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="N3" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="O3" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="P3" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q3" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="R3" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="S3" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="T3" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="U3" s="1" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="4" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="B4" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="G4" s="1">
+        <v>1</v>
+      </c>
+      <c r="H4" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="I4" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="J4" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="K4" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="L4" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="N4" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="O4" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="S4" s="1" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="5" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="B5" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="C5" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="E3" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="F3" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="G3" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="H3" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="I3" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="J3" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="K3" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="L3" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="M3" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="N3" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="O3" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="P3" s="1" t="s">
+      <c r="D5" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E5" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="Q3" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="R3" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="S3" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="T3" s="1" t="s">
+      <c r="F5" s="1">
+        <v>2</v>
+      </c>
+      <c r="G5" s="1">
+        <v>2</v>
+      </c>
+      <c r="H5" s="1">
+        <v>1</v>
+      </c>
+      <c r="I5" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="J5" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="K5" s="1" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="6" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="B6" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="E6" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="U3" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="V3" s="1" t="s">
+      <c r="F6" s="1">
+        <v>2</v>
+      </c>
+      <c r="G6" s="1">
+        <v>2</v>
+      </c>
+      <c r="H6" s="1">
+        <v>1</v>
+      </c>
+      <c r="I6" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="W3" s="1" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="4" spans="1:23" x14ac:dyDescent="0.2">
-      <c r="B4" s="1">
-        <v>1</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="E4" s="1">
-        <v>10</v>
-      </c>
-      <c r="F4" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="G4" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="H4" s="1">
-        <v>1</v>
-      </c>
-      <c r="I4" s="1">
-        <v>1</v>
-      </c>
-      <c r="J4" s="1">
-        <v>1</v>
-      </c>
-      <c r="K4" s="1">
-        <v>50</v>
-      </c>
-      <c r="L4" s="1">
-        <v>50</v>
-      </c>
-      <c r="M4" s="1">
-        <v>130</v>
-      </c>
-      <c r="N4" s="1">
-        <v>1</v>
-      </c>
-      <c r="O4" s="1">
-        <v>1</v>
-      </c>
-      <c r="P4" s="1">
-        <v>1</v>
-      </c>
-      <c r="Q4" s="1">
-        <v>1</v>
-      </c>
-      <c r="R4" s="1">
-        <v>1</v>
-      </c>
-      <c r="S4" s="1">
-        <v>1</v>
-      </c>
-      <c r="T4" s="1">
-        <v>1</v>
-      </c>
-      <c r="U4" s="1">
-        <v>1</v>
-      </c>
-      <c r="V4" s="1">
-        <v>1</v>
-      </c>
-      <c r="W4" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:23" x14ac:dyDescent="0.2">
-      <c r="B5" s="1">
-        <v>2</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="D5" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="E5" s="1">
-        <v>100</v>
-      </c>
-      <c r="F5" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="G5" s="1" t="s">
+      <c r="J6" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="K6" s="1" t="s">
         <v>57</v>
-      </c>
-      <c r="H5" s="1">
-        <v>2</v>
-      </c>
-      <c r="I5" s="1">
-        <v>2</v>
-      </c>
-      <c r="J5" s="1">
-        <v>1</v>
-      </c>
-      <c r="K5" s="1">
-        <v>50</v>
-      </c>
-      <c r="L5" s="1">
-        <v>50</v>
-      </c>
-      <c r="M5" s="1">
-        <v>120</v>
-      </c>
-      <c r="N5" s="1">
-        <v>1</v>
-      </c>
-      <c r="O5" s="1">
-        <v>1</v>
-      </c>
-      <c r="P5" s="1">
-        <v>1</v>
-      </c>
-      <c r="Q5" s="1">
-        <v>1</v>
-      </c>
-      <c r="R5" s="1">
-        <v>1</v>
-      </c>
-      <c r="S5" s="1">
-        <v>1</v>
-      </c>
-      <c r="T5" s="1">
-        <v>1</v>
-      </c>
-      <c r="U5" s="1">
-        <v>1</v>
-      </c>
-      <c r="V5" s="1">
-        <v>1</v>
-      </c>
-      <c r="W5" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:23" x14ac:dyDescent="0.2">
-      <c r="B6" s="1">
-        <v>3</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="D6" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="E6" s="1">
-        <v>100</v>
-      </c>
-      <c r="F6" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="G6" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="H6" s="1">
-        <v>2</v>
-      </c>
-      <c r="I6" s="1">
-        <v>2</v>
-      </c>
-      <c r="J6" s="1">
-        <v>1</v>
-      </c>
-      <c r="K6" s="1">
-        <v>50</v>
-      </c>
-      <c r="L6" s="1">
-        <v>50</v>
-      </c>
-      <c r="M6" s="1">
-        <v>120</v>
-      </c>
-      <c r="N6" s="1">
-        <v>1</v>
-      </c>
-      <c r="O6" s="1">
-        <v>1</v>
-      </c>
-      <c r="P6" s="1">
-        <v>1</v>
-      </c>
-      <c r="Q6" s="1">
-        <v>1</v>
-      </c>
-      <c r="R6" s="1">
-        <v>1</v>
-      </c>
-      <c r="S6" s="1">
-        <v>1</v>
-      </c>
-      <c r="T6" s="1">
-        <v>1</v>
-      </c>
-      <c r="U6" s="1">
-        <v>1</v>
-      </c>
-      <c r="V6" s="1">
-        <v>1</v>
-      </c>
-      <c r="W6" s="1">
-        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/Luban/Config/Datas/#BattleSkillConfig.xlsx
+++ b/Luban/Config/Datas/#BattleSkillConfig.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Project\Return0\Luban\Config\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AE2A94E8-608C-4D5B-8595-E189235FF622}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CC9D14AC-E6BC-4A8D-A7C5-B23C5C47F894}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-105" yWindow="0" windowWidth="19410" windowHeight="10545" xr2:uid="{53B3FBB6-B116-408D-BCC0-737AAAC6C9D0}"/>
+    <workbookView xWindow="19095" yWindow="0" windowWidth="19410" windowHeight="20985" xr2:uid="{53B3FBB6-B116-408D-BCC0-737AAAC6C9D0}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -24,8 +24,47 @@
 </workbook>
 </file>
 
+<file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+  <authors>
+    <author>Admin</author>
+  </authors>
+  <commentList>
+    <comment ref="Y3" authorId="0" shapeId="0" xr:uid="{3C3B5556-FC2D-46FC-88DD-3A72E51B7423}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="宋体"/>
+            <family val="3"/>
+            <charset val="134"/>
+          </rPr>
+          <t>Admin:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="宋体"/>
+            <family val="3"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+行动后 = 1
+下次行动前 = 2
+回合结束 = 3
+</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="90" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="315" uniqueCount="175">
   <si>
     <t>##var</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -67,10 +106,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>技能2</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>(list#sep=,),int</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -207,10 +242,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>技能3</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>AniName</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -231,10 +262,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>5</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>快速防守</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -275,19 +302,464 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>1001001,1001007</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1001008</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1001006</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1001009,1001010</t>
+    <t>起势</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3,3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>8</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1002001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1002002</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1002003</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>借力</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2,4</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1001004</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1001005,1001006</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1001003</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>息开始的扳机</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ActionWheelStartMoment</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1001002</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1001001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1003002</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1003001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1003003</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1004</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>汲苦</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2,2,1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1004001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1001007,1001008</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1003004,1003005</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1004003</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1004005</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1004006</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1004002,1004004,1004008</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1004007</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1005</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>招架</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2,2,3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1005001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1005002</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1005003</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1005004,1005005</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1005006,1005007</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>外炁屏障</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1006</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1,4,2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>25</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>技能移除扳机</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SkillRemoveMoment</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2,3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1006001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1006002</t>
+  </si>
+  <si>
+    <t>1006003,1006004</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>CalculateActionWheelMoment</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>计算息的时候扳机调用</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1007</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>风传</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2,3,3,2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>20</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1007001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1007002</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1007003,1007004</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>临阵之志</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1008</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2,2,4,1</t>
+  </si>
+  <si>
+    <t>1008001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1008002</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1008003</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>聚炁</t>
+  </si>
+  <si>
+    <t>1009</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1,1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1009001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1010</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>运玄流</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>运刚流</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1011</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1,1,3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1,1,4</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1010001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1011001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SkillPreUseDataScript</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SkillPreUse1010</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SkillPreUse1011</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1010002</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1011002</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1012</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>铩血功</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1,4,4,2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>30</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1012001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1012002</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1013</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>快服</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1014</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>披茧功</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3,1,3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1014001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1014002</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1014003</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1014004</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1015</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>汇力诀</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1,3,1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>45</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1015001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1015002</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1015003</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1016</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>玄龙灌体</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1,2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>35</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1016001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1016002</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1016003</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1016004</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1017</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>调步</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2,3,4,1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1017001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1017002</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -295,7 +767,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -316,6 +788,27 @@
       <color theme="1"/>
       <name val="微软雅黑"/>
       <family val="2"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="微软雅黑"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
   </fonts>
@@ -341,11 +834,14 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -661,29 +1157,33 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8D4CF470-E9E0-44FF-BA6C-71B5C42FB7B2}">
-  <dimension ref="A1:U6"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8D4CF470-E9E0-44FF-BA6C-71B5C42FB7B2}">
+  <dimension ref="A1:Y20"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="4" width="9" style="1"/>
-    <col min="5" max="7" width="17.5" style="1" customWidth="1"/>
-    <col min="8" max="8" width="15.375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="9" style="1"/>
-    <col min="10" max="10" width="14.125" style="1" customWidth="1"/>
-    <col min="11" max="11" width="17.5" style="1" customWidth="1"/>
-    <col min="12" max="12" width="41.25" style="1" customWidth="1"/>
-    <col min="13" max="13" width="24.125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="22.375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="17.75" style="1" customWidth="1"/>
-    <col min="16" max="16" width="17.5" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="22.25" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="27.5" style="1" customWidth="1"/>
-    <col min="19" max="19" width="18.625" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="21" width="17.75" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="16384" width="9" style="1"/>
+    <col min="5" max="5" width="22.5" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="8" width="17.5" style="1" customWidth="1"/>
+    <col min="9" max="9" width="15.375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="9" style="1"/>
+    <col min="11" max="11" width="14.125" style="1" customWidth="1"/>
+    <col min="12" max="12" width="17.5" style="1" customWidth="1"/>
+    <col min="13" max="13" width="31.75" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="41.25" style="1" customWidth="1"/>
+    <col min="16" max="16" width="24.125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="22.375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="17.75" style="1" customWidth="1"/>
+    <col min="19" max="19" width="17.5" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="22.25" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="27.5" style="1" customWidth="1"/>
+    <col min="22" max="22" width="18.625" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="17.75" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="28.125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="21.875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -697,58 +1197,70 @@
         <v>3</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>46</v>
+        <v>134</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>32</v>
+        <v>44</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="H1" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="L1" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="I1" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="L1" s="1" t="s">
+      <c r="M1" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="Q1" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="R1" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="S1" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="T1" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="M1" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="N1" s="1" t="s">
+      <c r="U1" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="O1" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="P1" s="1" t="s">
+      <c r="V1" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="Q1" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="R1" s="1" t="s">
+      <c r="W1" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="S1" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="T1" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="U1" s="1" t="s">
-        <v>26</v>
+      <c r="X1" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="Y1" s="1" t="s">
+        <v>102</v>
       </c>
     </row>
-    <row r="2" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
         <v>4</v>
       </c>
@@ -765,55 +1277,67 @@
         <v>6</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G2" s="1" t="s">
         <v>5</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="L2" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="M2" s="1" t="s">
-        <v>11</v>
+        <v>24</v>
+      </c>
+      <c r="M2" s="2" t="s">
+        <v>10</v>
       </c>
       <c r="N2" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="O2" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="P2" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="Q2" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="R2" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="S2" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T2" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="U2" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
+      </c>
+      <c r="V2" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="W2" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="X2" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="Y2" s="1" t="s">
+        <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
         <v>7</v>
       </c>
@@ -826,168 +1350,830 @@
       <c r="D3" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="E3" s="1" t="s">
+      <c r="F3" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="H3" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="I3" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="J3" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="K3" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="L3" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="M3" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="N3" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="O3" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="P3" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="Q3" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="R3" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="S3" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="T3" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="U3" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="V3" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="W3" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="X3" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="Y3" s="1" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="4" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="B4" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="G4" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="H4" s="1">
+        <v>1</v>
+      </c>
+      <c r="I4" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="J4" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="K4" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="L4" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="N4" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="O4" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="Q4" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="R4" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="V4" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="X4" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="Y4" s="1" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="5" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="B5" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="F5" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="F3" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="G3" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="H3" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="I3" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="J3" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="K3" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="L3" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="M3" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="N3" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="O3" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="P3" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="Q3" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="R3" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="S3" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="T3" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="U3" s="1" t="s">
-        <v>44</v>
+      <c r="G5" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="H5" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="I5" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="J5" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="K5" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="L5" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="N5" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="T5" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="V5" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="Y5" s="1" t="s">
+        <v>60</v>
       </c>
     </row>
-    <row r="4" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="B4" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="E4" s="1" t="s">
+    <row r="6" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="B6" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="F6" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="F4" s="1" t="s">
+      <c r="G6" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="H6" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="I6" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="J6" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="K6" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="L6" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="N6" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="O6" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="R6" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="X6" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="Y6" s="1" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="7" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="B7" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="F7" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="G7" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="H7" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="I7" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="J7" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="K7" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="L7" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="N7" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="O7" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="R7" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="U7" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="V7" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="X7" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="Y7" s="1" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="8" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="B8" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="F8" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="G8" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="H8" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="I8" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="J8" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="K8" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="L8" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="G4" s="1">
-        <v>1</v>
-      </c>
-      <c r="H4" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="I4" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="J4" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="K4" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="L4" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="N4" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="O4" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="S4" s="1" t="s">
-        <v>65</v>
+      <c r="N8" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="O8" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="R8" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="V8" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="X8" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="Y8" s="1" t="s">
+        <v>103</v>
       </c>
     </row>
-    <row r="5" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="B5" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="D5" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="E5" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="F5" s="1">
-        <v>2</v>
-      </c>
-      <c r="G5" s="1">
-        <v>2</v>
-      </c>
-      <c r="H5" s="1">
-        <v>1</v>
-      </c>
-      <c r="I5" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="J5" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="K5" s="1" t="s">
-        <v>58</v>
+    <row r="9" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="B9" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="F9" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="G9" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="H9" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="I9" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="J9" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="K9" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="L9" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="N9" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="T9" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="V9" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="Y9" s="1" t="s">
+        <v>60</v>
       </c>
     </row>
-    <row r="6" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="B6" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="D6" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="E6" s="1" t="s">
+    <row r="10" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="B10" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="F10" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="G10" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="F6" s="1">
-        <v>2</v>
-      </c>
-      <c r="G6" s="1">
-        <v>2</v>
-      </c>
-      <c r="H6" s="1">
-        <v>1</v>
-      </c>
-      <c r="I6" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="J6" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="K6" s="1" t="s">
-        <v>57</v>
+      <c r="H10" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="I10" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="J10" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="K10" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="L10" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="N10" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="T10" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="V10" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="Y10" s="1" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="11" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="B11" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="F11" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="G11" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="H11" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="I11" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="J11" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="K11" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="L11" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="N11" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="T11" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="V11" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="Y11" s="1" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="12" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="B12" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="F12" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="G12" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="H12" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="I12" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="J12" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="K12" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="L12" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="T12" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="Y12" s="1" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="13" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="B13" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="E13" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="F13" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="G13" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="H13" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="I13" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="J13" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="K13" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="L13" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="N13" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="T13" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="Y13" s="1" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="14" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="B14" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="D14" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="E14" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="F14" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="G14" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="H14" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="I14" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="J14" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="K14" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="L14" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="N14" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="T14" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="Y14" s="1" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="15" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="B15" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="D15" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="F15" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="G15" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="H15" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="I15" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="J15" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="K15" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="L15" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="T15" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="U15" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="Y15" s="1" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="16" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="B16" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="D16" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="F16" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="G16" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="H16" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="I16" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="J16" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="K16" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="L16" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="Y16" s="1" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="17" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="B17" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="D17" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="F17" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="G17" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="H17" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="I17" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="J17" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="K17" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="L17" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="N17" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="T17" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="V17" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="X17" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="Y17" s="1" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="18" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="B18" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="D18" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="F18" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="G18" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="H18" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="I18" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="J18" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="K18" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="L18" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="N18" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="T18" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="V18" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="Y18" s="1" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="19" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="B19" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="D19" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="F19" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="G19" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="H19" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="I19" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="J19" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="K19" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="L19" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="N19" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="T19" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="V19" s="1" t="s">
+        <v>168</v>
+      </c>
+      <c r="X19" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="Y19" s="1" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="20" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="B20" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>171</v>
+      </c>
+      <c r="D20" s="1" t="s">
+        <v>171</v>
+      </c>
+      <c r="F20" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="G20" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="H20" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="I20" s="1" t="s">
+        <v>172</v>
+      </c>
+      <c r="J20" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="K20" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="L20" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="T20" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="V20" s="1" t="s">
+        <v>174</v>
+      </c>
+      <c r="Y20" s="1" t="s">
+        <v>60</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <legacyDrawing r:id="rId1"/>
 </worksheet>
 </file>
--- a/Luban/Config/Datas/#BattleSkillConfig.xlsx
+++ b/Luban/Config/Datas/#BattleSkillConfig.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Project\Return0\Luban\Config\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CC9D14AC-E6BC-4A8D-A7C5-B23C5C47F894}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C1D977EA-534A-43AA-BF5B-11BDDF3BAD3D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="19095" yWindow="0" windowWidth="19410" windowHeight="20985" xr2:uid="{53B3FBB6-B116-408D-BCC0-737AAAC6C9D0}"/>
   </bookViews>
@@ -19,6 +19,15 @@
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
@@ -55,6 +64,7 @@
 行动后 = 1
 下次行动前 = 2
 回合结束 = 3
+下个回合开始 = 5
 </t>
         </r>
       </text>
@@ -64,7 +74,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="315" uniqueCount="175">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1447" uniqueCount="585">
   <si>
     <t>##var</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -278,488 +288,2103 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
+    <t>1001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1002</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1003</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>起势</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3,3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>8</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1002001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1002002</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1002003</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>借力</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2,4</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1001004</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1001003</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>息开始的扳机</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ActionWheelStartMoment</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1001002</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1001001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1003002</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1003001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1003003</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1004</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>汲苦</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2,2,1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1004001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1001007,1001008</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1003004,1003005</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1004003</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1004005</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1004002,1004004,1004008</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1004007</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1005</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>招架</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2,2,3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1005001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1005002</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1005003</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1005006,1005007</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>外炁屏障</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1006</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1,4,2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>25</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>技能移除扳机</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SkillRemoveMoment</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1006001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1006002</t>
+  </si>
+  <si>
+    <t>1006003,1006004</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>CalculateActionWheelMoment</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>计算息的时候扳机调用</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1007</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>风传</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2,3,3,2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>20</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1007001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1007002</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1007003,1007004</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>临阵之志</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1008</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2,2,4,1</t>
+  </si>
+  <si>
+    <t>1008001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1008002</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1008003</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>聚炁</t>
+  </si>
+  <si>
+    <t>1009</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1,1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1009001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1010</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>运玄流</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>运刚流</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1011</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1,1,3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1,1,4</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1010001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1011001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SkillPreUseDataScript</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SkillPreUse1010</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SkillPreUse1011</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1010002</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1011002</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1012</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>铩血功</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1,4,4,2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>30</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1012001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1012002</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1013</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>快服</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1014</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>披茧功</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3,1,3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1014001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1014002</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1014003</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1014004</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1015</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>汇力诀</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1,3,1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>45</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1015001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1015002</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1015003</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1016</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>玄龙灌体</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1,2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>35</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1016001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1016002</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1016003</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1016004</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1017</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>调步</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2,3,4,1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1017001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1017002</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1018</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>生生不息</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1,1,4,2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1018001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1018002</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1018003</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1018004</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1019</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1019002</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1019001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1019003</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1019004</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1020</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>灵归</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2,1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>5000</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1020001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1020002</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1020003</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1021</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>观</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>4,2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1021001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1021002</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1022</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1022003</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1023</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>铁筋功</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2,2,3,4</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1023001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1023002</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1023003</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1023004</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1023005,1023006</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1024</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>焚羽凌霄</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1,4,2,3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>80</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1024001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1024002</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1024003</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1025</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>40</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1025001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>10</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1025002</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1025003</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1026</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>鸩姿</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1026001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1026002</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1027</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2,3,3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1027001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1027002</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1027003,1027004</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1027005,1027006</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2,5</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>5</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1028</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>逃之夭夭</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1028001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1028002</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1028003</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1029</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>周旋</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>判断技能能否释放</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>CheckSkillDoDesition</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>CheckSkillDoDesitionRelation</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>200001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>判断技能能否释放或与（1与,2或）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3,3,3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1029001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1029002</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1030</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>遁江</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>迅速大于6层</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>在水域场景使用</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1030001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1030002</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1031</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>好戏开场</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1031001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1031002</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1032</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>围追堵截</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2,1,2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1032001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1032002</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1032003</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1032004,1032005</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1033</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>妖化</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1,1,2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>15</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1033001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1033002</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>持有猊煞状态可使用</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>200002</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1034</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>叩天门</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1034001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1034002</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1035</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>暴怒</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1700001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>剩余行动次数为1时可使用</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1036</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>舔舐伤口</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1036001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1037</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>垂身喘息</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1037003</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1037001,1037002</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1038</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>蜷缩抽搐</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1038001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1038002</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1038003</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1038004</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1038006,1038007</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1039</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>炁脉涌动</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1040</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1040001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1041</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1042</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1041001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1042001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1042003</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1041002</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1041003</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1041004</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1042002</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1042004</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1043</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1044</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1043001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1044001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1043002</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1044002</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1043003</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1044003</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1045</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1046</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1046001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1047</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1047003</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1047001,1047002,1047005</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1048</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1048001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1049</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1049001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1050</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1050001,1050002</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1050003</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1050004</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1050007,1050008</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1051</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>遮云手</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>4,2,2,3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1051001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1051002</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1051003</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1052</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>掩护我</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3,2,2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1052001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1052002</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1053</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>水戈再起</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1053001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1053002</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>上次行动若交锋失败才可使用</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1022001,1022002</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1022004</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1022005</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1039001,1039002</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1039003</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>200003</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>至少持有5层毒瘴状态才可使用</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1039004</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1001006</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1005005</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1050006</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>基法</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1</t>
+  </si>
+  <si>
+    <t>4,1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2001001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2002001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2003001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2004002</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2005002</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2006002</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2002</t>
+  </si>
+  <si>
+    <t>2003</t>
+  </si>
+  <si>
+    <t>奇术</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>杀伐技</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>4,1,2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>4,1,2,2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>90</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.4</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2004</t>
+  </si>
+  <si>
+    <t>2005</t>
+  </si>
+  <si>
+    <t>2006</t>
+  </si>
+  <si>
+    <t>引炁为刃</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>汇点一破</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>绝玄戮命</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1,3</t>
+  </si>
+  <si>
+    <t>1,3,4</t>
+  </si>
+  <si>
+    <t>1,3,4,4</t>
+  </si>
+  <si>
+    <t>9</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>49</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
     <t>1.1</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>1.0</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>0.9</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1001</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1002</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1003</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>起势</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>3,3</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>8</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1002001</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1002002</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1002003</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>借力</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>2,4</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1001004</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1001005,1001006</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1001003</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>息开始的扳机</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ActionWheelStartMoment</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1001002</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1001001</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1003002</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1003001</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1003003</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1004</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>汲苦</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>2,2,1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1004001</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1001007,1001008</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1003004,1003005</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1004003</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1004005</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1004006</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1004002,1004004,1004008</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1004007</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1005</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>招架</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>2,2,3</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1005001</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1005002</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1005003</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1005004,1005005</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1005006,1005007</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>外炁屏障</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1006</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1,4,2</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>25</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>技能移除扳机</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>SkillRemoveMoment</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>2,3</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1006001</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1006002</t>
-  </si>
-  <si>
-    <t>1006003,1006004</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>CalculateActionWheelMoment</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>计算息的时候扳机调用</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1007</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>风传</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>2,3,3,2</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>20</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1007001</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1007002</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1007003,1007004</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>临阵之志</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1008</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>2,2,4,1</t>
-  </si>
-  <si>
-    <t>1008001</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1008002</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1008003</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>聚炁</t>
-  </si>
-  <si>
-    <t>1009</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1,1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1009001</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1010</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>运玄流</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>运刚流</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1011</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1,1,3</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1,1,4</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1010001</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1011001</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>SkillPreUseDataScript</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>SkillPreUse1010</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>SkillPreUse1011</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1010002</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1011002</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1012</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>铩血功</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1,4,4,2</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>30</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1012001</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>2</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1012002</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1013</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>快服</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1014</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>披茧功</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>3,1,3</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1014001</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1014002</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1014003</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1014004</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1015</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>汇力诀</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1,3,1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>45</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1015001</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1015002</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1015003</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1016</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>玄龙灌体</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1,2</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>35</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1016001</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1016002</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1016003</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1016004</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1017</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>调步</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>2,3,4,1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1017001</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1017002</t>
+    <t>1.25</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2004001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2005001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2006001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2007</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>黭幽幻</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2,4,3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.15</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2007001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2007002</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2008</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>盗光</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1,1,2,4</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2008003</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2008002</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2008001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>贯日</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2009</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>4,4,4</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2009001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2009002</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2010</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>绝技·印月</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2011</t>
+  </si>
+  <si>
+    <t>2012</t>
+  </si>
+  <si>
+    <t>2013</t>
+  </si>
+  <si>
+    <t>2014</t>
+  </si>
+  <si>
+    <t>2015</t>
+  </si>
+  <si>
+    <t>2016</t>
+  </si>
+  <si>
+    <t>2017</t>
+  </si>
+  <si>
+    <t>2018</t>
+  </si>
+  <si>
+    <t>2019</t>
+  </si>
+  <si>
+    <t>2020</t>
+  </si>
+  <si>
+    <t>移阳秘术</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>挪阴秘术</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>卦引·天破</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>卦引·尘灭</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>卦引·雳诛</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>卦引·岚萧</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>卦引·焚眀</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>卦引·泽网</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>卦引·岳镇</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>卦引·涛绝</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3,1,1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>4,2,2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3,2,3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>4,1,4</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>4,3,3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>4,2,4</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3,4,4</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2021</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>胡乱术法</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2,1,4</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2021001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2021002</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2022</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>摒杀</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2022001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2023</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>敷宵剑</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.35</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.35</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.75</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2024</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>施力压迫</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3,3,4,1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>500</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2024001</t>
+  </si>
+  <si>
+    <t>2024002</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2024003</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2025</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2025001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2025002</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2025003</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2026</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>迭浪倾川</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3,4,3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2026001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2026002</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2026003</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2027</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>尖啸</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1,3,2,4</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>15000</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2027001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2027002</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2027003</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2028</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>森森邪气</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3,4</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2028001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2029</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2029001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2029002</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2029003</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2030</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2030001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2031</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>抹残香</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>4,3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1500</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.05</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2031001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2032</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2033</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2034</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>小</t>
+  </si>
+  <si>
+    <t>中</t>
+  </si>
+  <si>
+    <t>大</t>
+  </si>
+  <si>
+    <t>2035</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>小雷令</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2035001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2035002</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2036</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>燕子回梭</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.95</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2036001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2036002</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2036003</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2037</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>截斗运</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2037001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2038</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>苍涛破岳</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2039</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>撕裂魂魄</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1,3,1,2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.6</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2039001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2039002</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2039005</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2039003,2039004</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2040</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>红湃华雾</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>50</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2040001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2041</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>穿心煞</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2041001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2041002</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2041003</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2042</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>野火</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2042001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2042002</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2043</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>云螭一现</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2043001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2043002</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2043003</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2043004</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2044</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>薄暗虹霓</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1,3,2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2044001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2045</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>月升</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3,2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2045001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2045002</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2046</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>净阳火</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>4,1,1,4</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.45</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2046001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2046002</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2047</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>解术</t>
+  </si>
+  <si>
+    <t>2047001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>解术</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2048</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>4,1,3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2048001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2048002</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2049</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>霜连天</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>55</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2049001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2050</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>残月分江</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3,2,2,4</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2050001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2050002</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2051</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>追魂破</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1,3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2051001,2051002,2051003</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2051004</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2052</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>送长离</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2,4,4</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2052001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2053</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>过阴</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>若处于祖化身状态刚炁消耗变为玄炁消耗</t>
+  </si>
+  <si>
+    <t>2053001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2054</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>走旱势</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2054001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2054002</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -767,7 +2392,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -811,13 +2436,37 @@
       <family val="3"/>
       <charset val="134"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="微软雅黑"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -834,7 +2483,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -842,6 +2491,21 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1158,7 +2822,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8D4CF470-E9E0-44FF-BA6C-71B5C42FB7B2}">
-  <dimension ref="A1:Y20"/>
+  <dimension ref="A1:AB184"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="4" width="9" style="1"/>
@@ -1180,10 +2844,13 @@
     <col min="23" max="23" width="17.75" style="1" bestFit="1" customWidth="1"/>
     <col min="24" max="24" width="28.125" style="1" bestFit="1" customWidth="1"/>
     <col min="25" max="25" width="21.875" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="16384" width="9" style="1"/>
+    <col min="26" max="26" width="22.125" style="2" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="34.5" style="2" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="27.875" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1197,7 +2864,7 @@
         <v>3</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>134</v>
+        <v>127</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>44</v>
@@ -1221,13 +2888,13 @@
         <v>13</v>
       </c>
       <c r="M1" s="2" t="s">
-        <v>107</v>
+        <v>100</v>
       </c>
       <c r="N1" s="1" t="s">
         <v>22</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="P1" s="1" t="s">
         <v>35</v>
@@ -1257,10 +2924,19 @@
         <v>25</v>
       </c>
       <c r="Y1" s="1" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="2" spans="1:25" x14ac:dyDescent="0.2">
+        <v>96</v>
+      </c>
+      <c r="Z1" s="2" t="s">
+        <v>235</v>
+      </c>
+      <c r="AA1" s="2" t="s">
+        <v>236</v>
+      </c>
+      <c r="AB1" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
         <v>4</v>
       </c>
@@ -1336,8 +3012,14 @@
       <c r="Y2" s="1" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="3" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z2" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="AA2" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
         <v>7</v>
       </c>
@@ -1372,13 +3054,13 @@
         <v>14</v>
       </c>
       <c r="M3" s="2" t="s">
-        <v>108</v>
+        <v>101</v>
       </c>
       <c r="N3" s="1" t="s">
         <v>15</v>
       </c>
       <c r="O3" s="1" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="P3" s="1" t="s">
         <v>39</v>
@@ -1408,12 +3090,18 @@
         <v>43</v>
       </c>
       <c r="Y3" s="1" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="4" spans="1:25" x14ac:dyDescent="0.2">
+        <v>95</v>
+      </c>
+      <c r="Z3" s="2" t="s">
+        <v>234</v>
+      </c>
+      <c r="AA3" s="2" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="4" spans="1:28" x14ac:dyDescent="0.2">
       <c r="B4" s="1" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>49</v>
@@ -1440,39 +3128,39 @@
         <v>52</v>
       </c>
       <c r="L4" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="N4" s="1" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="O4" s="1" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="Q4" s="1" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="R4" s="1" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="V4" s="1" t="s">
-        <v>69</v>
+        <v>350</v>
       </c>
       <c r="X4" s="1" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="Y4" s="1" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="5" spans="1:25" x14ac:dyDescent="0.2">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="5" spans="1:28" x14ac:dyDescent="0.2">
       <c r="B5" s="1" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="F5" s="1" t="s">
         <v>47</v>
@@ -1481,42 +3169,42 @@
         <v>50</v>
       </c>
       <c r="H5" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="I5" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="J5" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="K5" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="L5" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="N5" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="I5" s="1" t="s">
+      <c r="T5" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="J5" s="1" t="s">
+      <c r="V5" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="K5" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="L5" s="1" t="s">
+      <c r="Y5" s="1" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="6" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="B6" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="N5" s="1" t="s">
+      <c r="C6" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="T5" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="V5" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="Y5" s="1" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="6" spans="1:25" x14ac:dyDescent="0.2">
-      <c r="B6" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>66</v>
-      </c>
       <c r="D6" s="1" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="F6" s="1" t="s">
         <v>48</v>
@@ -1525,10 +3213,10 @@
         <v>50</v>
       </c>
       <c r="H6" s="1" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="J6" s="1" t="s">
         <v>52</v>
@@ -1537,33 +3225,33 @@
         <v>52</v>
       </c>
       <c r="L6" s="1" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="N6" s="1" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="O6" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="R6" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="X6" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="Y6" s="1" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="7" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="B7" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="C7" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="R6" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="X6" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="Y6" s="1" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="7" spans="1:25" x14ac:dyDescent="0.2">
-      <c r="B7" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="C7" s="1" t="s">
-        <v>79</v>
-      </c>
       <c r="D7" s="1" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="F7" s="1" t="s">
         <v>46</v>
@@ -1572,51 +3260,48 @@
         <v>50</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="I7" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="J7" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="K7" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="L7" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="N7" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="O7" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="J7" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="K7" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="L7" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="N7" s="1" t="s">
+      <c r="R7" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="O7" s="1" t="s">
+      <c r="U7" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="X7" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="Y7" s="1" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="8" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="B8" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="R7" s="1" t="s">
+      <c r="C8" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="U7" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="V7" s="1" t="s">
-        <v>86</v>
-      </c>
-      <c r="X7" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="Y7" s="1" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="8" spans="1:25" x14ac:dyDescent="0.2">
-      <c r="B8" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="C8" s="1" t="s">
-        <v>90</v>
-      </c>
       <c r="D8" s="1" t="s">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="F8" s="1" t="s">
         <v>46</v>
@@ -1625,48 +3310,48 @@
         <v>50</v>
       </c>
       <c r="H8" s="1" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="I8" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="J8" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="K8" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="L8" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="N8" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="O8" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="R8" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="V8" s="1" t="s">
+        <v>351</v>
+      </c>
+      <c r="X8" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="Y8" s="1" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="9" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="B9" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="C9" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="J8" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="K8" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="L8" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="N8" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="O8" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="R8" s="1" t="s">
-        <v>94</v>
-      </c>
-      <c r="V8" s="1" t="s">
-        <v>95</v>
-      </c>
-      <c r="X8" s="1" t="s">
-        <v>96</v>
-      </c>
-      <c r="Y8" s="1" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="9" spans="1:25" x14ac:dyDescent="0.2">
-      <c r="B9" s="1" t="s">
-        <v>98</v>
-      </c>
-      <c r="C9" s="1" t="s">
-        <v>97</v>
-      </c>
       <c r="D9" s="1" t="s">
-        <v>97</v>
+        <v>91</v>
       </c>
       <c r="F9" s="1" t="s">
         <v>46</v>
@@ -1675,42 +3360,42 @@
         <v>50</v>
       </c>
       <c r="H9" s="1" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="I9" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="J9" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="K9" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="L9" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="N9" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="T9" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="V9" s="1" t="s">
         <v>99</v>
       </c>
-      <c r="J9" s="1" t="s">
-        <v>100</v>
-      </c>
-      <c r="K9" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="L9" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="N9" s="1" t="s">
-        <v>104</v>
-      </c>
-      <c r="T9" s="1" t="s">
-        <v>105</v>
-      </c>
-      <c r="V9" s="1" t="s">
-        <v>106</v>
-      </c>
       <c r="Y9" s="1" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="10" spans="1:25" x14ac:dyDescent="0.2">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="10" spans="1:28" x14ac:dyDescent="0.2">
       <c r="B10" s="1" t="s">
-        <v>109</v>
+        <v>102</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>110</v>
+        <v>103</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>110</v>
+        <v>103</v>
       </c>
       <c r="F10" s="1" t="s">
         <v>46</v>
@@ -1719,42 +3404,42 @@
         <v>50</v>
       </c>
       <c r="H10" s="1" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="I10" s="1" t="s">
-        <v>111</v>
+        <v>104</v>
       </c>
       <c r="J10" s="1" t="s">
-        <v>112</v>
+        <v>105</v>
       </c>
       <c r="K10" s="1" t="s">
         <v>52</v>
       </c>
       <c r="L10" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="N10" s="1" t="s">
-        <v>113</v>
+        <v>106</v>
       </c>
       <c r="T10" s="1" t="s">
-        <v>114</v>
+        <v>107</v>
       </c>
       <c r="V10" s="1" t="s">
-        <v>115</v>
+        <v>108</v>
       </c>
       <c r="Y10" s="1" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="11" spans="1:25" x14ac:dyDescent="0.2">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="11" spans="1:28" x14ac:dyDescent="0.2">
       <c r="B11" s="1" t="s">
-        <v>117</v>
+        <v>110</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>116</v>
+        <v>109</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>116</v>
+        <v>109</v>
       </c>
       <c r="F11" s="1" t="s">
         <v>46</v>
@@ -1763,42 +3448,42 @@
         <v>50</v>
       </c>
       <c r="H11" s="1" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="I11" s="1" t="s">
-        <v>118</v>
+        <v>111</v>
       </c>
       <c r="J11" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="K11" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="L11" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="N11" s="1" t="s">
         <v>112</v>
       </c>
-      <c r="K11" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="L11" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="N11" s="1" t="s">
-        <v>119</v>
-      </c>
       <c r="T11" s="1" t="s">
-        <v>120</v>
+        <v>113</v>
       </c>
       <c r="V11" s="1" t="s">
-        <v>121</v>
+        <v>114</v>
       </c>
       <c r="Y11" s="1" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="12" spans="1:25" x14ac:dyDescent="0.2">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="12" spans="1:28" x14ac:dyDescent="0.2">
       <c r="B12" s="1" t="s">
-        <v>123</v>
+        <v>116</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>122</v>
+        <v>115</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>122</v>
+        <v>115</v>
       </c>
       <c r="F12" s="1" t="s">
         <v>46</v>
@@ -1807,10 +3492,10 @@
         <v>50</v>
       </c>
       <c r="H12" s="1" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="I12" s="1" t="s">
-        <v>124</v>
+        <v>117</v>
       </c>
       <c r="J12" s="1" t="s">
         <v>52</v>
@@ -1819,27 +3504,27 @@
         <v>52</v>
       </c>
       <c r="L12" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="T12" s="1" t="s">
-        <v>125</v>
+        <v>118</v>
       </c>
       <c r="Y12" s="1" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="13" spans="1:25" x14ac:dyDescent="0.2">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="13" spans="1:28" x14ac:dyDescent="0.2">
       <c r="B13" s="1" t="s">
-        <v>126</v>
+        <v>119</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>127</v>
+        <v>120</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>127</v>
+        <v>120</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>135</v>
+        <v>128</v>
       </c>
       <c r="F13" s="1" t="s">
         <v>46</v>
@@ -1848,42 +3533,42 @@
         <v>50</v>
       </c>
       <c r="H13" s="1" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="I13" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="J13" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="K13" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="L13" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="N13" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="T13" s="1" t="s">
         <v>130</v>
       </c>
-      <c r="J13" s="1" t="s">
-        <v>112</v>
-      </c>
-      <c r="K13" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="L13" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="N13" s="1" t="s">
-        <v>132</v>
-      </c>
-      <c r="T13" s="1" t="s">
-        <v>137</v>
-      </c>
       <c r="Y13" s="1" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="14" spans="1:25" x14ac:dyDescent="0.2">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="14" spans="1:28" x14ac:dyDescent="0.2">
       <c r="B14" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="D14" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="E14" s="1" t="s">
         <v>129</v>
-      </c>
-      <c r="C14" s="1" t="s">
-        <v>128</v>
-      </c>
-      <c r="D14" s="1" t="s">
-        <v>128</v>
-      </c>
-      <c r="E14" s="1" t="s">
-        <v>136</v>
       </c>
       <c r="F14" s="1" t="s">
         <v>46</v>
@@ -1892,39 +3577,39 @@
         <v>50</v>
       </c>
       <c r="H14" s="1" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="I14" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="J14" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="K14" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="L14" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="N14" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="T14" s="1" t="s">
         <v>131</v>
       </c>
-      <c r="J14" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="K14" s="1" t="s">
-        <v>112</v>
-      </c>
-      <c r="L14" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="N14" s="1" t="s">
+      <c r="Y14" s="1" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="15" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="B15" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="C15" s="1" t="s">
         <v>133</v>
       </c>
-      <c r="T14" s="1" t="s">
-        <v>138</v>
-      </c>
-      <c r="Y14" s="1" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="15" spans="1:25" x14ac:dyDescent="0.2">
-      <c r="B15" s="1" t="s">
-        <v>139</v>
-      </c>
-      <c r="C15" s="1" t="s">
-        <v>140</v>
-      </c>
       <c r="D15" s="1" t="s">
-        <v>140</v>
+        <v>133</v>
       </c>
       <c r="F15" s="1" t="s">
         <v>46</v>
@@ -1933,39 +3618,39 @@
         <v>50</v>
       </c>
       <c r="H15" s="1" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="I15" s="1" t="s">
-        <v>141</v>
+        <v>134</v>
       </c>
       <c r="J15" s="1" t="s">
-        <v>142</v>
+        <v>135</v>
       </c>
       <c r="K15" s="1" t="s">
         <v>52</v>
       </c>
       <c r="L15" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="T15" s="1" t="s">
-        <v>143</v>
+        <v>136</v>
       </c>
       <c r="U15" s="1" t="s">
-        <v>145</v>
+        <v>138</v>
       </c>
       <c r="Y15" s="1" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="16" spans="1:25" x14ac:dyDescent="0.2">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="16" spans="1:28" x14ac:dyDescent="0.2">
       <c r="B16" s="1" t="s">
-        <v>146</v>
+        <v>139</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>147</v>
+        <v>140</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>147</v>
+        <v>140</v>
       </c>
       <c r="F16" s="1" t="s">
         <v>46</v>
@@ -1974,7 +3659,7 @@
         <v>50</v>
       </c>
       <c r="H16" s="1" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="I16" s="1" t="s">
         <v>50</v>
@@ -1989,18 +3674,18 @@
         <v>52</v>
       </c>
       <c r="Y16" s="1" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="17" spans="2:25" x14ac:dyDescent="0.2">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="17" spans="2:28" x14ac:dyDescent="0.2">
       <c r="B17" s="1" t="s">
-        <v>148</v>
+        <v>141</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>149</v>
+        <v>142</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>149</v>
+        <v>142</v>
       </c>
       <c r="F17" s="1" t="s">
         <v>46</v>
@@ -2009,45 +3694,45 @@
         <v>50</v>
       </c>
       <c r="H17" s="1" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="I17" s="1" t="s">
-        <v>150</v>
+        <v>143</v>
       </c>
       <c r="J17" s="1" t="s">
         <v>52</v>
       </c>
       <c r="K17" s="1" t="s">
-        <v>100</v>
+        <v>94</v>
       </c>
       <c r="L17" s="1" t="s">
         <v>52</v>
       </c>
       <c r="N17" s="1" t="s">
-        <v>151</v>
+        <v>144</v>
       </c>
       <c r="T17" s="1" t="s">
-        <v>152</v>
+        <v>145</v>
       </c>
       <c r="V17" s="1" t="s">
-        <v>153</v>
+        <v>146</v>
       </c>
       <c r="X17" s="1" t="s">
-        <v>154</v>
+        <v>147</v>
       </c>
       <c r="Y17" s="1" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="18" spans="2:25" x14ac:dyDescent="0.2">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="18" spans="2:28" x14ac:dyDescent="0.2">
       <c r="B18" s="1" t="s">
-        <v>155</v>
+        <v>148</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>156</v>
+        <v>149</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>156</v>
+        <v>149</v>
       </c>
       <c r="F18" s="1" t="s">
         <v>46</v>
@@ -2056,13 +3741,13 @@
         <v>50</v>
       </c>
       <c r="H18" s="1" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="I18" s="1" t="s">
-        <v>157</v>
+        <v>150</v>
       </c>
       <c r="J18" s="1" t="s">
-        <v>158</v>
+        <v>151</v>
       </c>
       <c r="K18" s="1" t="s">
         <v>52</v>
@@ -2071,27 +3756,27 @@
         <v>52</v>
       </c>
       <c r="N18" s="1" t="s">
-        <v>159</v>
+        <v>152</v>
       </c>
       <c r="T18" s="1" t="s">
-        <v>160</v>
+        <v>153</v>
       </c>
       <c r="V18" s="1" t="s">
-        <v>161</v>
+        <v>154</v>
       </c>
       <c r="Y18" s="1" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="19" spans="2:25" x14ac:dyDescent="0.2">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="19" spans="2:28" x14ac:dyDescent="0.2">
       <c r="B19" s="1" t="s">
-        <v>162</v>
+        <v>155</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>163</v>
+        <v>156</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>163</v>
+        <v>156</v>
       </c>
       <c r="F19" s="1" t="s">
         <v>46</v>
@@ -2100,45 +3785,45 @@
         <v>50</v>
       </c>
       <c r="H19" s="1" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="I19" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="J19" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="K19" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="L19" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="N19" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="T19" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="V19" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="X19" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="Y19" s="1" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="20" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="B20" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="C20" s="1" t="s">
         <v>164</v>
       </c>
-      <c r="J19" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="K19" s="1" t="s">
-        <v>165</v>
-      </c>
-      <c r="L19" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="N19" s="1" t="s">
-        <v>166</v>
-      </c>
-      <c r="T19" s="1" t="s">
-        <v>167</v>
-      </c>
-      <c r="V19" s="1" t="s">
-        <v>168</v>
-      </c>
-      <c r="X19" s="1" t="s">
-        <v>169</v>
-      </c>
-      <c r="Y19" s="1" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="20" spans="2:25" x14ac:dyDescent="0.2">
-      <c r="B20" s="1" t="s">
-        <v>170</v>
-      </c>
-      <c r="C20" s="1" t="s">
-        <v>171</v>
-      </c>
       <c r="D20" s="1" t="s">
-        <v>171</v>
+        <v>164</v>
       </c>
       <c r="F20" s="1" t="s">
         <v>46</v>
@@ -2147,29 +3832,3605 @@
         <v>50</v>
       </c>
       <c r="H20" s="1" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="I20" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="J20" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="K20" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="L20" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="T20" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="V20" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="Y20" s="1" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="21" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="B21" s="1" t="s">
+        <v>168</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="D21" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="F21" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="G21" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="H21" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="I21" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="J21" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="K21" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="L21" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="N21" s="1" t="s">
+        <v>171</v>
+      </c>
+      <c r="T21" s="1" t="s">
         <v>172</v>
       </c>
-      <c r="J20" s="1" t="s">
-        <v>142</v>
-      </c>
-      <c r="K20" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="L20" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="T20" s="1" t="s">
+      <c r="V21" s="1" t="s">
         <v>173</v>
       </c>
-      <c r="V20" s="1" t="s">
+      <c r="X21" s="1" t="s">
         <v>174</v>
       </c>
-      <c r="Y20" s="1" t="s">
-        <v>60</v>
-      </c>
+      <c r="Y21" s="1" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="22" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="B22" s="1" t="s">
+        <v>175</v>
+      </c>
+      <c r="C22" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="D22" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="F22" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="G22" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="H22" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="I22" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="J22" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="K22" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="L22" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="N22" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="T22" s="1" t="s">
+        <v>176</v>
+      </c>
+      <c r="V22" s="1" t="s">
+        <v>178</v>
+      </c>
+      <c r="X22" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="Y22" s="1" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="23" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="B23" s="1" t="s">
+        <v>180</v>
+      </c>
+      <c r="C23" s="1" t="s">
+        <v>181</v>
+      </c>
+      <c r="D23" s="1" t="s">
+        <v>181</v>
+      </c>
+      <c r="F23" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="G23" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="H23" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="I23" s="1" t="s">
+        <v>182</v>
+      </c>
+      <c r="J23" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="K23" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="L23" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="N23" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="T23" s="1" t="s">
+        <v>185</v>
+      </c>
+      <c r="V23" s="1" t="s">
+        <v>186</v>
+      </c>
+      <c r="Y23" s="1" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="24" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="B24" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="C24" s="1" t="s">
+        <v>188</v>
+      </c>
+      <c r="D24" s="1" t="s">
+        <v>188</v>
+      </c>
+      <c r="F24" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="G24" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="H24" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="I24" s="1" t="s">
+        <v>189</v>
+      </c>
+      <c r="J24" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="K24" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="L24" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="N24" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="T24" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="Y24" s="1" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="25" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="B25" s="1" t="s">
+        <v>192</v>
+      </c>
+      <c r="C25" s="1" t="s">
+        <v>181</v>
+      </c>
+      <c r="D25" s="1" t="s">
+        <v>181</v>
+      </c>
+      <c r="F25" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="G25" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="H25" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="I25" s="1" t="s">
+        <v>182</v>
+      </c>
+      <c r="J25" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="K25" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="L25" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="N25" s="1" t="s">
+        <v>342</v>
+      </c>
+      <c r="T25" s="1" t="s">
+        <v>193</v>
+      </c>
+      <c r="V25" s="1" t="s">
+        <v>343</v>
+      </c>
+      <c r="X25" s="1" t="s">
+        <v>344</v>
+      </c>
+      <c r="Y25" s="1" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="26" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="B26" s="1" t="s">
+        <v>194</v>
+      </c>
+      <c r="C26" s="1" t="s">
+        <v>195</v>
+      </c>
+      <c r="D26" s="1" t="s">
+        <v>195</v>
+      </c>
+      <c r="F26" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="G26" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="H26" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="I26" s="1" t="s">
+        <v>196</v>
+      </c>
+      <c r="J26" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="K26" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="L26" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="N26" s="1" t="s">
+        <v>197</v>
+      </c>
+      <c r="O26" s="1" t="s">
+        <v>198</v>
+      </c>
+      <c r="R26" s="1" t="s">
+        <v>199</v>
+      </c>
+      <c r="V26" s="1" t="s">
+        <v>200</v>
+      </c>
+      <c r="X26" s="1" t="s">
+        <v>201</v>
+      </c>
+      <c r="Y26" s="1" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="27" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="B27" s="1" t="s">
+        <v>202</v>
+      </c>
+      <c r="C27" s="1" t="s">
+        <v>203</v>
+      </c>
+      <c r="D27" s="1" t="s">
+        <v>203</v>
+      </c>
+      <c r="F27" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="G27" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="H27" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="I27" s="1" t="s">
+        <v>204</v>
+      </c>
+      <c r="J27" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="K27" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="L27" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="N27" s="1" t="s">
+        <v>206</v>
+      </c>
+      <c r="T27" s="1" t="s">
+        <v>207</v>
+      </c>
+      <c r="V27" s="1" t="s">
+        <v>208</v>
+      </c>
+      <c r="Y27" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="Z27" s="4"/>
+      <c r="AA27" s="4"/>
+    </row>
+    <row r="28" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="B28" s="1" t="s">
+        <v>209</v>
+      </c>
+      <c r="C28" s="1" t="s">
+        <v>209</v>
+      </c>
+      <c r="D28" s="1" t="s">
+        <v>209</v>
+      </c>
+      <c r="F28" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="G28" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="H28" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="J28" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="K28" s="1" t="s">
+        <v>210</v>
+      </c>
+      <c r="L28" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="N28" s="1" t="s">
+        <v>211</v>
+      </c>
+      <c r="T28" s="1" t="s">
+        <v>213</v>
+      </c>
+      <c r="V28" s="1" t="s">
+        <v>214</v>
+      </c>
+      <c r="Y28" s="1" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="29" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="B29" s="1" t="s">
+        <v>215</v>
+      </c>
+      <c r="C29" s="1" t="s">
+        <v>216</v>
+      </c>
+      <c r="D29" s="1" t="s">
+        <v>216</v>
+      </c>
+      <c r="F29" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="G29" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="H29" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="I29" s="1" t="s">
+        <v>220</v>
+      </c>
+      <c r="J29" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="K29" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="L29" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="N29" s="1" t="s">
+        <v>217</v>
+      </c>
+      <c r="T29" s="1" t="s">
+        <v>218</v>
+      </c>
+      <c r="Y29" s="1" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="30" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="B30" s="1" t="s">
+        <v>219</v>
+      </c>
+      <c r="C30" s="1" t="s">
+        <v>219</v>
+      </c>
+      <c r="D30" s="1" t="s">
+        <v>219</v>
+      </c>
+      <c r="F30" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="G30" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="H30" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="I30" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="J30" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="K30" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="L30" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="N30" s="1" t="s">
+        <v>221</v>
+      </c>
+      <c r="O30" s="1" t="s">
+        <v>222</v>
+      </c>
+      <c r="R30" s="1" t="s">
+        <v>223</v>
+      </c>
+      <c r="X30" s="1" t="s">
+        <v>224</v>
+      </c>
+      <c r="Y30" s="1" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="31" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="B31" s="1" t="s">
+        <v>227</v>
+      </c>
+      <c r="C31" s="1" t="s">
+        <v>228</v>
+      </c>
+      <c r="D31" s="1" t="s">
+        <v>228</v>
+      </c>
+      <c r="F31" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="G31" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="H31" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="J31" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="K31" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="L31" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="N31" s="1" t="s">
+        <v>229</v>
+      </c>
+      <c r="T31" s="1" t="s">
+        <v>230</v>
+      </c>
+      <c r="X31" s="1" t="s">
+        <v>231</v>
+      </c>
+      <c r="Y31" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="Z31" s="2" t="s">
+        <v>237</v>
+      </c>
+      <c r="AA31" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="AB31" s="1" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="32" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="B32" s="1" t="s">
+        <v>232</v>
+      </c>
+      <c r="C32" s="1" t="s">
+        <v>233</v>
+      </c>
+      <c r="D32" s="1" t="s">
+        <v>233</v>
+      </c>
+      <c r="F32" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="G32" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="H32" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="I32" s="1" t="s">
+        <v>239</v>
+      </c>
+      <c r="J32" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="K32" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="L32" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="T32" s="1" t="s">
+        <v>240</v>
+      </c>
+      <c r="V32" s="1" t="s">
+        <v>241</v>
+      </c>
+      <c r="Y32" s="1" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="33" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="B33" s="1" t="s">
+        <v>242</v>
+      </c>
+      <c r="C33" s="1" t="s">
+        <v>243</v>
+      </c>
+      <c r="D33" s="1" t="s">
+        <v>243</v>
+      </c>
+      <c r="F33" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="G33" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="H33" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="I33" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="J33" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="K33" s="1" t="s">
+        <v>212</v>
+      </c>
+      <c r="L33" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="N33" s="1" t="s">
+        <v>246</v>
+      </c>
+      <c r="V33" s="1" t="s">
+        <v>247</v>
+      </c>
+      <c r="Y33" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="AB33" s="5" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="34" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="B34" s="1" t="s">
+        <v>248</v>
+      </c>
+      <c r="C34" s="1" t="s">
+        <v>249</v>
+      </c>
+      <c r="D34" s="1" t="s">
+        <v>249</v>
+      </c>
+      <c r="F34" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="G34" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="H34" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="J34" s="1" t="s">
+        <v>226</v>
+      </c>
+      <c r="K34" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="L34" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="N34" s="1" t="s">
+        <v>250</v>
+      </c>
+      <c r="T34" s="1" t="s">
+        <v>251</v>
+      </c>
+      <c r="Y34" s="1" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="35" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="B35" s="1" t="s">
+        <v>252</v>
+      </c>
+      <c r="C35" s="1" t="s">
+        <v>253</v>
+      </c>
+      <c r="D35" s="1" t="s">
+        <v>253</v>
+      </c>
+      <c r="F35" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="G35" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="H35" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="I35" s="1" t="s">
+        <v>254</v>
+      </c>
+      <c r="J35" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="K35" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="L35" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="N35" s="1" t="s">
+        <v>255</v>
+      </c>
+      <c r="O35" s="1" t="s">
+        <v>256</v>
+      </c>
+      <c r="T35" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="X35" s="1" t="s">
+        <v>258</v>
+      </c>
+      <c r="Y35" s="1" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="36" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="B36" s="1" t="s">
+        <v>259</v>
+      </c>
+      <c r="C36" s="1" t="s">
+        <v>260</v>
+      </c>
+      <c r="D36" s="1" t="s">
+        <v>260</v>
+      </c>
+      <c r="F36" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="G36" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="H36" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="I36" s="1" t="s">
+        <v>261</v>
+      </c>
+      <c r="J36" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="K36" s="1" t="s">
+        <v>262</v>
+      </c>
+      <c r="L36" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="T36" s="1" t="s">
+        <v>263</v>
+      </c>
+      <c r="X36" s="1" t="s">
+        <v>264</v>
+      </c>
+      <c r="Y36" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="Z36" s="2" t="s">
+        <v>266</v>
+      </c>
+      <c r="AA36" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="AB36" s="1" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="37" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="B37" s="1" t="s">
+        <v>267</v>
+      </c>
+      <c r="C37" s="1" t="s">
+        <v>268</v>
+      </c>
+      <c r="D37" s="1" t="s">
+        <v>268</v>
+      </c>
+      <c r="F37" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="G37" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="H37" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="J37" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="K37" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="L37" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="N37" s="1" t="s">
+        <v>269</v>
+      </c>
+      <c r="T37" s="1" t="s">
+        <v>270</v>
+      </c>
+      <c r="Y37" s="1" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="38" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="B38" s="5" t="s">
+        <v>271</v>
+      </c>
+      <c r="C38" s="1" t="s">
+        <v>272</v>
+      </c>
+      <c r="D38" s="1" t="s">
+        <v>272</v>
+      </c>
+      <c r="F38" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="G38" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="H38" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="J38" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="K38" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="L38" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="Y38" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="Z38" s="2" t="s">
+        <v>273</v>
+      </c>
+      <c r="AA38" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="AB38" s="1" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="39" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="B39" s="1" t="s">
+        <v>275</v>
+      </c>
+      <c r="C39" s="1" t="s">
+        <v>276</v>
+      </c>
+      <c r="D39" s="1" t="s">
+        <v>276</v>
+      </c>
+      <c r="F39" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="G39" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="H39" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="J39" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="K39" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="L39" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="T39" s="1" t="s">
+        <v>277</v>
+      </c>
+      <c r="Y39" s="1" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="40" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="B40" s="1" t="s">
+        <v>278</v>
+      </c>
+      <c r="C40" s="1" t="s">
+        <v>279</v>
+      </c>
+      <c r="D40" s="1" t="s">
+        <v>279</v>
+      </c>
+      <c r="F40" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="G40" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="H40" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="J40" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="K40" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="L40" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="R40" s="1" t="s">
+        <v>281</v>
+      </c>
+      <c r="T40" s="1" t="s">
+        <v>280</v>
+      </c>
+      <c r="Y40" s="1" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="41" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="B41" s="1" t="s">
+        <v>282</v>
+      </c>
+      <c r="C41" s="1" t="s">
+        <v>283</v>
+      </c>
+      <c r="D41" s="1" t="s">
+        <v>283</v>
+      </c>
+      <c r="F41" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="G41" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="H41" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="J41" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="K41" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="L41" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="N41" s="1" t="s">
+        <v>284</v>
+      </c>
+      <c r="O41" s="1" t="s">
+        <v>285</v>
+      </c>
+      <c r="R41" s="1" t="s">
+        <v>286</v>
+      </c>
+      <c r="T41" s="1" t="s">
+        <v>287</v>
+      </c>
+      <c r="X41" s="1" t="s">
+        <v>288</v>
+      </c>
+      <c r="Y41" s="1" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="42" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="B42" s="6" t="s">
+        <v>289</v>
+      </c>
+      <c r="C42" s="1" t="s">
+        <v>290</v>
+      </c>
+      <c r="D42" s="1" t="s">
+        <v>290</v>
+      </c>
+      <c r="F42" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="G42" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="H42" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="J42" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="K42" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="L42" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="N42" s="1" t="s">
+        <v>345</v>
+      </c>
+      <c r="T42" s="1" t="s">
+        <v>346</v>
+      </c>
+      <c r="X42" s="1" t="s">
+        <v>349</v>
+      </c>
+      <c r="Y42" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="Z42" s="2" t="s">
+        <v>347</v>
+      </c>
+      <c r="AA42" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="AB42" s="1" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="43" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="B43" s="1" t="s">
+        <v>291</v>
+      </c>
+      <c r="C43" s="1" t="s">
+        <v>276</v>
+      </c>
+      <c r="D43" s="1" t="s">
+        <v>276</v>
+      </c>
+      <c r="F43" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="G43" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="H43" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="J43" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="K43" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="L43" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="T43" s="1" t="s">
+        <v>292</v>
+      </c>
+      <c r="Y43" s="1" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="44" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="B44" s="1" t="s">
+        <v>293</v>
+      </c>
+      <c r="C44" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="D44" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="F44" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="G44" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="H44" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="I44" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="J44" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="K44" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="L44" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="N44" s="1" t="s">
+        <v>295</v>
+      </c>
+      <c r="T44" s="1" t="s">
+        <v>298</v>
+      </c>
+      <c r="V44" s="1" t="s">
+        <v>299</v>
+      </c>
+      <c r="X44" s="1" t="s">
+        <v>300</v>
+      </c>
+      <c r="Y44" s="1" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="45" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="B45" s="1" t="s">
+        <v>294</v>
+      </c>
+      <c r="C45" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="D45" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="F45" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="G45" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="H45" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="I45" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="J45" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="K45" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="L45" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="N45" s="1" t="s">
+        <v>296</v>
+      </c>
+      <c r="T45" s="1" t="s">
+        <v>301</v>
+      </c>
+      <c r="V45" s="1" t="s">
+        <v>297</v>
+      </c>
+      <c r="X45" s="1" t="s">
+        <v>302</v>
+      </c>
+      <c r="Y45" s="1" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="46" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="B46" s="1" t="s">
+        <v>303</v>
+      </c>
+      <c r="C46" s="1" t="s">
+        <v>181</v>
+      </c>
+      <c r="D46" s="1" t="s">
+        <v>181</v>
+      </c>
+      <c r="F46" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="G46" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="H46" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="I46" s="1" t="s">
+        <v>182</v>
+      </c>
+      <c r="J46" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="K46" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="L46" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="N46" s="1" t="s">
+        <v>305</v>
+      </c>
+      <c r="T46" s="1" t="s">
+        <v>307</v>
+      </c>
+      <c r="V46" s="1" t="s">
+        <v>309</v>
+      </c>
+      <c r="Y46" s="1" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="47" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="B47" s="1" t="s">
+        <v>304</v>
+      </c>
+      <c r="C47" s="1" t="s">
+        <v>181</v>
+      </c>
+      <c r="D47" s="1" t="s">
+        <v>181</v>
+      </c>
+      <c r="F47" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="G47" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="H47" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="I47" s="1" t="s">
+        <v>182</v>
+      </c>
+      <c r="J47" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="K47" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="L47" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="N47" s="1" t="s">
+        <v>306</v>
+      </c>
+      <c r="T47" s="1" t="s">
+        <v>308</v>
+      </c>
+      <c r="V47" s="1" t="s">
+        <v>310</v>
+      </c>
+      <c r="Y47" s="1" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="48" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="B48" s="5" t="s">
+        <v>311</v>
+      </c>
+      <c r="C48" s="1" t="s">
+        <v>272</v>
+      </c>
+      <c r="D48" s="1" t="s">
+        <v>272</v>
+      </c>
+      <c r="F48" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="G48" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="H48" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="J48" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="K48" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="L48" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="Y48" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="Z48" s="2" t="s">
+        <v>273</v>
+      </c>
+      <c r="AA48" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="AB48" s="1" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="49" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="B49" s="1" t="s">
+        <v>312</v>
+      </c>
+      <c r="C49" s="1" t="s">
+        <v>276</v>
+      </c>
+      <c r="D49" s="1" t="s">
+        <v>276</v>
+      </c>
+      <c r="F49" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="G49" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="H49" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="J49" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="K49" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="L49" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="T49" s="1" t="s">
+        <v>313</v>
+      </c>
+      <c r="Y49" s="1" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="50" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="B50" s="1" t="s">
+        <v>314</v>
+      </c>
+      <c r="C50" s="1" t="s">
+        <v>279</v>
+      </c>
+      <c r="D50" s="1" t="s">
+        <v>279</v>
+      </c>
+      <c r="F50" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="G50" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="H50" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="J50" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="K50" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="L50" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="R50" s="1" t="s">
+        <v>316</v>
+      </c>
+      <c r="T50" s="1" t="s">
+        <v>315</v>
+      </c>
+      <c r="Y50" s="1" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="51" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="B51" s="1" t="s">
+        <v>317</v>
+      </c>
+      <c r="C51" s="1" t="s">
+        <v>317</v>
+      </c>
+      <c r="D51" s="1" t="s">
+        <v>317</v>
+      </c>
+      <c r="F51" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="G51" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="H51" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="J51" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="K51" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="L51" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="T51" s="1" t="s">
+        <v>318</v>
+      </c>
+      <c r="Y51" s="1" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="52" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="B52" s="1" t="s">
+        <v>319</v>
+      </c>
+      <c r="C52" s="1" t="s">
+        <v>319</v>
+      </c>
+      <c r="D52" s="1" t="s">
+        <v>319</v>
+      </c>
+      <c r="F52" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="G52" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="H52" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="J52" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="K52" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="L52" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="T52" s="1" t="s">
+        <v>320</v>
+      </c>
+      <c r="Y52" s="1" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="53" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="B53" s="1" t="s">
+        <v>321</v>
+      </c>
+      <c r="C53" s="1" t="s">
+        <v>321</v>
+      </c>
+      <c r="D53" s="1" t="s">
+        <v>321</v>
+      </c>
+      <c r="F53" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="G53" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="H53" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="I53" s="1" t="s">
+        <v>328</v>
+      </c>
+      <c r="J53" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="K53" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="L53" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="N53" s="1" t="s">
+        <v>322</v>
+      </c>
+      <c r="O53" s="1" t="s">
+        <v>323</v>
+      </c>
+      <c r="R53" s="1" t="s">
+        <v>324</v>
+      </c>
+      <c r="V53" s="1" t="s">
+        <v>352</v>
+      </c>
+      <c r="X53" s="1" t="s">
+        <v>325</v>
+      </c>
+      <c r="Y53" s="1" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="54" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="B54" s="1" t="s">
+        <v>326</v>
+      </c>
+      <c r="C54" s="1" t="s">
+        <v>327</v>
+      </c>
+      <c r="D54" s="1" t="s">
+        <v>327</v>
+      </c>
+      <c r="F54" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="G54" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="H54" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="I54" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="J54" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="K54" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="L54" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="O54" s="1" t="s">
+        <v>329</v>
+      </c>
+      <c r="V54" s="1" t="s">
+        <v>330</v>
+      </c>
+      <c r="X54" s="1" t="s">
+        <v>331</v>
+      </c>
+      <c r="Y54" s="1" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="55" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="B55" s="1" t="s">
+        <v>332</v>
+      </c>
+      <c r="C55" s="1" t="s">
+        <v>333</v>
+      </c>
+      <c r="D55" s="1" t="s">
+        <v>333</v>
+      </c>
+      <c r="F55" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="G55" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="H55" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="I55" s="1" t="s">
+        <v>334</v>
+      </c>
+      <c r="J55" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="K55" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="L55" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="T55" s="1" t="s">
+        <v>335</v>
+      </c>
+      <c r="V55" s="1" t="s">
+        <v>336</v>
+      </c>
+      <c r="Y55" s="1" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="56" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="B56" s="1" t="s">
+        <v>337</v>
+      </c>
+      <c r="C56" s="1" t="s">
+        <v>338</v>
+      </c>
+      <c r="D56" s="1" t="s">
+        <v>338</v>
+      </c>
+      <c r="F56" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="G56" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="H56" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="I56" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="J56" s="1" t="s">
+        <v>226</v>
+      </c>
+      <c r="K56" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="L56" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="T56" s="1" t="s">
+        <v>339</v>
+      </c>
+      <c r="V56" s="1" t="s">
+        <v>340</v>
+      </c>
+      <c r="Y56" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="AB56" s="5" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="58" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="B58" s="1" t="s">
+        <v>353</v>
+      </c>
+      <c r="C58" s="1" t="s">
+        <v>354</v>
+      </c>
+      <c r="D58" s="1" t="s">
+        <v>354</v>
+      </c>
+      <c r="F58" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="G58" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="H58" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="I58" s="1" t="s">
+        <v>356</v>
+      </c>
+      <c r="J58" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="K58" s="1" t="s">
+        <v>212</v>
+      </c>
+      <c r="L58" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="V58" s="1" t="s">
+        <v>357</v>
+      </c>
+      <c r="Y58" s="1" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="59" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="B59" s="1" t="s">
+        <v>363</v>
+      </c>
+      <c r="C59" s="1" t="s">
+        <v>365</v>
+      </c>
+      <c r="D59" s="1" t="s">
+        <v>365</v>
+      </c>
+      <c r="F59" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="G59" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="H59" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="I59" s="1" t="s">
+        <v>367</v>
+      </c>
+      <c r="J59" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="K59" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="L59" s="1" t="s">
+        <v>370</v>
+      </c>
+      <c r="V59" s="1" t="s">
+        <v>358</v>
+      </c>
+      <c r="Y59" s="1" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="60" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="B60" s="1" t="s">
+        <v>364</v>
+      </c>
+      <c r="C60" s="1" t="s">
+        <v>366</v>
+      </c>
+      <c r="D60" s="1" t="s">
+        <v>366</v>
+      </c>
+      <c r="F60" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="G60" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="H60" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="I60" s="1" t="s">
+        <v>368</v>
+      </c>
+      <c r="J60" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="K60" s="1" t="s">
+        <v>369</v>
+      </c>
+      <c r="L60" s="1" t="s">
+        <v>371</v>
+      </c>
+      <c r="V60" s="1" t="s">
+        <v>359</v>
+      </c>
+      <c r="Y60" s="1" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="61" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="B61" s="1" t="s">
+        <v>372</v>
+      </c>
+      <c r="C61" s="1" t="s">
+        <v>375</v>
+      </c>
+      <c r="D61" s="1" t="s">
+        <v>375</v>
+      </c>
+      <c r="F61" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="G61" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="H61" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="I61" s="1" t="s">
+        <v>378</v>
+      </c>
+      <c r="J61" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="K61" s="1" t="s">
+        <v>381</v>
+      </c>
+      <c r="L61" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="N61" s="1" t="s">
+        <v>385</v>
+      </c>
+      <c r="V61" s="1" t="s">
+        <v>360</v>
+      </c>
+      <c r="Y61" s="1" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="62" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="B62" s="1" t="s">
+        <v>373</v>
+      </c>
+      <c r="C62" s="1" t="s">
+        <v>376</v>
+      </c>
+      <c r="D62" s="1" t="s">
+        <v>376</v>
+      </c>
+      <c r="F62" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="G62" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="H62" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="I62" s="1" t="s">
+        <v>379</v>
+      </c>
+      <c r="J62" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="K62" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="L62" s="1" t="s">
+        <v>383</v>
+      </c>
+      <c r="N62" s="1" t="s">
+        <v>386</v>
+      </c>
+      <c r="V62" s="1" t="s">
+        <v>361</v>
+      </c>
+      <c r="Y62" s="1" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="63" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="B63" s="1" t="s">
+        <v>374</v>
+      </c>
+      <c r="C63" s="1" t="s">
+        <v>377</v>
+      </c>
+      <c r="D63" s="1" t="s">
+        <v>377</v>
+      </c>
+      <c r="F63" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="G63" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="H63" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="I63" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="J63" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="K63" s="1" t="s">
+        <v>382</v>
+      </c>
+      <c r="L63" s="1" t="s">
+        <v>384</v>
+      </c>
+      <c r="N63" s="1" t="s">
+        <v>387</v>
+      </c>
+      <c r="V63" s="1" t="s">
+        <v>362</v>
+      </c>
+      <c r="Y63" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="Z63" s="3"/>
+      <c r="AA63" s="3"/>
+    </row>
+    <row r="64" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="B64" s="1" t="s">
+        <v>388</v>
+      </c>
+      <c r="C64" s="1" t="s">
+        <v>389</v>
+      </c>
+      <c r="D64" s="1" t="s">
+        <v>389</v>
+      </c>
+      <c r="F64" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="G64" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="H64" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="I64" s="1" t="s">
+        <v>390</v>
+      </c>
+      <c r="J64" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="K64" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="L64" s="1" t="s">
+        <v>391</v>
+      </c>
+      <c r="T64" s="1" t="s">
+        <v>392</v>
+      </c>
+      <c r="V64" s="1" t="s">
+        <v>393</v>
+      </c>
+      <c r="Y64" s="1" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="65" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="B65" s="1" t="s">
+        <v>394</v>
+      </c>
+      <c r="C65" s="1" t="s">
+        <v>395</v>
+      </c>
+      <c r="D65" s="1" t="s">
+        <v>395</v>
+      </c>
+      <c r="F65" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="G65" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="H65" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="I65" s="1" t="s">
+        <v>396</v>
+      </c>
+      <c r="J65" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="K65" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="L65" s="1" t="s">
+        <v>384</v>
+      </c>
+      <c r="N65" s="1" t="s">
+        <v>399</v>
+      </c>
+      <c r="R65" s="1" t="s">
+        <v>398</v>
+      </c>
+      <c r="V65" s="1" t="s">
+        <v>397</v>
+      </c>
+      <c r="Y65" s="1" t="s">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="66" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="B66" s="1" t="s">
+        <v>401</v>
+      </c>
+      <c r="C66" s="1" t="s">
+        <v>400</v>
+      </c>
+      <c r="D66" s="1" t="s">
+        <v>400</v>
+      </c>
+      <c r="F66" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="G66" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="H66" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="I66" s="1" t="s">
+        <v>402</v>
+      </c>
+      <c r="J66" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="K66" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="L66" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="N66" s="1" t="s">
+        <v>403</v>
+      </c>
+      <c r="V66" s="1" t="s">
+        <v>404</v>
+      </c>
+      <c r="Y66" s="1" t="s">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="67" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="B67" s="7" t="s">
+        <v>405</v>
+      </c>
+      <c r="C67" s="1" t="s">
+        <v>406</v>
+      </c>
+      <c r="D67" s="1" t="s">
+        <v>406</v>
+      </c>
+      <c r="F67" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="G67" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="H67" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="L67" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="Y67" s="1" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="68" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="B68" s="7" t="s">
+        <v>407</v>
+      </c>
+      <c r="C68" s="1" t="s">
+        <v>417</v>
+      </c>
+      <c r="D68" s="1" t="s">
+        <v>417</v>
+      </c>
+      <c r="F68" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="G68" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="H68" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="L68" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="Y68" s="1" t="s">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="69" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="B69" s="7" t="s">
+        <v>408</v>
+      </c>
+      <c r="C69" s="1" t="s">
+        <v>418</v>
+      </c>
+      <c r="D69" s="1" t="s">
+        <v>418</v>
+      </c>
+      <c r="F69" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="G69" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="H69" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="L69" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="Y69" s="1" t="s">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="70" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="B70" s="7" t="s">
+        <v>409</v>
+      </c>
+      <c r="C70" s="1" t="s">
+        <v>419</v>
+      </c>
+      <c r="D70" s="1" t="s">
+        <v>419</v>
+      </c>
+      <c r="F70" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="G70" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="H70" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="I70" s="1" t="s">
+        <v>427</v>
+      </c>
+      <c r="J70" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="K70" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="L70" s="1" t="s">
+        <v>370</v>
+      </c>
+      <c r="Y70" s="1" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="71" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="B71" s="7" t="s">
+        <v>410</v>
+      </c>
+      <c r="C71" s="1" t="s">
+        <v>420</v>
+      </c>
+      <c r="D71" s="1" t="s">
+        <v>420</v>
+      </c>
+      <c r="F71" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="G71" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="H71" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="I71" s="1" t="s">
+        <v>428</v>
+      </c>
+      <c r="J71" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="K71" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="L71" s="1" t="s">
+        <v>370</v>
+      </c>
+      <c r="Y71" s="1" t="s">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="72" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="B72" s="7" t="s">
+        <v>411</v>
+      </c>
+      <c r="C72" s="1" t="s">
+        <v>421</v>
+      </c>
+      <c r="D72" s="1" t="s">
+        <v>421</v>
+      </c>
+      <c r="F72" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="G72" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="H72" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="I72" s="1" t="s">
+        <v>429</v>
+      </c>
+      <c r="J72" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="K72" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="L72" s="1" t="s">
+        <v>370</v>
+      </c>
+      <c r="Y72" s="1" t="s">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="73" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="B73" s="7" t="s">
+        <v>412</v>
+      </c>
+      <c r="C73" s="1" t="s">
+        <v>422</v>
+      </c>
+      <c r="D73" s="1" t="s">
+        <v>422</v>
+      </c>
+      <c r="F73" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="G73" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="H73" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="I73" s="1" t="s">
+        <v>430</v>
+      </c>
+      <c r="J73" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="K73" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="L73" s="1" t="s">
+        <v>370</v>
+      </c>
+      <c r="Y73" s="1" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="74" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="B74" s="7" t="s">
+        <v>413</v>
+      </c>
+      <c r="C74" s="1" t="s">
+        <v>423</v>
+      </c>
+      <c r="D74" s="1" t="s">
+        <v>423</v>
+      </c>
+      <c r="F74" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="G74" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="H74" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="I74" s="1" t="s">
+        <v>431</v>
+      </c>
+      <c r="J74" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="K74" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="L74" s="1" t="s">
+        <v>370</v>
+      </c>
+      <c r="Y74" s="1" t="s">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="75" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="B75" s="7" t="s">
+        <v>414</v>
+      </c>
+      <c r="C75" s="1" t="s">
+        <v>424</v>
+      </c>
+      <c r="D75" s="1" t="s">
+        <v>424</v>
+      </c>
+      <c r="F75" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="G75" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="H75" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="I75" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="J75" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="K75" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="L75" s="1" t="s">
+        <v>370</v>
+      </c>
+      <c r="Y75" s="1" t="s">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="76" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="B76" s="7" t="s">
+        <v>415</v>
+      </c>
+      <c r="C76" s="1" t="s">
+        <v>425</v>
+      </c>
+      <c r="D76" s="1" t="s">
+        <v>425</v>
+      </c>
+      <c r="F76" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="G76" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="H76" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="I76" s="1" t="s">
+        <v>432</v>
+      </c>
+      <c r="J76" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="K76" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="L76" s="1" t="s">
+        <v>370</v>
+      </c>
+      <c r="Y76" s="1" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="77" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="B77" s="7" t="s">
+        <v>416</v>
+      </c>
+      <c r="C77" s="1" t="s">
+        <v>426</v>
+      </c>
+      <c r="D77" s="1" t="s">
+        <v>426</v>
+      </c>
+      <c r="F77" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="G77" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="H77" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="I77" s="1" t="s">
+        <v>433</v>
+      </c>
+      <c r="J77" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="K77" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="L77" s="1" t="s">
+        <v>370</v>
+      </c>
+      <c r="Y77" s="1" t="s">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="78" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="B78" s="1" t="s">
+        <v>434</v>
+      </c>
+      <c r="C78" s="1" t="s">
+        <v>435</v>
+      </c>
+      <c r="D78" s="1" t="s">
+        <v>435</v>
+      </c>
+      <c r="F78" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="G78" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="H78" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="I78" s="1" t="s">
+        <v>436</v>
+      </c>
+      <c r="J78" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="K78" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="L78" s="1" t="s">
+        <v>445</v>
+      </c>
+      <c r="N78" s="1" t="s">
+        <v>437</v>
+      </c>
+      <c r="T78" s="1" t="s">
+        <v>438</v>
+      </c>
+      <c r="Y78" s="1" t="s">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="79" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="B79" s="1" t="s">
+        <v>439</v>
+      </c>
+      <c r="C79" s="1" t="s">
+        <v>440</v>
+      </c>
+      <c r="D79" s="1" t="s">
+        <v>440</v>
+      </c>
+      <c r="F79" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="G79" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="H79" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="L79" s="1" t="s">
+        <v>446</v>
+      </c>
+      <c r="T79" s="1" t="s">
+        <v>441</v>
+      </c>
+      <c r="Y79" s="1" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="80" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="B80" s="1" t="s">
+        <v>442</v>
+      </c>
+      <c r="C80" s="1" t="s">
+        <v>443</v>
+      </c>
+      <c r="D80" s="1" t="s">
+        <v>443</v>
+      </c>
+      <c r="F80" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="G80" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="H80" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="L80" s="1" t="s">
+        <v>444</v>
+      </c>
+      <c r="Y80" s="1" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="81" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="B81" s="1" t="s">
+        <v>447</v>
+      </c>
+      <c r="C81" s="1" t="s">
+        <v>448</v>
+      </c>
+      <c r="D81" s="1" t="s">
+        <v>448</v>
+      </c>
+      <c r="F81" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="G81" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="H81" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="I81" s="1" t="s">
+        <v>449</v>
+      </c>
+      <c r="J81" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="K81" s="1" t="s">
+        <v>450</v>
+      </c>
+      <c r="L81" s="1" t="s">
+        <v>384</v>
+      </c>
+      <c r="R81" s="1" t="s">
+        <v>451</v>
+      </c>
+      <c r="T81" s="1" t="s">
+        <v>452</v>
+      </c>
+      <c r="X81" s="1" t="s">
+        <v>453</v>
+      </c>
+      <c r="Y81" s="1" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="82" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="B82" s="1" t="s">
+        <v>454</v>
+      </c>
+      <c r="C82" s="1" t="s">
+        <v>448</v>
+      </c>
+      <c r="D82" s="1" t="s">
+        <v>448</v>
+      </c>
+      <c r="F82" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="G82" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="H82" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="I82" s="1" t="s">
+        <v>449</v>
+      </c>
+      <c r="J82" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="K82" s="1" t="s">
+        <v>450</v>
+      </c>
+      <c r="L82" s="1" t="s">
+        <v>445</v>
+      </c>
+      <c r="N82" s="1" t="s">
+        <v>455</v>
+      </c>
+      <c r="T82" s="1" t="s">
+        <v>456</v>
+      </c>
+      <c r="X82" s="1" t="s">
+        <v>457</v>
+      </c>
+      <c r="Y82" s="1" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="83" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="B83" s="1" t="s">
+        <v>458</v>
+      </c>
+      <c r="C83" s="1" t="s">
+        <v>459</v>
+      </c>
+      <c r="D83" s="1" t="s">
+        <v>459</v>
+      </c>
+      <c r="F83" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="G83" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="H83" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="I83" s="1" t="s">
+        <v>460</v>
+      </c>
+      <c r="J83" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="K83" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="L83" s="1" t="s">
+        <v>383</v>
+      </c>
+      <c r="R83" s="1" t="s">
+        <v>461</v>
+      </c>
+      <c r="T83" s="1" t="s">
+        <v>462</v>
+      </c>
+      <c r="X83" s="1" t="s">
+        <v>463</v>
+      </c>
+      <c r="Y83" s="1" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="84" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="B84" s="1" t="s">
+        <v>464</v>
+      </c>
+      <c r="C84" s="1" t="s">
+        <v>465</v>
+      </c>
+      <c r="D84" s="1" t="s">
+        <v>465</v>
+      </c>
+      <c r="F84" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="G84" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="H84" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="I84" s="1" t="s">
+        <v>466</v>
+      </c>
+      <c r="J84" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="K84" s="1" t="s">
+        <v>467</v>
+      </c>
+      <c r="L84" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="N84" s="1" t="s">
+        <v>468</v>
+      </c>
+      <c r="T84" s="1" t="s">
+        <v>469</v>
+      </c>
+      <c r="V84" s="1" t="s">
+        <v>470</v>
+      </c>
+      <c r="Y84" s="1" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="85" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="B85" s="7" t="s">
+        <v>471</v>
+      </c>
+      <c r="C85" s="1" t="s">
+        <v>472</v>
+      </c>
+      <c r="D85" s="1" t="s">
+        <v>472</v>
+      </c>
+      <c r="F85" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="G85" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="H85" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="I85" s="1" t="s">
+        <v>473</v>
+      </c>
+      <c r="J85" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="K85" s="1" t="s">
+        <v>484</v>
+      </c>
+      <c r="L85" s="1" t="s">
+        <v>384</v>
+      </c>
+      <c r="N85" s="1" t="s">
+        <v>474</v>
+      </c>
+      <c r="Y85" s="1" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="86" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="B86" s="1" t="s">
+        <v>475</v>
+      </c>
+      <c r="C86" s="1" t="s">
+        <v>465</v>
+      </c>
+      <c r="D86" s="1" t="s">
+        <v>465</v>
+      </c>
+      <c r="F86" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="G86" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="H86" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="I86" s="1" t="s">
+        <v>466</v>
+      </c>
+      <c r="J86" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="K86" s="1" t="s">
+        <v>467</v>
+      </c>
+      <c r="L86" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="N86" s="1" t="s">
+        <v>476</v>
+      </c>
+      <c r="T86" s="1" t="s">
+        <v>477</v>
+      </c>
+      <c r="V86" s="1" t="s">
+        <v>478</v>
+      </c>
+      <c r="Y86" s="1" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="87" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="B87" s="7" t="s">
+        <v>479</v>
+      </c>
+      <c r="C87" s="1" t="s">
+        <v>472</v>
+      </c>
+      <c r="D87" s="1" t="s">
+        <v>472</v>
+      </c>
+      <c r="F87" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="G87" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="H87" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="I87" s="1" t="s">
+        <v>473</v>
+      </c>
+      <c r="J87" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="K87" s="1" t="s">
+        <v>484</v>
+      </c>
+      <c r="L87" s="1" t="s">
+        <v>445</v>
+      </c>
+      <c r="N87" s="1" t="s">
+        <v>480</v>
+      </c>
+      <c r="Y87" s="1" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="88" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="B88" s="1" t="s">
+        <v>481</v>
+      </c>
+      <c r="C88" s="1" t="s">
+        <v>482</v>
+      </c>
+      <c r="D88" s="1" t="s">
+        <v>482</v>
+      </c>
+      <c r="F88" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="G88" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="H88" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="I88" s="1" t="s">
+        <v>483</v>
+      </c>
+      <c r="J88" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="K88" s="1" t="s">
+        <v>262</v>
+      </c>
+      <c r="L88" s="1" t="s">
+        <v>485</v>
+      </c>
+      <c r="T88" s="1" t="s">
+        <v>486</v>
+      </c>
+      <c r="Y88" s="1" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="89" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="B89" s="7" t="s">
+        <v>487</v>
+      </c>
+      <c r="C89" s="1" t="s">
+        <v>490</v>
+      </c>
+      <c r="D89" s="1" t="s">
+        <v>490</v>
+      </c>
+      <c r="F89" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="G89" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="H89" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="Y89" s="1" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="90" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="B90" s="7" t="s">
+        <v>488</v>
+      </c>
+      <c r="C90" s="1" t="s">
+        <v>491</v>
+      </c>
+      <c r="D90" s="1" t="s">
+        <v>491</v>
+      </c>
+      <c r="F90" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="G90" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="H90" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="Y90" s="1" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="91" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="B91" s="7" t="s">
+        <v>489</v>
+      </c>
+      <c r="C91" s="1" t="s">
+        <v>492</v>
+      </c>
+      <c r="D91" s="1" t="s">
+        <v>492</v>
+      </c>
+      <c r="F91" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="G91" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="H91" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="Y91" s="1" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="92" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="B92" s="1" t="s">
+        <v>493</v>
+      </c>
+      <c r="C92" s="1" t="s">
+        <v>494</v>
+      </c>
+      <c r="D92" s="1" t="s">
+        <v>494</v>
+      </c>
+      <c r="F92" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="G92" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="H92" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="J92" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="K92" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="L92" s="1" t="s">
+        <v>485</v>
+      </c>
+      <c r="T92" s="1" t="s">
+        <v>495</v>
+      </c>
+      <c r="V92" s="1" t="s">
+        <v>496</v>
+      </c>
+      <c r="Y92" s="1" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="93" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="B93" s="1" t="s">
+        <v>497</v>
+      </c>
+      <c r="C93" s="1" t="s">
+        <v>498</v>
+      </c>
+      <c r="D93" s="1" t="s">
+        <v>498</v>
+      </c>
+      <c r="F93" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="G93" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="H93" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="J93" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="K93" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="L93" s="1" t="s">
+        <v>499</v>
+      </c>
+      <c r="N93" s="1" t="s">
+        <v>500</v>
+      </c>
+      <c r="T93" s="1" t="s">
+        <v>501</v>
+      </c>
+      <c r="V93" s="1" t="s">
+        <v>502</v>
+      </c>
+      <c r="Y93" s="1" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="94" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="B94" s="1" t="s">
+        <v>503</v>
+      </c>
+      <c r="C94" s="1" t="s">
+        <v>504</v>
+      </c>
+      <c r="D94" s="1" t="s">
+        <v>504</v>
+      </c>
+      <c r="F94" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="G94" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="H94" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="J94" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="K94" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="L94" s="1" t="s">
+        <v>384</v>
+      </c>
+      <c r="T94" s="1" t="s">
+        <v>505</v>
+      </c>
+      <c r="Y94" s="1" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="95" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="B95" s="7" t="s">
+        <v>506</v>
+      </c>
+      <c r="C95" s="1" t="s">
+        <v>507</v>
+      </c>
+      <c r="D95" s="1" t="s">
+        <v>507</v>
+      </c>
+      <c r="F95" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="G95" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="H95" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="Y95" s="1" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="96" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="B96" s="1" t="s">
+        <v>508</v>
+      </c>
+      <c r="C96" s="1" t="s">
+        <v>509</v>
+      </c>
+      <c r="D96" s="1" t="s">
+        <v>509</v>
+      </c>
+      <c r="F96" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="G96" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="H96" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="I96" s="1" t="s">
+        <v>510</v>
+      </c>
+      <c r="J96" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="K96" s="1" t="s">
+        <v>467</v>
+      </c>
+      <c r="L96" s="1" t="s">
+        <v>511</v>
+      </c>
+      <c r="N96" s="1" t="s">
+        <v>512</v>
+      </c>
+      <c r="P96" s="1" t="s">
+        <v>513</v>
+      </c>
+      <c r="T96" s="1" t="s">
+        <v>515</v>
+      </c>
+      <c r="V96" s="1" t="s">
+        <v>514</v>
+      </c>
+      <c r="Y96" s="1" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="97" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="B97" s="1" t="s">
+        <v>516</v>
+      </c>
+      <c r="C97" s="1" t="s">
+        <v>517</v>
+      </c>
+      <c r="D97" s="1" t="s">
+        <v>517</v>
+      </c>
+      <c r="F97" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="G97" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="H97" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="J97" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="K97" s="1" t="s">
+        <v>518</v>
+      </c>
+      <c r="L97" s="1" t="s">
+        <v>519</v>
+      </c>
+      <c r="V97" s="1" t="s">
+        <v>520</v>
+      </c>
+      <c r="Y97" s="1" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="98" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="B98" s="1" t="s">
+        <v>521</v>
+      </c>
+      <c r="C98" s="1" t="s">
+        <v>522</v>
+      </c>
+      <c r="D98" s="1" t="s">
+        <v>522</v>
+      </c>
+      <c r="F98" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="G98" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="H98" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="J98" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="K98" s="1" t="s">
+        <v>518</v>
+      </c>
+      <c r="L98" s="1" t="s">
+        <v>445</v>
+      </c>
+      <c r="N98" s="1" t="s">
+        <v>523</v>
+      </c>
+      <c r="T98" s="1" t="s">
+        <v>524</v>
+      </c>
+      <c r="V98" s="1" t="s">
+        <v>525</v>
+      </c>
+      <c r="Y98" s="1" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="99" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="B99" s="1" t="s">
+        <v>526</v>
+      </c>
+      <c r="C99" s="1" t="s">
+        <v>527</v>
+      </c>
+      <c r="D99" s="1" t="s">
+        <v>527</v>
+      </c>
+      <c r="F99" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="G99" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="H99" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="J99" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="K99" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="L99" s="1" t="s">
+        <v>384</v>
+      </c>
+      <c r="T99" s="1" t="s">
+        <v>528</v>
+      </c>
+      <c r="V99" s="1" t="s">
+        <v>529</v>
+      </c>
+      <c r="Y99" s="1" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="100" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="B100" s="1" t="s">
+        <v>530</v>
+      </c>
+      <c r="C100" s="1" t="s">
+        <v>531</v>
+      </c>
+      <c r="D100" s="1" t="s">
+        <v>531</v>
+      </c>
+      <c r="F100" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="G100" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="H100" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="J100" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="K100" s="1" t="s">
+        <v>210</v>
+      </c>
+      <c r="L100" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="N100" s="1" t="s">
+        <v>532</v>
+      </c>
+      <c r="R100" s="1" t="s">
+        <v>533</v>
+      </c>
+      <c r="T100" s="1" t="s">
+        <v>534</v>
+      </c>
+      <c r="V100" s="1" t="s">
+        <v>535</v>
+      </c>
+      <c r="Y100" s="1" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="101" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="B101" s="1" t="s">
+        <v>536</v>
+      </c>
+      <c r="C101" s="1" t="s">
+        <v>537</v>
+      </c>
+      <c r="D101" s="1" t="s">
+        <v>537</v>
+      </c>
+      <c r="F101" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="G101" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="H101" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="I101" s="1" t="s">
+        <v>538</v>
+      </c>
+      <c r="J101" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="K101" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="L101" s="1" t="s">
+        <v>384</v>
+      </c>
+      <c r="T101" s="1" t="s">
+        <v>539</v>
+      </c>
+      <c r="Y101" s="1" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="102" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="B102" s="1" t="s">
+        <v>540</v>
+      </c>
+      <c r="C102" s="1" t="s">
+        <v>541</v>
+      </c>
+      <c r="D102" s="1" t="s">
+        <v>541</v>
+      </c>
+      <c r="F102" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="G102" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="H102" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="I102" s="1" t="s">
+        <v>542</v>
+      </c>
+      <c r="J102" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="K102" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="L102" s="1" t="s">
+        <v>383</v>
+      </c>
+      <c r="R102" s="1" t="s">
+        <v>543</v>
+      </c>
+      <c r="V102" s="1" t="s">
+        <v>544</v>
+      </c>
+      <c r="Y102" s="1" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="103" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="B103" s="1" t="s">
+        <v>545</v>
+      </c>
+      <c r="C103" s="1" t="s">
+        <v>546</v>
+      </c>
+      <c r="D103" s="1" t="s">
+        <v>546</v>
+      </c>
+      <c r="F103" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="G103" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="H103" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="I103" s="1" t="s">
+        <v>547</v>
+      </c>
+      <c r="J103" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="K103" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="L103" s="1" t="s">
+        <v>548</v>
+      </c>
+      <c r="N103" s="1" t="s">
+        <v>549</v>
+      </c>
+      <c r="R103" s="1" t="s">
+        <v>550</v>
+      </c>
+      <c r="Y103" s="1" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="104" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="B104" s="1" t="s">
+        <v>551</v>
+      </c>
+      <c r="C104" s="1" t="s">
+        <v>554</v>
+      </c>
+      <c r="D104" s="1" t="s">
+        <v>552</v>
+      </c>
+      <c r="F104" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="G104" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="H104" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="I104" s="1" t="s">
+        <v>427</v>
+      </c>
+      <c r="J104" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="K104" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="L104" s="1" t="s">
+        <v>383</v>
+      </c>
+      <c r="T104" s="1" t="s">
+        <v>553</v>
+      </c>
+      <c r="Y104" s="1" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="105" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="B105" s="1" t="s">
+        <v>555</v>
+      </c>
+      <c r="C105" s="1" t="s">
+        <v>555</v>
+      </c>
+      <c r="D105" s="1" t="s">
+        <v>555</v>
+      </c>
+      <c r="F105" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="G105" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="H105" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="I105" s="1" t="s">
+        <v>556</v>
+      </c>
+      <c r="J105" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="K105" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="L105" s="1" t="s">
+        <v>370</v>
+      </c>
+      <c r="N105" s="1" t="s">
+        <v>557</v>
+      </c>
+      <c r="V105" s="1" t="s">
+        <v>558</v>
+      </c>
+      <c r="Y105" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="Z105" s="3"/>
+      <c r="AA105" s="3"/>
+    </row>
+    <row r="106" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="B106" s="1" t="s">
+        <v>559</v>
+      </c>
+      <c r="C106" s="1" t="s">
+        <v>560</v>
+      </c>
+      <c r="D106" s="1" t="s">
+        <v>560</v>
+      </c>
+      <c r="F106" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="G106" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="H106" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="I106" s="1" t="s">
+        <v>460</v>
+      </c>
+      <c r="J106" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="K106" s="1" t="s">
+        <v>561</v>
+      </c>
+      <c r="L106" s="1" t="s">
+        <v>371</v>
+      </c>
+      <c r="R106" s="1" t="s">
+        <v>562</v>
+      </c>
+      <c r="Y106" s="1" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="107" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="B107" s="1" t="s">
+        <v>563</v>
+      </c>
+      <c r="C107" s="1" t="s">
+        <v>564</v>
+      </c>
+      <c r="D107" s="1" t="s">
+        <v>564</v>
+      </c>
+      <c r="F107" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="G107" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="H107" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="I107" s="1" t="s">
+        <v>565</v>
+      </c>
+      <c r="J107" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="K107" s="1" t="s">
+        <v>210</v>
+      </c>
+      <c r="L107" s="1" t="s">
+        <v>384</v>
+      </c>
+      <c r="N107" s="1" t="s">
+        <v>566</v>
+      </c>
+      <c r="T107" s="1" t="s">
+        <v>567</v>
+      </c>
+      <c r="Y107" s="1" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="108" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="B108" s="1" t="s">
+        <v>568</v>
+      </c>
+      <c r="C108" s="1" t="s">
+        <v>569</v>
+      </c>
+      <c r="D108" s="1" t="s">
+        <v>569</v>
+      </c>
+      <c r="F108" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="G108" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="H108" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="I108" s="1" t="s">
+        <v>570</v>
+      </c>
+      <c r="J108" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="K108" s="1" t="s">
+        <v>518</v>
+      </c>
+      <c r="L108" s="1" t="s">
+        <v>371</v>
+      </c>
+      <c r="N108" s="1" t="s">
+        <v>571</v>
+      </c>
+      <c r="T108" s="1" t="s">
+        <v>572</v>
+      </c>
+      <c r="Y108" s="1" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="109" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="B109" s="1" t="s">
+        <v>573</v>
+      </c>
+      <c r="C109" s="1" t="s">
+        <v>574</v>
+      </c>
+      <c r="D109" s="1" t="s">
+        <v>574</v>
+      </c>
+      <c r="F109" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="G109" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="H109" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="I109" s="1" t="s">
+        <v>575</v>
+      </c>
+      <c r="J109" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="K109" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="L109" s="1" t="s">
+        <v>519</v>
+      </c>
+      <c r="T109" s="1" t="s">
+        <v>576</v>
+      </c>
+      <c r="Y109" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="Z109" s="2" t="s">
+        <v>273</v>
+      </c>
+      <c r="AA109" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="AB109" s="1" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="110" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="B110" s="1" t="s">
+        <v>577</v>
+      </c>
+      <c r="C110" s="1" t="s">
+        <v>578</v>
+      </c>
+      <c r="D110" s="1" t="s">
+        <v>578</v>
+      </c>
+      <c r="F110" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="G110" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="H110" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="I110" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="J110" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="K110" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="L110" s="1" t="s">
+        <v>371</v>
+      </c>
+      <c r="V110" s="1" t="s">
+        <v>580</v>
+      </c>
+      <c r="Y110" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="AB110" s="7" t="s">
+        <v>579</v>
+      </c>
+    </row>
+    <row r="111" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="B111" s="1" t="s">
+        <v>581</v>
+      </c>
+      <c r="C111" s="1" t="s">
+        <v>582</v>
+      </c>
+      <c r="D111" s="1" t="s">
+        <v>582</v>
+      </c>
+      <c r="F111" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="G111" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="H111" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="I111" s="1" t="s">
+        <v>356</v>
+      </c>
+      <c r="J111" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="K111" s="1" t="s">
+        <v>518</v>
+      </c>
+      <c r="L111" s="1" t="s">
+        <v>384</v>
+      </c>
+      <c r="T111" s="1" t="s">
+        <v>583</v>
+      </c>
+      <c r="V111" s="1" t="s">
+        <v>584</v>
+      </c>
+      <c r="Y111" s="1" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="174" spans="26:27" x14ac:dyDescent="0.2">
+      <c r="Z174" s="3"/>
+      <c r="AA174" s="3"/>
+    </row>
+    <row r="179" spans="26:27" x14ac:dyDescent="0.2">
+      <c r="Z179" s="3"/>
+      <c r="AA179" s="3"/>
+    </row>
+    <row r="184" spans="26:27" x14ac:dyDescent="0.2">
+      <c r="Z184" s="3"/>
+      <c r="AA184" s="3"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>

--- a/Luban/Config/Datas/#BattleSkillConfig.xlsx
+++ b/Luban/Config/Datas/#BattleSkillConfig.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Project\Return0\Luban\Config\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{53F79851-930B-4261-8874-D7BA3A988C6C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{31D71918-7A80-40EB-BDDF-7D3467866354}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{53B3FBB6-B116-408D-BCC0-737AAAC6C9D0}"/>
   </bookViews>

--- a/Luban/Config/Datas/#BattleSkillConfig.xlsx
+++ b/Luban/Config/Datas/#BattleSkillConfig.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Project\Return0\Luban\Config\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A52B2A8A-C252-4DA2-AEAA-AEE51D3773D4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4CC5FE26-C88B-4C30-92FE-10EDAF8FFEC3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="38280" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{53B3FBB6-B116-408D-BCC0-737AAAC6C9D0}"/>
   </bookViews>

--- a/Luban/Config/Datas/#BattleSkillConfig.xlsx
+++ b/Luban/Config/Datas/#BattleSkillConfig.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Project\Return0\Luban\Config\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4CC5FE26-C88B-4C30-92FE-10EDAF8FFEC3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CE410167-9835-4BD1-9C96-1FA012668196}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="38280" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{53B3FBB6-B116-408D-BCC0-737AAAC6C9D0}"/>
   </bookViews>
@@ -74,7 +74,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4534" uniqueCount="970">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4207" uniqueCount="970">
   <si>
     <t>##var</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -4394,8 +4394,8 @@
       <c r="S4" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="AE4" s="1" t="s">
-        <v>36</v>
+      <c r="AE4" s="1">
+        <v>0</v>
       </c>
       <c r="AF4" s="1" t="s">
         <v>31</v>
@@ -4438,8 +4438,8 @@
       <c r="S5" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="AE5" s="1" t="s">
-        <v>36</v>
+      <c r="AE5" s="1">
+        <v>0</v>
       </c>
       <c r="AF5" s="1" t="s">
         <v>31</v>
@@ -4485,8 +4485,8 @@
       <c r="S6" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="AE6" s="1" t="s">
-        <v>36</v>
+      <c r="AE6" s="1">
+        <v>0</v>
       </c>
       <c r="AF6" s="1" t="s">
         <v>31</v>
@@ -4529,8 +4529,8 @@
       <c r="S7" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="AE7" s="1" t="s">
-        <v>36</v>
+      <c r="AE7" s="1">
+        <v>0</v>
       </c>
       <c r="AF7" s="1" t="s">
         <v>31</v>
@@ -4576,8 +4576,8 @@
       <c r="S8" s="1" t="s">
         <v>117</v>
       </c>
-      <c r="AE8" s="1" t="s">
-        <v>36</v>
+      <c r="AE8" s="1">
+        <v>0</v>
       </c>
       <c r="AF8" s="1" t="s">
         <v>31</v>
@@ -4620,8 +4620,8 @@
       <c r="S9" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="AE9" s="1" t="s">
-        <v>36</v>
+      <c r="AE9" s="1">
+        <v>0</v>
       </c>
       <c r="AF9" s="1" t="s">
         <v>31</v>
@@ -4664,8 +4664,8 @@
       <c r="S10" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="AE10" s="1" t="s">
-        <v>36</v>
+      <c r="AE10" s="1">
+        <v>0</v>
       </c>
       <c r="AF10" s="1" t="s">
         <v>31</v>
@@ -4708,8 +4708,8 @@
       <c r="S11" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="AE11" s="1" t="s">
-        <v>36</v>
+      <c r="AE11" s="1">
+        <v>0</v>
       </c>
       <c r="AF11" s="1" t="s">
         <v>31</v>
@@ -4752,8 +4752,8 @@
       <c r="S12" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="AE12" s="1" t="s">
-        <v>36</v>
+      <c r="AE12" s="1">
+        <v>0</v>
       </c>
       <c r="AF12" s="1" t="s">
         <v>31</v>
@@ -4805,8 +4805,8 @@
       <c r="S13" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="AE13" s="1" t="s">
-        <v>36</v>
+      <c r="AE13" s="1">
+        <v>0</v>
       </c>
       <c r="AF13" s="1" t="s">
         <v>31</v>
@@ -4858,8 +4858,8 @@
       <c r="S14" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="AE14" s="1" t="s">
-        <v>36</v>
+      <c r="AE14" s="1">
+        <v>0</v>
       </c>
       <c r="AF14" s="1" t="s">
         <v>31</v>
@@ -4902,8 +4902,8 @@
       <c r="S15" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="AE15" s="1" t="s">
-        <v>36</v>
+      <c r="AE15" s="1">
+        <v>0</v>
       </c>
       <c r="AF15" s="1" t="s">
         <v>31</v>
@@ -4946,8 +4946,8 @@
       <c r="S16" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="AE16" s="1" t="s">
-        <v>36</v>
+      <c r="AE16" s="1">
+        <v>0</v>
       </c>
       <c r="AF16" s="1" t="s">
         <v>31</v>
@@ -4990,8 +4990,8 @@
       <c r="S17" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="AE17" s="1" t="s">
-        <v>36</v>
+      <c r="AE17" s="1">
+        <v>0</v>
       </c>
       <c r="AF17" s="1" t="s">
         <v>31</v>
@@ -5034,8 +5034,8 @@
       <c r="S18" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="AE18" s="1" t="s">
-        <v>36</v>
+      <c r="AE18" s="1">
+        <v>0</v>
       </c>
       <c r="AF18" s="1" t="s">
         <v>31</v>
@@ -5078,8 +5078,8 @@
       <c r="S19" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="AE19" s="1" t="s">
-        <v>36</v>
+      <c r="AE19" s="1">
+        <v>0</v>
       </c>
       <c r="AF19" s="1" t="s">
         <v>31</v>
@@ -5122,8 +5122,8 @@
       <c r="S20" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="AE20" s="1" t="s">
-        <v>36</v>
+      <c r="AE20" s="1">
+        <v>0</v>
       </c>
       <c r="AF20" s="1" t="s">
         <v>31</v>
@@ -5166,8 +5166,8 @@
       <c r="S21" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="AE21" s="1" t="s">
-        <v>36</v>
+      <c r="AE21" s="1">
+        <v>0</v>
       </c>
       <c r="AF21" s="1" t="s">
         <v>31</v>
@@ -5210,8 +5210,8 @@
       <c r="S22" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="AE22" s="1" t="s">
-        <v>36</v>
+      <c r="AE22" s="1">
+        <v>0</v>
       </c>
       <c r="AF22" s="1" t="s">
         <v>31</v>
@@ -5254,8 +5254,8 @@
       <c r="S23" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="AE23" s="1" t="s">
-        <v>36</v>
+      <c r="AE23" s="1">
+        <v>0</v>
       </c>
       <c r="AF23" s="1" t="s">
         <v>31</v>
@@ -5298,8 +5298,8 @@
       <c r="S24" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="AE24" s="1" t="s">
-        <v>36</v>
+      <c r="AE24" s="1">
+        <v>0</v>
       </c>
       <c r="AF24" s="1" t="s">
         <v>31</v>
@@ -5342,8 +5342,8 @@
       <c r="S25" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="AE25" s="1" t="s">
-        <v>36</v>
+      <c r="AE25" s="1">
+        <v>0</v>
       </c>
       <c r="AF25" s="1" t="s">
         <v>31</v>
@@ -5389,8 +5389,8 @@
       <c r="S26" s="1" t="s">
         <v>118</v>
       </c>
-      <c r="AE26" s="1" t="s">
-        <v>36</v>
+      <c r="AE26" s="1">
+        <v>0</v>
       </c>
       <c r="AF26" s="1" t="s">
         <v>31</v>
@@ -5435,8 +5435,8 @@
       </c>
       <c r="T27" s="4"/>
       <c r="U27" s="4"/>
-      <c r="AE27" s="1" t="s">
-        <v>36</v>
+      <c r="AE27" s="1">
+        <v>0</v>
       </c>
       <c r="AF27" s="1" t="s">
         <v>31</v>
@@ -5476,8 +5476,8 @@
       <c r="S28" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="AE28" s="1" t="s">
-        <v>36</v>
+      <c r="AE28" s="1">
+        <v>0</v>
       </c>
       <c r="AF28" s="1" t="s">
         <v>31</v>
@@ -5520,8 +5520,8 @@
       <c r="S29" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="AE29" s="1" t="s">
-        <v>36</v>
+      <c r="AE29" s="1">
+        <v>0</v>
       </c>
       <c r="AF29" s="1" t="s">
         <v>31</v>
@@ -5564,8 +5564,8 @@
       <c r="S30" s="1" t="s">
         <v>117</v>
       </c>
-      <c r="AE30" s="1" t="s">
-        <v>36</v>
+      <c r="AE30" s="1">
+        <v>0</v>
       </c>
       <c r="AF30" s="1" t="s">
         <v>31</v>
@@ -5614,8 +5614,8 @@
       <c r="V31" s="1" t="s">
         <v>131</v>
       </c>
-      <c r="AE31" s="1" t="s">
-        <v>36</v>
+      <c r="AE31" s="1">
+        <v>0</v>
       </c>
       <c r="AF31" s="1" t="s">
         <v>31</v>
@@ -5658,8 +5658,8 @@
       <c r="S32" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="AE32" s="1" t="s">
-        <v>36</v>
+      <c r="AE32" s="1">
+        <v>0</v>
       </c>
       <c r="AF32" s="1" t="s">
         <v>31</v>
@@ -5705,8 +5705,8 @@
       <c r="V33" s="5" t="s">
         <v>132</v>
       </c>
-      <c r="AE33" s="1" t="s">
-        <v>36</v>
+      <c r="AE33" s="1">
+        <v>0</v>
       </c>
       <c r="AF33" s="1" t="s">
         <v>31</v>
@@ -5746,8 +5746,8 @@
       <c r="S34" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="AE34" s="1" t="s">
-        <v>36</v>
+      <c r="AE34" s="1">
+        <v>0</v>
       </c>
       <c r="AF34" s="1" t="s">
         <v>31</v>
@@ -5793,8 +5793,8 @@
       <c r="S35" s="1" t="s">
         <v>118</v>
       </c>
-      <c r="AE35" s="1" t="s">
-        <v>36</v>
+      <c r="AE35" s="1">
+        <v>0</v>
       </c>
       <c r="AF35" s="1" t="s">
         <v>31</v>
@@ -5846,8 +5846,8 @@
       <c r="V36" s="1" t="s">
         <v>142</v>
       </c>
-      <c r="AE36" s="1" t="s">
-        <v>36</v>
+      <c r="AE36" s="1">
+        <v>0</v>
       </c>
       <c r="AF36" s="1" t="s">
         <v>31</v>
@@ -5887,8 +5887,8 @@
       <c r="S37" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="AE37" s="1" t="s">
-        <v>36</v>
+      <c r="AE37" s="1">
+        <v>0</v>
       </c>
       <c r="AF37" s="1" t="s">
         <v>31</v>
@@ -5937,8 +5937,8 @@
       <c r="V38" s="1" t="s">
         <v>148</v>
       </c>
-      <c r="AE38" s="1" t="s">
-        <v>36</v>
+      <c r="AE38" s="1">
+        <v>0</v>
       </c>
       <c r="AF38" s="1" t="s">
         <v>31</v>
@@ -5978,8 +5978,8 @@
       <c r="S39" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="AE39" s="1" t="s">
-        <v>36</v>
+      <c r="AE39" s="1">
+        <v>0</v>
       </c>
       <c r="AF39" s="1" t="s">
         <v>31</v>
@@ -6022,8 +6022,8 @@
       <c r="S40" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="AE40" s="1" t="s">
-        <v>36</v>
+      <c r="AE40" s="1">
+        <v>0</v>
       </c>
       <c r="AF40" s="1" t="s">
         <v>31</v>
@@ -6066,8 +6066,8 @@
       <c r="S41" s="1" t="s">
         <v>118</v>
       </c>
-      <c r="AE41" s="1" t="s">
-        <v>36</v>
+      <c r="AE41" s="1">
+        <v>0</v>
       </c>
       <c r="AF41" s="1" t="s">
         <v>31</v>
@@ -6122,8 +6122,8 @@
       <c r="V42" s="1" t="s">
         <v>178</v>
       </c>
-      <c r="AE42" s="1" t="s">
-        <v>36</v>
+      <c r="AE42" s="1">
+        <v>0</v>
       </c>
       <c r="AF42" s="1" t="s">
         <v>31</v>
@@ -6163,8 +6163,8 @@
       <c r="S43" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="AE43" s="1" t="s">
-        <v>36</v>
+      <c r="AE43" s="1">
+        <v>0</v>
       </c>
       <c r="AF43" s="1" t="s">
         <v>31</v>
@@ -6207,8 +6207,8 @@
       <c r="S44" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="AE44" s="1" t="s">
-        <v>36</v>
+      <c r="AE44" s="1">
+        <v>0</v>
       </c>
       <c r="AF44" s="1" t="s">
         <v>31</v>
@@ -6251,8 +6251,8 @@
       <c r="S45" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="AE45" s="1" t="s">
-        <v>36</v>
+      <c r="AE45" s="1">
+        <v>0</v>
       </c>
       <c r="AF45" s="1" t="s">
         <v>31</v>
@@ -6295,8 +6295,8 @@
       <c r="S46" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="AE46" s="1" t="s">
-        <v>36</v>
+      <c r="AE46" s="1">
+        <v>0</v>
       </c>
       <c r="AF46" s="1" t="s">
         <v>31</v>
@@ -6339,8 +6339,8 @@
       <c r="S47" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="AE47" s="1" t="s">
-        <v>36</v>
+      <c r="AE47" s="1">
+        <v>0</v>
       </c>
       <c r="AF47" s="1" t="s">
         <v>31</v>
@@ -6389,8 +6389,8 @@
       <c r="V48" s="1" t="s">
         <v>148</v>
       </c>
-      <c r="AE48" s="1" t="s">
-        <v>36</v>
+      <c r="AE48" s="1">
+        <v>0</v>
       </c>
       <c r="AF48" s="1" t="s">
         <v>31</v>
@@ -6430,8 +6430,8 @@
       <c r="S49" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="AE49" s="1" t="s">
-        <v>36</v>
+      <c r="AE49" s="1">
+        <v>0</v>
       </c>
       <c r="AF49" s="1" t="s">
         <v>31</v>
@@ -6474,8 +6474,8 @@
       <c r="S50" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="AE50" s="1" t="s">
-        <v>36</v>
+      <c r="AE50" s="1">
+        <v>0</v>
       </c>
       <c r="AF50" s="1" t="s">
         <v>31</v>
@@ -6515,8 +6515,8 @@
       <c r="S51" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="AE51" s="1" t="s">
-        <v>36</v>
+      <c r="AE51" s="1">
+        <v>0</v>
       </c>
       <c r="AF51" s="1" t="s">
         <v>31</v>
@@ -6556,8 +6556,8 @@
       <c r="S52" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="AE52" s="1" t="s">
-        <v>36</v>
+      <c r="AE52" s="1">
+        <v>0</v>
       </c>
       <c r="AF52" s="1" t="s">
         <v>31</v>
@@ -6606,8 +6606,8 @@
       <c r="S53" s="1" t="s">
         <v>117</v>
       </c>
-      <c r="AE53" s="1" t="s">
-        <v>36</v>
+      <c r="AE53" s="1">
+        <v>0</v>
       </c>
       <c r="AF53" s="1" t="s">
         <v>31</v>
@@ -6653,8 +6653,8 @@
       <c r="S54" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="AE54" s="1" t="s">
-        <v>36</v>
+      <c r="AE54" s="1">
+        <v>0</v>
       </c>
       <c r="AF54" s="1" t="s">
         <v>31</v>
@@ -6697,8 +6697,8 @@
       <c r="S55" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="AE55" s="1" t="s">
-        <v>36</v>
+      <c r="AE55" s="1">
+        <v>0</v>
       </c>
       <c r="AF55" s="1" t="s">
         <v>31</v>
@@ -6744,8 +6744,8 @@
       <c r="V56" s="5" t="s">
         <v>176</v>
       </c>
-      <c r="AE56" s="1" t="s">
-        <v>36</v>
+      <c r="AE56" s="1">
+        <v>0</v>
       </c>
       <c r="AF56" s="1" t="s">
         <v>31</v>
@@ -6792,8 +6792,8 @@
       <c r="S58" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="AE58" s="1" t="s">
-        <v>36</v>
+      <c r="AE58" s="1">
+        <v>0</v>
       </c>
       <c r="AF58" s="1" t="s">
         <v>31</v>
@@ -6836,8 +6836,8 @@
       <c r="S59" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="AE59" s="1" t="s">
-        <v>36</v>
+      <c r="AE59" s="1">
+        <v>0</v>
       </c>
       <c r="AF59" s="1" t="s">
         <v>31</v>
@@ -6880,8 +6880,8 @@
       <c r="S60" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="AE60" s="1" t="s">
-        <v>36</v>
+      <c r="AE60" s="1">
+        <v>0</v>
       </c>
       <c r="AF60" s="1" t="s">
         <v>31</v>
@@ -6924,8 +6924,8 @@
       <c r="S61" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="AE61" s="1" t="s">
-        <v>36</v>
+      <c r="AE61" s="1">
+        <v>0</v>
       </c>
       <c r="AF61" s="1" t="s">
         <v>31</v>
@@ -6968,8 +6968,8 @@
       <c r="S62" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="AE62" s="1" t="s">
-        <v>36</v>
+      <c r="AE62" s="1">
+        <v>0</v>
       </c>
       <c r="AF62" s="1" t="s">
         <v>31</v>
@@ -7014,8 +7014,8 @@
       </c>
       <c r="T63" s="3"/>
       <c r="U63" s="3"/>
-      <c r="AE63" s="1" t="s">
-        <v>36</v>
+      <c r="AE63" s="1">
+        <v>0</v>
       </c>
       <c r="AF63" s="1" t="s">
         <v>31</v>
@@ -7058,8 +7058,8 @@
       <c r="S64" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="AE64" s="1" t="s">
-        <v>36</v>
+      <c r="AE64" s="1">
+        <v>0</v>
       </c>
       <c r="AF64" s="1" t="s">
         <v>31</v>
@@ -7108,8 +7108,8 @@
       <c r="S65" s="1" t="s">
         <v>181</v>
       </c>
-      <c r="AE65" s="1" t="s">
-        <v>36</v>
+      <c r="AE65" s="1">
+        <v>0</v>
       </c>
       <c r="AF65" s="1" t="s">
         <v>31</v>
@@ -7158,8 +7158,8 @@
       <c r="Y66" s="1" t="s">
         <v>835</v>
       </c>
-      <c r="AE66" s="1" t="s">
-        <v>36</v>
+      <c r="AE66" s="1">
+        <v>0</v>
       </c>
       <c r="AF66" s="1" t="s">
         <v>31</v>
@@ -7193,8 +7193,8 @@
       <c r="S67" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="AE67" s="1" t="s">
-        <v>36</v>
+      <c r="AE67" s="1">
+        <v>0</v>
       </c>
       <c r="AF67" s="1" t="s">
         <v>31</v>
@@ -7228,8 +7228,8 @@
       <c r="S68" s="1" t="s">
         <v>181</v>
       </c>
-      <c r="AE68" s="1" t="s">
-        <v>36</v>
+      <c r="AE68" s="1">
+        <v>0</v>
       </c>
       <c r="AF68" s="1" t="s">
         <v>31</v>
@@ -7263,8 +7263,8 @@
       <c r="S69" s="1" t="s">
         <v>181</v>
       </c>
-      <c r="AE69" s="1" t="s">
-        <v>36</v>
+      <c r="AE69" s="1">
+        <v>0</v>
       </c>
       <c r="AF69" s="1" t="s">
         <v>31</v>
@@ -7307,8 +7307,8 @@
       <c r="S70" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="AE70" s="1" t="s">
-        <v>36</v>
+      <c r="AE70" s="1">
+        <v>0</v>
       </c>
       <c r="AF70" s="1" t="s">
         <v>31</v>
@@ -7351,8 +7351,8 @@
       <c r="S71" s="1" t="s">
         <v>181</v>
       </c>
-      <c r="AE71" s="1" t="s">
-        <v>36</v>
+      <c r="AE71" s="1">
+        <v>0</v>
       </c>
       <c r="AF71" s="1" t="s">
         <v>31</v>
@@ -7395,8 +7395,8 @@
       <c r="S72" s="1" t="s">
         <v>181</v>
       </c>
-      <c r="AE72" s="1" t="s">
-        <v>36</v>
+      <c r="AE72" s="1">
+        <v>0</v>
       </c>
       <c r="AF72" s="1" t="s">
         <v>31</v>
@@ -7439,8 +7439,8 @@
       <c r="S73" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="AE73" s="1" t="s">
-        <v>36</v>
+      <c r="AE73" s="1">
+        <v>0</v>
       </c>
       <c r="AF73" s="1" t="s">
         <v>31</v>
@@ -7483,8 +7483,8 @@
       <c r="S74" s="1" t="s">
         <v>181</v>
       </c>
-      <c r="AE74" s="1" t="s">
-        <v>36</v>
+      <c r="AE74" s="1">
+        <v>0</v>
       </c>
       <c r="AF74" s="1" t="s">
         <v>31</v>
@@ -7527,8 +7527,8 @@
       <c r="S75" s="1" t="s">
         <v>181</v>
       </c>
-      <c r="AE75" s="1" t="s">
-        <v>36</v>
+      <c r="AE75" s="1">
+        <v>0</v>
       </c>
       <c r="AF75" s="1" t="s">
         <v>31</v>
@@ -7571,8 +7571,8 @@
       <c r="S76" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="AE76" s="1" t="s">
-        <v>36</v>
+      <c r="AE76" s="1">
+        <v>0</v>
       </c>
       <c r="AF76" s="1" t="s">
         <v>31</v>
@@ -7615,8 +7615,8 @@
       <c r="S77" s="1" t="s">
         <v>181</v>
       </c>
-      <c r="AE77" s="1" t="s">
-        <v>36</v>
+      <c r="AE77" s="1">
+        <v>0</v>
       </c>
       <c r="AF77" s="1" t="s">
         <v>31</v>
@@ -7659,8 +7659,8 @@
       <c r="S78" s="1" t="s">
         <v>181</v>
       </c>
-      <c r="AE78" s="1" t="s">
-        <v>36</v>
+      <c r="AE78" s="1">
+        <v>0</v>
       </c>
       <c r="AF78" s="1" t="s">
         <v>31</v>
@@ -7694,8 +7694,8 @@
       <c r="S79" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="AE79" s="1" t="s">
-        <v>36</v>
+      <c r="AE79" s="1">
+        <v>0</v>
       </c>
       <c r="AF79" s="1" t="s">
         <v>31</v>
@@ -7729,8 +7729,8 @@
       <c r="S80" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="AE80" s="1" t="s">
-        <v>36</v>
+      <c r="AE80" s="1">
+        <v>0</v>
       </c>
       <c r="AF80" s="1" t="s">
         <v>31</v>
@@ -7773,8 +7773,8 @@
       <c r="S81" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="AE81" s="1" t="s">
-        <v>36</v>
+      <c r="AE81" s="1">
+        <v>0</v>
       </c>
       <c r="AF81" s="1" t="s">
         <v>31</v>
@@ -7826,8 +7826,8 @@
       <c r="S82" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="AE82" s="1" t="s">
-        <v>36</v>
+      <c r="AE82" s="1">
+        <v>0</v>
       </c>
       <c r="AF82" s="1" t="s">
         <v>31</v>
@@ -7873,8 +7873,8 @@
       <c r="S83" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="AE83" s="1" t="s">
-        <v>36</v>
+      <c r="AE83" s="1">
+        <v>0</v>
       </c>
       <c r="AF83" s="1" t="s">
         <v>31</v>
@@ -7920,8 +7920,8 @@
       <c r="S84" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="AE84" s="1" t="s">
-        <v>36</v>
+      <c r="AE84" s="1">
+        <v>0</v>
       </c>
       <c r="AF84" s="1" t="s">
         <v>31</v>
@@ -7967,8 +7967,8 @@
       <c r="S85" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="AE85" s="1" t="s">
-        <v>36</v>
+      <c r="AE85" s="1">
+        <v>0</v>
       </c>
       <c r="AF85" s="1" t="s">
         <v>31</v>
@@ -8014,8 +8014,8 @@
       <c r="S86" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="AE86" s="1" t="s">
-        <v>36</v>
+      <c r="AE86" s="1">
+        <v>0</v>
       </c>
       <c r="AF86" s="1" t="s">
         <v>31</v>
@@ -8061,8 +8061,8 @@
       <c r="S87" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="AE87" s="1" t="s">
-        <v>36</v>
+      <c r="AE87" s="1">
+        <v>0</v>
       </c>
       <c r="AF87" s="1" t="s">
         <v>31</v>
@@ -8105,8 +8105,8 @@
       <c r="S88" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="AE88" s="1" t="s">
-        <v>36</v>
+      <c r="AE88" s="1">
+        <v>0</v>
       </c>
       <c r="AF88" s="1" t="s">
         <v>31</v>
@@ -8164,8 +8164,8 @@
       <c r="Y89" s="1" t="s">
         <v>845</v>
       </c>
-      <c r="AE89" s="1" t="s">
-        <v>36</v>
+      <c r="AE89" s="1">
+        <v>0</v>
       </c>
       <c r="AF89" s="1" t="s">
         <v>31</v>
@@ -8214,8 +8214,8 @@
       <c r="Y90" s="1" t="s">
         <v>846</v>
       </c>
-      <c r="AE90" s="1" t="s">
-        <v>36</v>
+      <c r="AE90" s="1">
+        <v>0</v>
       </c>
       <c r="AF90" s="1" t="s">
         <v>31</v>
@@ -8252,8 +8252,8 @@
       <c r="S91" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="AE91" s="1" t="s">
-        <v>36</v>
+      <c r="AE91" s="1">
+        <v>0</v>
       </c>
       <c r="AF91" s="1" t="s">
         <v>31</v>
@@ -8293,8 +8293,8 @@
       <c r="S92" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="AE92" s="1" t="s">
-        <v>36</v>
+      <c r="AE92" s="1">
+        <v>0</v>
       </c>
       <c r="AF92" s="1" t="s">
         <v>31</v>
@@ -8334,8 +8334,8 @@
       <c r="S93" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="AE93" s="1" t="s">
-        <v>36</v>
+      <c r="AE93" s="1">
+        <v>0</v>
       </c>
       <c r="AF93" s="1" t="s">
         <v>31</v>
@@ -8375,8 +8375,8 @@
       <c r="S94" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="AE94" s="1" t="s">
-        <v>36</v>
+      <c r="AE94" s="1">
+        <v>0</v>
       </c>
       <c r="AF94" s="1" t="s">
         <v>31</v>
@@ -8407,8 +8407,8 @@
       <c r="S95" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="AE95" s="1" t="s">
-        <v>36</v>
+      <c r="AE95" s="1">
+        <v>0</v>
       </c>
       <c r="AF95" s="1" t="s">
         <v>31</v>
@@ -8463,8 +8463,8 @@
       <c r="AD96" s="8" t="s">
         <v>819</v>
       </c>
-      <c r="AE96" s="1" t="s">
-        <v>36</v>
+      <c r="AE96" s="1">
+        <v>0</v>
       </c>
       <c r="AF96" s="1" t="s">
         <v>31</v>
@@ -8504,8 +8504,8 @@
       <c r="S97" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="AE97" s="1" t="s">
-        <v>36</v>
+      <c r="AE97" s="1">
+        <v>0</v>
       </c>
       <c r="AF97" s="1" t="s">
         <v>31</v>
@@ -8545,8 +8545,8 @@
       <c r="S98" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="AE98" s="1" t="s">
-        <v>36</v>
+      <c r="AE98" s="1">
+        <v>0</v>
       </c>
       <c r="AF98" s="1" t="s">
         <v>31</v>
@@ -8586,8 +8586,8 @@
       <c r="S99" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="AE99" s="1" t="s">
-        <v>36</v>
+      <c r="AE99" s="1">
+        <v>0</v>
       </c>
       <c r="AF99" s="1" t="s">
         <v>31</v>
@@ -8636,8 +8636,8 @@
       <c r="AD100" s="1" t="s">
         <v>821</v>
       </c>
-      <c r="AE100" s="1" t="s">
-        <v>36</v>
+      <c r="AE100" s="1">
+        <v>0</v>
       </c>
       <c r="AF100" s="1" t="s">
         <v>31</v>
@@ -8680,8 +8680,8 @@
       <c r="S101" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="AE101" s="1" t="s">
-        <v>36</v>
+      <c r="AE101" s="1">
+        <v>0</v>
       </c>
       <c r="AF101" s="1" t="s">
         <v>31</v>
@@ -8724,8 +8724,8 @@
       <c r="S102" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="AE102" s="1" t="s">
-        <v>36</v>
+      <c r="AE102" s="1">
+        <v>0</v>
       </c>
       <c r="AF102" s="1" t="s">
         <v>31</v>
@@ -8768,8 +8768,8 @@
       <c r="S103" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="AE103" s="1" t="s">
-        <v>36</v>
+      <c r="AE103" s="1">
+        <v>0</v>
       </c>
       <c r="AF103" s="1" t="s">
         <v>31</v>
@@ -8812,8 +8812,8 @@
       <c r="S104" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="AE104" s="1" t="s">
-        <v>36</v>
+      <c r="AE104" s="1">
+        <v>0</v>
       </c>
       <c r="AF104" s="1" t="s">
         <v>31</v>
@@ -8858,8 +8858,8 @@
       </c>
       <c r="T105" s="3"/>
       <c r="U105" s="3"/>
-      <c r="AE105" s="1" t="s">
-        <v>36</v>
+      <c r="AE105" s="1">
+        <v>0</v>
       </c>
       <c r="AF105" s="1" t="s">
         <v>31</v>
@@ -8902,8 +8902,8 @@
       <c r="S106" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="AE106" s="1" t="s">
-        <v>36</v>
+      <c r="AE106" s="1">
+        <v>0</v>
       </c>
       <c r="AF106" s="1" t="s">
         <v>31</v>
@@ -8946,8 +8946,8 @@
       <c r="S107" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="AE107" s="1" t="s">
-        <v>36</v>
+      <c r="AE107" s="1">
+        <v>0</v>
       </c>
       <c r="AF107" s="1" t="s">
         <v>31</v>
@@ -8990,8 +8990,8 @@
       <c r="S108" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="AE108" s="1" t="s">
-        <v>36</v>
+      <c r="AE108" s="1">
+        <v>0</v>
       </c>
       <c r="AF108" s="1" t="s">
         <v>31</v>
@@ -9043,8 +9043,8 @@
       <c r="V109" s="1" t="s">
         <v>148</v>
       </c>
-      <c r="AE109" s="1" t="s">
-        <v>36</v>
+      <c r="AE109" s="1">
+        <v>0</v>
       </c>
       <c r="AF109" s="1" t="s">
         <v>31</v>
@@ -9090,8 +9090,8 @@
       <c r="V110" s="9" t="s">
         <v>334</v>
       </c>
-      <c r="AE110" s="1" t="s">
-        <v>36</v>
+      <c r="AE110" s="1">
+        <v>0</v>
       </c>
       <c r="AF110" s="1" t="s">
         <v>31</v>
@@ -9134,8 +9134,8 @@
       <c r="S111" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="AE111" s="1" t="s">
-        <v>36</v>
+      <c r="AE111" s="1">
+        <v>0</v>
       </c>
       <c r="AF111" s="1" t="s">
         <v>31</v>
@@ -9178,8 +9178,8 @@
       <c r="S112" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="AE112" s="1" t="s">
-        <v>36</v>
+      <c r="AE112" s="1">
+        <v>0</v>
       </c>
       <c r="AF112" s="1" t="s">
         <v>31</v>
@@ -9231,8 +9231,8 @@
       <c r="V113" s="1" t="s">
         <v>148</v>
       </c>
-      <c r="AE113" s="1" t="s">
-        <v>36</v>
+      <c r="AE113" s="1">
+        <v>0</v>
       </c>
       <c r="AF113" s="1" t="s">
         <v>31</v>
@@ -9281,8 +9281,8 @@
       <c r="V114" s="9" t="s">
         <v>383</v>
       </c>
-      <c r="AE114" s="1" t="s">
-        <v>36</v>
+      <c r="AE114" s="1">
+        <v>0</v>
       </c>
       <c r="AF114" s="1" t="s">
         <v>31</v>
@@ -9334,8 +9334,8 @@
       <c r="Z115" s="8" t="s">
         <v>817</v>
       </c>
-      <c r="AE115" s="1" t="s">
-        <v>36</v>
+      <c r="AE115" s="1">
+        <v>0</v>
       </c>
       <c r="AF115" s="1" t="s">
         <v>31</v>
@@ -9375,8 +9375,8 @@
       <c r="S116" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="AE116" s="1" t="s">
-        <v>36</v>
+      <c r="AE116" s="1">
+        <v>0</v>
       </c>
       <c r="AF116" s="1" t="s">
         <v>31</v>
@@ -9432,8 +9432,8 @@
       <c r="S117" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="AE117" s="1" t="s">
-        <v>36</v>
+      <c r="AE117" s="1">
+        <v>0</v>
       </c>
       <c r="AF117" s="1" t="s">
         <v>31</v>
@@ -9476,8 +9476,8 @@
       <c r="S118" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="AE118" s="1" t="s">
-        <v>36</v>
+      <c r="AE118" s="1">
+        <v>0</v>
       </c>
       <c r="AF118" s="1" t="s">
         <v>31</v>
@@ -9529,8 +9529,8 @@
       <c r="S119" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="AE119" s="1" t="s">
-        <v>36</v>
+      <c r="AE119" s="1">
+        <v>0</v>
       </c>
       <c r="AF119" s="1" t="s">
         <v>31</v>
@@ -9573,8 +9573,8 @@
       <c r="S120" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="AE120" s="1" t="s">
-        <v>36</v>
+      <c r="AE120" s="1">
+        <v>0</v>
       </c>
       <c r="AF120" s="1" t="s">
         <v>31</v>
@@ -9617,8 +9617,8 @@
       <c r="S121" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="AE121" s="1" t="s">
-        <v>36</v>
+      <c r="AE121" s="1">
+        <v>0</v>
       </c>
       <c r="AF121" s="1" t="s">
         <v>31</v>
@@ -9665,8 +9665,8 @@
       <c r="S122" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="AE122" s="1" t="s">
-        <v>36</v>
+      <c r="AE122" s="1">
+        <v>0</v>
       </c>
       <c r="AF122" s="1" t="s">
         <v>31</v>
@@ -9712,8 +9712,8 @@
       <c r="S123" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="AE123" s="1" t="s">
-        <v>36</v>
+      <c r="AE123" s="1">
+        <v>0</v>
       </c>
       <c r="AF123" s="1" t="s">
         <v>31</v>
@@ -9759,8 +9759,8 @@
       <c r="V124" s="7" t="s">
         <v>388</v>
       </c>
-      <c r="AE124" s="1" t="s">
-        <v>36</v>
+      <c r="AE124" s="1">
+        <v>0</v>
       </c>
       <c r="AF124" s="1" t="s">
         <v>31</v>
@@ -9800,8 +9800,8 @@
       <c r="S125" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="AE125" s="1" t="s">
-        <v>36</v>
+      <c r="AE125" s="1">
+        <v>0</v>
       </c>
       <c r="AF125" s="1" t="s">
         <v>31</v>
@@ -9844,8 +9844,8 @@
       <c r="S126" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="AE126" s="1" t="s">
-        <v>36</v>
+      <c r="AE126" s="1">
+        <v>0</v>
       </c>
       <c r="AF126" s="1" t="s">
         <v>31</v>
@@ -9888,8 +9888,8 @@
       <c r="S127" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="AE127" s="1" t="s">
-        <v>36</v>
+      <c r="AE127" s="1">
+        <v>0</v>
       </c>
       <c r="AF127" s="1" t="s">
         <v>31</v>
@@ -9930,8 +9930,8 @@
         <v>36</v>
       </c>
       <c r="V128" s="8"/>
-      <c r="AE128" s="1" t="s">
-        <v>36</v>
+      <c r="AE128" s="1">
+        <v>0</v>
       </c>
       <c r="AF128" s="1" t="s">
         <v>31</v>
@@ -9971,8 +9971,8 @@
       <c r="S129" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="AE129" s="1" t="s">
-        <v>36</v>
+      <c r="AE129" s="1">
+        <v>0</v>
       </c>
       <c r="AF129" s="1" t="s">
         <v>31</v>
@@ -10012,8 +10012,8 @@
       <c r="S130" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="AE130" s="1" t="s">
-        <v>36</v>
+      <c r="AE130" s="1">
+        <v>0</v>
       </c>
       <c r="AF130" s="1" t="s">
         <v>31</v>
@@ -10053,8 +10053,8 @@
       <c r="S131" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="AE131" s="1" t="s">
-        <v>36</v>
+      <c r="AE131" s="1">
+        <v>0</v>
       </c>
       <c r="AF131" s="1" t="s">
         <v>31</v>
@@ -10094,8 +10094,8 @@
       <c r="S132" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="AE132" s="1" t="s">
-        <v>36</v>
+      <c r="AE132" s="1">
+        <v>0</v>
       </c>
       <c r="AF132" s="1" t="s">
         <v>31</v>
@@ -10142,8 +10142,8 @@
       <c r="S134" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="AE134" s="1" t="s">
-        <v>36</v>
+      <c r="AE134" s="1">
+        <v>0</v>
       </c>
       <c r="AF134" s="1" t="s">
         <v>31</v>
@@ -10186,8 +10186,8 @@
       <c r="S135" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="AE135" s="1" t="s">
-        <v>36</v>
+      <c r="AE135" s="1">
+        <v>0</v>
       </c>
       <c r="AF135" s="1" t="s">
         <v>31</v>
@@ -10230,8 +10230,8 @@
       <c r="S136" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="AE136" s="1" t="s">
-        <v>36</v>
+      <c r="AE136" s="1">
+        <v>0</v>
       </c>
       <c r="AF136" s="1" t="s">
         <v>31</v>
@@ -10274,8 +10274,8 @@
       <c r="S137" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="AE137" s="1" t="s">
-        <v>36</v>
+      <c r="AE137" s="1">
+        <v>0</v>
       </c>
       <c r="AF137" s="1" t="s">
         <v>31</v>
@@ -10318,8 +10318,8 @@
       <c r="S138" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="AE138" s="1" t="s">
-        <v>36</v>
+      <c r="AE138" s="1">
+        <v>0</v>
       </c>
       <c r="AF138" s="1" t="s">
         <v>31</v>
@@ -10362,8 +10362,8 @@
       <c r="S139" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="AE139" s="1" t="s">
-        <v>36</v>
+      <c r="AE139" s="1">
+        <v>0</v>
       </c>
       <c r="AF139" s="1" t="s">
         <v>31</v>
@@ -10406,8 +10406,8 @@
       <c r="S140" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="AE140" s="1" t="s">
-        <v>36</v>
+      <c r="AE140" s="1">
+        <v>0</v>
       </c>
       <c r="AF140" s="1" t="s">
         <v>31</v>
@@ -10450,8 +10450,8 @@
       <c r="S141" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="AE141" s="1" t="s">
-        <v>36</v>
+      <c r="AE141" s="1">
+        <v>0</v>
       </c>
       <c r="AF141" s="1" t="s">
         <v>31</v>
@@ -10497,8 +10497,8 @@
       <c r="S142" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="AE142" s="1" t="s">
-        <v>36</v>
+      <c r="AE142" s="1">
+        <v>0</v>
       </c>
       <c r="AF142" s="1" t="s">
         <v>31</v>
@@ -10541,8 +10541,8 @@
       <c r="S143" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="AE143" s="1" t="s">
-        <v>36</v>
+      <c r="AE143" s="1">
+        <v>0</v>
       </c>
       <c r="AF143" s="1" t="s">
         <v>31</v>
@@ -10582,8 +10582,8 @@
       <c r="R144" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="AE144" s="1" t="s">
-        <v>36</v>
+      <c r="AE144" s="1">
+        <v>0</v>
       </c>
       <c r="AF144" s="1" t="s">
         <v>31</v>
@@ -10629,8 +10629,8 @@
       <c r="AD145" s="1" t="s">
         <v>821</v>
       </c>
-      <c r="AE145" s="1" t="s">
-        <v>36</v>
+      <c r="AE145" s="1">
+        <v>0</v>
       </c>
       <c r="AF145" s="1" t="s">
         <v>31</v>
@@ -10673,8 +10673,8 @@
       <c r="S146" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="AE146" s="1" t="s">
-        <v>36</v>
+      <c r="AE146" s="1">
+        <v>0</v>
       </c>
       <c r="AF146" s="1" t="s">
         <v>31</v>
@@ -10714,8 +10714,8 @@
       <c r="S147" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="AE147" s="1" t="s">
-        <v>36</v>
+      <c r="AE147" s="1">
+        <v>0</v>
       </c>
       <c r="AF147" s="1" t="s">
         <v>31</v>
@@ -10758,8 +10758,8 @@
       <c r="S148" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="AE148" s="1" t="s">
-        <v>36</v>
+      <c r="AE148" s="1">
+        <v>0</v>
       </c>
       <c r="AF148" s="1" t="s">
         <v>31</v>
@@ -10802,8 +10802,8 @@
       <c r="S149" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="AE149" s="1" t="s">
-        <v>36</v>
+      <c r="AE149" s="1">
+        <v>0</v>
       </c>
       <c r="AF149" s="1" t="s">
         <v>31</v>
@@ -10843,8 +10843,8 @@
       <c r="S150" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="AE150" s="1" t="s">
-        <v>36</v>
+      <c r="AE150" s="1">
+        <v>0</v>
       </c>
       <c r="AF150" s="1" t="s">
         <v>31</v>
@@ -10884,8 +10884,8 @@
       <c r="S151" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="AE151" s="1" t="s">
-        <v>36</v>
+      <c r="AE151" s="1">
+        <v>0</v>
       </c>
       <c r="AF151" s="1" t="s">
         <v>31</v>
@@ -10925,8 +10925,8 @@
       <c r="S152" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="AE152" s="1" t="s">
-        <v>36</v>
+      <c r="AE152" s="1">
+        <v>0</v>
       </c>
       <c r="AF152" s="1" t="s">
         <v>31</v>
@@ -10981,8 +10981,8 @@
       <c r="Z153" s="8" t="s">
         <v>882</v>
       </c>
-      <c r="AE153" s="1" t="s">
-        <v>36</v>
+      <c r="AE153" s="1">
+        <v>0</v>
       </c>
       <c r="AF153" s="1" t="s">
         <v>31</v>
@@ -11031,8 +11031,8 @@
       <c r="Z154" s="8" t="s">
         <v>881</v>
       </c>
-      <c r="AE154" s="1" t="s">
-        <v>36</v>
+      <c r="AE154" s="1">
+        <v>0</v>
       </c>
       <c r="AF154" s="1" t="s">
         <v>31</v>
@@ -11075,8 +11075,8 @@
       <c r="S155" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="AE155" s="1" t="s">
-        <v>36</v>
+      <c r="AE155" s="1">
+        <v>0</v>
       </c>
       <c r="AF155" s="1" t="s">
         <v>634</v>
@@ -11113,8 +11113,8 @@
       <c r="S156" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="AE156" s="1" t="s">
-        <v>36</v>
+      <c r="AE156" s="1">
+        <v>0</v>
       </c>
       <c r="AF156" s="1" t="s">
         <v>31</v>
@@ -11154,8 +11154,8 @@
       <c r="S157" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="AE157" s="1" t="s">
-        <v>36</v>
+      <c r="AE157" s="1">
+        <v>0</v>
       </c>
       <c r="AF157" s="1" t="s">
         <v>31</v>
@@ -11207,8 +11207,8 @@
       <c r="Z158" s="8" t="s">
         <v>854</v>
       </c>
-      <c r="AE158" s="1" t="s">
-        <v>36</v>
+      <c r="AE158" s="1">
+        <v>0</v>
       </c>
       <c r="AF158" s="1" t="s">
         <v>31</v>
@@ -11245,8 +11245,8 @@
       <c r="S159" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="AE159" s="1" t="s">
-        <v>36</v>
+      <c r="AE159" s="1">
+        <v>0</v>
       </c>
       <c r="AF159" s="1" t="s">
         <v>31</v>
@@ -11289,8 +11289,8 @@
       <c r="S160" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="AE160" s="1" t="s">
-        <v>36</v>
+      <c r="AE160" s="1">
+        <v>0</v>
       </c>
       <c r="AF160" s="1" t="s">
         <v>31</v>
@@ -11333,8 +11333,8 @@
       <c r="S161" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="AE161" s="1" t="s">
-        <v>36</v>
+      <c r="AE161" s="1">
+        <v>0</v>
       </c>
       <c r="AF161" s="1" t="s">
         <v>31</v>
@@ -11377,8 +11377,8 @@
       <c r="S162" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="AE162" s="1" t="s">
-        <v>36</v>
+      <c r="AE162" s="1">
+        <v>0</v>
       </c>
       <c r="AF162" s="1" t="s">
         <v>31</v>
@@ -11421,8 +11421,8 @@
       <c r="S163" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="AE163" s="1" t="s">
-        <v>36</v>
+      <c r="AE163" s="1">
+        <v>0</v>
       </c>
       <c r="AF163" s="1" t="s">
         <v>31</v>
@@ -11465,8 +11465,8 @@
       <c r="S164" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="AE164" s="1" t="s">
-        <v>36</v>
+      <c r="AE164" s="1">
+        <v>0</v>
       </c>
       <c r="AF164" s="1" t="s">
         <v>31</v>
@@ -11506,8 +11506,8 @@
       <c r="S165" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="AE165" s="1" t="s">
-        <v>36</v>
+      <c r="AE165" s="1">
+        <v>0</v>
       </c>
       <c r="AF165" s="1" t="s">
         <v>31</v>
@@ -11550,8 +11550,8 @@
       <c r="S166" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="AE166" s="1" t="s">
-        <v>36</v>
+      <c r="AE166" s="1">
+        <v>0</v>
       </c>
       <c r="AF166" s="1" t="s">
         <v>31</v>
@@ -11591,8 +11591,8 @@
       <c r="S167" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="AE167" s="1" t="s">
-        <v>36</v>
+      <c r="AE167" s="1">
+        <v>0</v>
       </c>
       <c r="AF167" s="1" t="s">
         <v>31</v>
@@ -11626,8 +11626,8 @@
       <c r="S168" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="AE168" s="1" t="s">
-        <v>36</v>
+      <c r="AE168" s="1">
+        <v>0</v>
       </c>
       <c r="AF168" s="1" t="s">
         <v>31</v>
@@ -11670,8 +11670,8 @@
       <c r="S169" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="AE169" s="1" t="s">
-        <v>36</v>
+      <c r="AE169" s="1">
+        <v>0</v>
       </c>
       <c r="AF169" s="1" t="s">
         <v>31</v>
@@ -11705,8 +11705,8 @@
       <c r="S170" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="AE170" s="1" t="s">
-        <v>36</v>
+      <c r="AE170" s="1">
+        <v>0</v>
       </c>
       <c r="AF170" s="1" t="s">
         <v>31</v>
@@ -11761,8 +11761,8 @@
       <c r="Z171" s="8" t="s">
         <v>858</v>
       </c>
-      <c r="AE171" s="1" t="s">
-        <v>36</v>
+      <c r="AE171" s="1">
+        <v>0</v>
       </c>
       <c r="AF171" s="1" t="s">
         <v>31</v>
@@ -11802,8 +11802,8 @@
       <c r="S172" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="AE172" s="1" t="s">
-        <v>36</v>
+      <c r="AE172" s="1">
+        <v>0</v>
       </c>
       <c r="AF172" s="1" t="s">
         <v>31</v>
@@ -11858,8 +11858,8 @@
       <c r="Z173" s="8" t="s">
         <v>857</v>
       </c>
-      <c r="AE173" s="1" t="s">
-        <v>36</v>
+      <c r="AE173" s="1">
+        <v>0</v>
       </c>
       <c r="AF173" s="1" t="s">
         <v>31</v>
@@ -11904,8 +11904,8 @@
       </c>
       <c r="T174" s="3"/>
       <c r="U174" s="3"/>
-      <c r="AE174" s="1" t="s">
-        <v>36</v>
+      <c r="AE174" s="1">
+        <v>0</v>
       </c>
       <c r="AF174" s="1" t="s">
         <v>31</v>
@@ -11948,8 +11948,8 @@
       <c r="S175" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="AE175" s="1" t="s">
-        <v>36</v>
+      <c r="AE175" s="1">
+        <v>0</v>
       </c>
       <c r="AF175" s="1" t="s">
         <v>31</v>
@@ -12004,8 +12004,8 @@
       <c r="Z176" s="8" t="s">
         <v>858</v>
       </c>
-      <c r="AE176" s="1" t="s">
-        <v>36</v>
+      <c r="AE176" s="1">
+        <v>0</v>
       </c>
       <c r="AF176" s="1" t="s">
         <v>31</v>
@@ -12051,8 +12051,8 @@
       <c r="S177" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="AE177" s="1" t="s">
-        <v>36</v>
+      <c r="AE177" s="1">
+        <v>0</v>
       </c>
       <c r="AF177" s="1" t="s">
         <v>31</v>
@@ -12098,8 +12098,8 @@
       <c r="S178" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="AE178" s="1" t="s">
-        <v>36</v>
+      <c r="AE178" s="1">
+        <v>0</v>
       </c>
       <c r="AF178" s="1" t="s">
         <v>31</v>
@@ -12141,8 +12141,8 @@
       </c>
       <c r="T179" s="3"/>
       <c r="U179" s="3"/>
-      <c r="AE179" s="1" t="s">
-        <v>36</v>
+      <c r="AE179" s="1">
+        <v>0</v>
       </c>
       <c r="AF179" s="1" t="s">
         <v>31</v>
@@ -12188,8 +12188,8 @@
       <c r="S180" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="AE180" s="1" t="s">
-        <v>36</v>
+      <c r="AE180" s="1">
+        <v>0</v>
       </c>
       <c r="AF180" s="1" t="s">
         <v>31</v>
@@ -12244,8 +12244,8 @@
       <c r="Z181" s="8" t="s">
         <v>861</v>
       </c>
-      <c r="AE181" s="1" t="s">
-        <v>36</v>
+      <c r="AE181" s="1">
+        <v>0</v>
       </c>
       <c r="AF181" s="1" t="s">
         <v>31</v>
@@ -12285,8 +12285,8 @@
       <c r="S182" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="AE182" s="1" t="s">
-        <v>36</v>
+      <c r="AE182" s="1">
+        <v>0</v>
       </c>
       <c r="AF182" s="1" t="s">
         <v>31</v>
@@ -12326,8 +12326,8 @@
       <c r="S183" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="AE183" s="1" t="s">
-        <v>36</v>
+      <c r="AE183" s="1">
+        <v>0</v>
       </c>
       <c r="AF183" s="1" t="s">
         <v>31</v>
@@ -12375,8 +12375,8 @@
       </c>
       <c r="T184" s="3"/>
       <c r="U184" s="3"/>
-      <c r="AE184" s="1" t="s">
-        <v>36</v>
+      <c r="AE184" s="1">
+        <v>0</v>
       </c>
       <c r="AF184" s="1" t="s">
         <v>31</v>
@@ -12416,8 +12416,8 @@
       <c r="S185" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="AE185" s="1" t="s">
-        <v>36</v>
+      <c r="AE185" s="1">
+        <v>0</v>
       </c>
       <c r="AF185" s="1" t="s">
         <v>31</v>
@@ -12460,8 +12460,8 @@
       <c r="S186" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="AE186" s="1" t="s">
-        <v>36</v>
+      <c r="AE186" s="1">
+        <v>0</v>
       </c>
       <c r="AF186" s="1" t="s">
         <v>31</v>
@@ -12504,8 +12504,8 @@
       <c r="S187" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="AE187" s="1" t="s">
-        <v>36</v>
+      <c r="AE187" s="1">
+        <v>0</v>
       </c>
       <c r="AF187" s="1" t="s">
         <v>31</v>
@@ -12545,8 +12545,8 @@
       <c r="S188" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="AE188" s="1" t="s">
-        <v>36</v>
+      <c r="AE188" s="1">
+        <v>0</v>
       </c>
       <c r="AF188" s="1" t="s">
         <v>31</v>
@@ -12589,8 +12589,8 @@
       <c r="S189" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="AE189" s="1" t="s">
-        <v>36</v>
+      <c r="AE189" s="1">
+        <v>0</v>
       </c>
       <c r="AF189" s="1" t="s">
         <v>31</v>
@@ -12630,8 +12630,8 @@
       <c r="S190" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="AE190" s="1" t="s">
-        <v>36</v>
+      <c r="AE190" s="1">
+        <v>0</v>
       </c>
       <c r="AF190" s="1" t="s">
         <v>31</v>
@@ -12674,8 +12674,8 @@
       <c r="S191" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="AE191" s="1" t="s">
-        <v>36</v>
+      <c r="AE191" s="1">
+        <v>0</v>
       </c>
       <c r="AF191" s="1" t="s">
         <v>31</v>
@@ -12718,8 +12718,8 @@
       <c r="S192" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="AE192" s="1" t="s">
-        <v>36</v>
+      <c r="AE192" s="1">
+        <v>0</v>
       </c>
       <c r="AF192" s="1" t="s">
         <v>31</v>
@@ -12759,8 +12759,8 @@
       <c r="S193" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="AE193" s="1" t="s">
-        <v>36</v>
+      <c r="AE193" s="1">
+        <v>0</v>
       </c>
       <c r="AF193" s="1" t="s">
         <v>31</v>
@@ -12815,8 +12815,8 @@
       <c r="AD194" s="8" t="s">
         <v>864</v>
       </c>
-      <c r="AE194" s="1" t="s">
-        <v>36</v>
+      <c r="AE194" s="1">
+        <v>0</v>
       </c>
       <c r="AF194" s="1" t="s">
         <v>31</v>
@@ -12859,8 +12859,8 @@
       <c r="S195" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="AE195" s="1" t="s">
-        <v>36</v>
+      <c r="AE195" s="1">
+        <v>0</v>
       </c>
       <c r="AF195" s="1" t="s">
         <v>31</v>
@@ -12903,8 +12903,8 @@
       <c r="S196" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="AE196" s="1" t="s">
-        <v>36</v>
+      <c r="AE196" s="1">
+        <v>0</v>
       </c>
       <c r="AF196" s="1" t="s">
         <v>31</v>
@@ -12959,8 +12959,8 @@
       <c r="V197" s="1" t="s">
         <v>142</v>
       </c>
-      <c r="AE197" s="1" t="s">
-        <v>36</v>
+      <c r="AE197" s="1">
+        <v>0</v>
       </c>
       <c r="AF197" s="1" t="s">
         <v>31</v>
@@ -13009,8 +13009,8 @@
       <c r="S198" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="AE198" s="1" t="s">
-        <v>36</v>
+      <c r="AE198" s="1">
+        <v>0</v>
       </c>
       <c r="AF198" s="1" t="s">
         <v>31</v>
@@ -13053,8 +13053,8 @@
       <c r="S199" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="AE199" s="1" t="s">
-        <v>36</v>
+      <c r="AE199" s="1">
+        <v>0</v>
       </c>
       <c r="AF199" s="1" t="s">
         <v>31</v>
@@ -13097,8 +13097,8 @@
       <c r="S200" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="AE200" s="1" t="s">
-        <v>36</v>
+      <c r="AE200" s="1">
+        <v>0</v>
       </c>
       <c r="AF200" s="1" t="s">
         <v>31</v>
@@ -13141,8 +13141,8 @@
       <c r="S201" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="AE201" s="1" t="s">
-        <v>36</v>
+      <c r="AE201" s="1">
+        <v>0</v>
       </c>
       <c r="AF201" s="1" t="s">
         <v>31</v>
@@ -13185,8 +13185,8 @@
       <c r="S202" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="AE202" s="1" t="s">
-        <v>36</v>
+      <c r="AE202" s="1">
+        <v>0</v>
       </c>
       <c r="AF202" s="1" t="s">
         <v>31</v>
@@ -13229,8 +13229,8 @@
       <c r="S203" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="AE203" s="1" t="s">
-        <v>36</v>
+      <c r="AE203" s="1">
+        <v>0</v>
       </c>
       <c r="AF203" s="1" t="s">
         <v>31</v>
@@ -13267,8 +13267,8 @@
       <c r="S204" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="AE204" s="1" t="s">
-        <v>36</v>
+      <c r="AE204" s="1">
+        <v>0</v>
       </c>
       <c r="AF204" s="1" t="s">
         <v>31</v>
@@ -13314,8 +13314,8 @@
       <c r="S205" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="AE205" s="1" t="s">
-        <v>36</v>
+      <c r="AE205" s="1">
+        <v>0</v>
       </c>
       <c r="AF205" s="1" t="s">
         <v>31</v>
@@ -13352,8 +13352,8 @@
       <c r="S206" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="AE206" s="1" t="s">
-        <v>36</v>
+      <c r="AE206" s="1">
+        <v>0</v>
       </c>
       <c r="AF206" s="1" t="s">
         <v>31</v>
@@ -13393,8 +13393,8 @@
       <c r="S207" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="AE207" s="1" t="s">
-        <v>36</v>
+      <c r="AE207" s="1">
+        <v>0</v>
       </c>
       <c r="AF207" s="1" t="s">
         <v>31</v>
@@ -13437,8 +13437,8 @@
       <c r="S208" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="AE208" s="1" t="s">
-        <v>74</v>
+      <c r="AE208" s="1">
+        <v>1</v>
       </c>
       <c r="AF208" s="1" t="s">
         <v>31</v>
@@ -13481,8 +13481,8 @@
       <c r="S209" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="AE209" s="1" t="s">
-        <v>36</v>
+      <c r="AE209" s="1">
+        <v>0</v>
       </c>
       <c r="AF209" s="1" t="s">
         <v>31</v>
@@ -13519,8 +13519,8 @@
       <c r="S210" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="AE210" s="1" t="s">
-        <v>36</v>
+      <c r="AE210" s="1">
+        <v>0</v>
       </c>
       <c r="AF210" s="1" t="s">
         <v>31</v>
@@ -13557,8 +13557,8 @@
       <c r="S211" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="AE211" s="1" t="s">
-        <v>36</v>
+      <c r="AE211" s="1">
+        <v>0</v>
       </c>
       <c r="AF211" s="1" t="s">
         <v>31</v>
@@ -13592,8 +13592,8 @@
       <c r="S212" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="AE212" s="1" t="s">
-        <v>36</v>
+      <c r="AE212" s="1">
+        <v>0</v>
       </c>
       <c r="AF212" s="1" t="s">
         <v>31</v>
@@ -13627,8 +13627,8 @@
       <c r="S213" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="AE213" s="1" t="s">
-        <v>36</v>
+      <c r="AE213" s="1">
+        <v>0</v>
       </c>
       <c r="AF213" s="1" t="s">
         <v>31</v>
@@ -13671,8 +13671,8 @@
       <c r="S214" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="AE214" s="1" t="s">
-        <v>36</v>
+      <c r="AE214" s="1">
+        <v>0</v>
       </c>
       <c r="AF214" s="1" t="s">
         <v>31</v>
@@ -13709,8 +13709,8 @@
       <c r="S215" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="AE215" s="1" t="s">
-        <v>36</v>
+      <c r="AE215" s="1">
+        <v>0</v>
       </c>
       <c r="AF215" s="1" t="s">
         <v>31</v>
@@ -13750,8 +13750,8 @@
       <c r="S216" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="AE216" s="1" t="s">
-        <v>36</v>
+      <c r="AE216" s="1">
+        <v>0</v>
       </c>
       <c r="AF216" s="1" t="s">
         <v>31</v>
@@ -13797,8 +13797,8 @@
       <c r="Y217" s="1" t="s">
         <v>866</v>
       </c>
-      <c r="AE217" s="1" t="s">
-        <v>36</v>
+      <c r="AE217" s="1">
+        <v>0</v>
       </c>
       <c r="AF217" s="1" t="s">
         <v>31</v>
@@ -13838,8 +13838,8 @@
       <c r="S218" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="AE218" s="1" t="s">
-        <v>36</v>
+      <c r="AE218" s="1">
+        <v>0</v>
       </c>
       <c r="AF218" s="1" t="s">
         <v>31</v>
@@ -13882,8 +13882,8 @@
       <c r="S219" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="AE219" s="1" t="s">
-        <v>36</v>
+      <c r="AE219" s="1">
+        <v>0</v>
       </c>
       <c r="AF219" s="1" t="s">
         <v>31</v>
@@ -13923,8 +13923,8 @@
       <c r="S220" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="AE220" s="1" t="s">
-        <v>36</v>
+      <c r="AE220" s="1">
+        <v>0</v>
       </c>
       <c r="AF220" s="1" t="s">
         <v>31</v>
@@ -13967,8 +13967,8 @@
       <c r="S221" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="AE221" s="1" t="s">
-        <v>74</v>
+      <c r="AE221" s="1">
+        <v>1</v>
       </c>
       <c r="AF221" s="1" t="s">
         <v>31</v>
@@ -14015,8 +14015,8 @@
       <c r="AD222" s="8" t="s">
         <v>868</v>
       </c>
-      <c r="AE222" s="1" t="s">
-        <v>36</v>
+      <c r="AE222" s="1">
+        <v>0</v>
       </c>
       <c r="AF222" s="1" t="s">
         <v>31</v>
@@ -14059,8 +14059,8 @@
       <c r="S223" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="AE223" s="1" t="s">
-        <v>36</v>
+      <c r="AE223" s="1">
+        <v>0</v>
       </c>
       <c r="AF223" s="1" t="s">
         <v>31</v>
@@ -14112,8 +14112,8 @@
       <c r="AD224" s="8" t="s">
         <v>886</v>
       </c>
-      <c r="AE224" s="1" t="s">
-        <v>36</v>
+      <c r="AE224" s="1">
+        <v>0</v>
       </c>
       <c r="AF224" s="1" t="s">
         <v>31</v>
@@ -14153,8 +14153,8 @@
       <c r="S225" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="AE225" s="1" t="s">
-        <v>36</v>
+      <c r="AE225" s="1">
+        <v>0</v>
       </c>
       <c r="AF225" s="1" t="s">
         <v>31</v>
@@ -14200,8 +14200,8 @@
       <c r="AD226" s="8" t="s">
         <v>869</v>
       </c>
-      <c r="AE226" s="1" t="s">
-        <v>36</v>
+      <c r="AE226" s="1">
+        <v>0</v>
       </c>
       <c r="AF226" s="1" t="s">
         <v>31</v>
@@ -14247,8 +14247,8 @@
       <c r="S227" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="AE227" s="1" t="s">
-        <v>36</v>
+      <c r="AE227" s="1">
+        <v>0</v>
       </c>
       <c r="AF227" s="1" t="s">
         <v>31</v>
@@ -14303,8 +14303,8 @@
       <c r="Z228" s="8" t="s">
         <v>874</v>
       </c>
-      <c r="AE228" s="1" t="s">
-        <v>36</v>
+      <c r="AE228" s="1">
+        <v>0</v>
       </c>
       <c r="AF228" s="1" t="s">
         <v>31</v>
@@ -14359,8 +14359,8 @@
       <c r="Z229" s="8" t="s">
         <v>874</v>
       </c>
-      <c r="AE229" s="1" t="s">
-        <v>36</v>
+      <c r="AE229" s="1">
+        <v>0</v>
       </c>
       <c r="AF229" s="1" t="s">
         <v>31</v>
@@ -14403,8 +14403,8 @@
       <c r="S230" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="AE230" s="1" t="s">
-        <v>36</v>
+      <c r="AE230" s="1">
+        <v>0</v>
       </c>
       <c r="AF230" s="1" t="s">
         <v>31</v>
@@ -14444,8 +14444,8 @@
       <c r="S231" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="AE231" s="1" t="s">
-        <v>36</v>
+      <c r="AE231" s="1">
+        <v>0</v>
       </c>
       <c r="AF231" s="1" t="s">
         <v>31</v>
@@ -14485,8 +14485,8 @@
       <c r="S232" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="AE232" s="1" t="s">
-        <v>36</v>
+      <c r="AE232" s="1">
+        <v>0</v>
       </c>
       <c r="AF232" s="1" t="s">
         <v>31</v>
@@ -14529,8 +14529,8 @@
       <c r="Y233" s="1" t="s">
         <v>866</v>
       </c>
-      <c r="AE233" s="1" t="s">
-        <v>36</v>
+      <c r="AE233" s="1">
+        <v>0</v>
       </c>
       <c r="AF233" s="1" t="s">
         <v>31</v>
@@ -14573,8 +14573,8 @@
       <c r="S234" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="AE234" s="1" t="s">
-        <v>36</v>
+      <c r="AE234" s="1">
+        <v>0</v>
       </c>
       <c r="AF234" s="1" t="s">
         <v>31</v>
@@ -14614,8 +14614,8 @@
       <c r="S235" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="AE235" s="1" t="s">
-        <v>36</v>
+      <c r="AE235" s="1">
+        <v>0</v>
       </c>
       <c r="AF235" s="1" t="s">
         <v>31</v>
@@ -14658,8 +14658,8 @@
       <c r="S236" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="AE236" s="1" t="s">
-        <v>74</v>
+      <c r="AE236" s="1">
+        <v>1</v>
       </c>
       <c r="AF236" s="1" t="s">
         <v>31</v>
@@ -14699,8 +14699,8 @@
       <c r="S237" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="AE237" s="1" t="s">
-        <v>36</v>
+      <c r="AE237" s="1">
+        <v>0</v>
       </c>
       <c r="AF237" s="1" t="s">
         <v>31</v>
@@ -14746,8 +14746,8 @@
       <c r="Y238" s="1" t="s">
         <v>877</v>
       </c>
-      <c r="AE238" s="1" t="s">
-        <v>36</v>
+      <c r="AE238" s="1">
+        <v>0</v>
       </c>
       <c r="AF238" s="1" t="s">
         <v>31</v>
@@ -14790,8 +14790,8 @@
       <c r="S239" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="AE239" s="1" t="s">
-        <v>36</v>
+      <c r="AE239" s="1">
+        <v>0</v>
       </c>
       <c r="AF239" s="1" t="s">
         <v>31</v>
@@ -14831,8 +14831,8 @@
       <c r="S240" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="AE240" s="1" t="s">
-        <v>36</v>
+      <c r="AE240" s="1">
+        <v>0</v>
       </c>
       <c r="AF240" s="1" t="s">
         <v>31</v>
@@ -14875,8 +14875,8 @@
       <c r="S241" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="AE241" s="1" t="s">
-        <v>74</v>
+      <c r="AE241" s="1">
+        <v>1</v>
       </c>
       <c r="AF241" s="1" t="s">
         <v>31</v>
@@ -14913,8 +14913,8 @@
       <c r="S242" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="AE242" s="1" t="s">
-        <v>36</v>
+      <c r="AE242" s="1">
+        <v>0</v>
       </c>
       <c r="AF242" s="1" t="s">
         <v>31</v>
@@ -14951,8 +14951,8 @@
       <c r="AC243" s="1" t="s">
         <v>879</v>
       </c>
-      <c r="AE243" s="1" t="s">
-        <v>36</v>
+      <c r="AE243" s="1">
+        <v>0</v>
       </c>
       <c r="AF243" s="1" t="s">
         <v>31</v>
@@ -14983,8 +14983,8 @@
       <c r="S244" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="AE244" s="1" t="s">
-        <v>36</v>
+      <c r="AE244" s="1">
+        <v>0</v>
       </c>
       <c r="AF244" s="1" t="s">
         <v>31</v>
@@ -15015,8 +15015,8 @@
       <c r="S245" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="AE245" s="1" t="s">
-        <v>36</v>
+      <c r="AE245" s="1">
+        <v>0</v>
       </c>
       <c r="AF245" s="1" t="s">
         <v>31</v>
@@ -15047,8 +15047,8 @@
       <c r="S246" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="AE246" s="1" t="s">
-        <v>36</v>
+      <c r="AE246" s="1">
+        <v>0</v>
       </c>
       <c r="AF246" s="1" t="s">
         <v>31</v>
@@ -15094,8 +15094,8 @@
       <c r="Z247" s="8" t="s">
         <v>894</v>
       </c>
-      <c r="AE247" s="1" t="s">
-        <v>36</v>
+      <c r="AE247" s="1">
+        <v>0</v>
       </c>
       <c r="AF247" s="1" t="s">
         <v>31</v>
@@ -15141,8 +15141,8 @@
       <c r="Z248" s="8" t="s">
         <v>875</v>
       </c>
-      <c r="AE248" s="1" t="s">
-        <v>36</v>
+      <c r="AE248" s="1">
+        <v>0</v>
       </c>
       <c r="AF248" s="1" t="s">
         <v>634</v>
@@ -15186,8 +15186,8 @@
       <c r="S250" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="AE250" s="1" t="s">
-        <v>36</v>
+      <c r="AE250" s="1">
+        <v>0</v>
       </c>
       <c r="AF250" s="1" t="s">
         <v>31</v>
@@ -15230,8 +15230,8 @@
       <c r="S251" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="AE251" s="1" t="s">
-        <v>36</v>
+      <c r="AE251" s="1">
+        <v>0</v>
       </c>
       <c r="AF251" s="1" t="s">
         <v>31</v>
@@ -15274,8 +15274,8 @@
       <c r="S252" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="AE252" s="1" t="s">
-        <v>36</v>
+      <c r="AE252" s="1">
+        <v>0</v>
       </c>
       <c r="AF252" s="1" t="s">
         <v>31</v>
@@ -15321,8 +15321,8 @@
       <c r="S253" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="AE253" s="1" t="s">
-        <v>36</v>
+      <c r="AE253" s="1">
+        <v>0</v>
       </c>
       <c r="AF253" s="1" t="s">
         <v>31</v>
@@ -15365,8 +15365,8 @@
       <c r="S254" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="AE254" s="1" t="s">
-        <v>36</v>
+      <c r="AE254" s="1">
+        <v>0</v>
       </c>
       <c r="AF254" s="1" t="s">
         <v>31</v>
@@ -15406,8 +15406,8 @@
       <c r="S255" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="AE255" s="1" t="s">
-        <v>36</v>
+      <c r="AE255" s="1">
+        <v>0</v>
       </c>
       <c r="AF255" s="1" t="s">
         <v>31</v>
@@ -15450,8 +15450,8 @@
       <c r="S256" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="AE256" s="1" t="s">
-        <v>36</v>
+      <c r="AE256" s="1">
+        <v>0</v>
       </c>
       <c r="AF256" s="1" t="s">
         <v>31</v>
@@ -15494,8 +15494,8 @@
       <c r="S257" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="AE257" s="1" t="s">
-        <v>36</v>
+      <c r="AE257" s="1">
+        <v>0</v>
       </c>
       <c r="AF257" s="1" t="s">
         <v>31</v>
@@ -15538,8 +15538,8 @@
       <c r="S258" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="AE258" s="1" t="s">
-        <v>36</v>
+      <c r="AE258" s="1">
+        <v>0</v>
       </c>
       <c r="AF258" s="1" t="s">
         <v>31</v>
@@ -15579,8 +15579,8 @@
       <c r="S259" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="AE259" s="1" t="s">
-        <v>36</v>
+      <c r="AE259" s="1">
+        <v>0</v>
       </c>
       <c r="AF259" s="1" t="s">
         <v>31</v>
@@ -15620,8 +15620,8 @@
       <c r="S260" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="AE260" s="1" t="s">
-        <v>36</v>
+      <c r="AE260" s="1">
+        <v>0</v>
       </c>
       <c r="AF260" s="1" t="s">
         <v>31</v>
@@ -15661,8 +15661,8 @@
       <c r="S261" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="AE261" s="1" t="s">
-        <v>36</v>
+      <c r="AE261" s="1">
+        <v>0</v>
       </c>
       <c r="AF261" s="1" t="s">
         <v>31</v>
@@ -15705,8 +15705,8 @@
       <c r="S262" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="AE262" s="1" t="s">
-        <v>36</v>
+      <c r="AE262" s="1">
+        <v>0</v>
       </c>
       <c r="AF262" s="1" t="s">
         <v>31</v>
@@ -15752,8 +15752,8 @@
       <c r="S263" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="AE263" s="1" t="s">
-        <v>36</v>
+      <c r="AE263" s="1">
+        <v>0</v>
       </c>
       <c r="AF263" s="1" t="s">
         <v>31</v>
@@ -15796,8 +15796,8 @@
       <c r="S264" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="AE264" s="1" t="s">
-        <v>36</v>
+      <c r="AE264" s="1">
+        <v>0</v>
       </c>
       <c r="AF264" s="1" t="s">
         <v>31</v>
@@ -15837,8 +15837,8 @@
       <c r="S265" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="AE265" s="1" t="s">
-        <v>36</v>
+      <c r="AE265" s="1">
+        <v>0</v>
       </c>
       <c r="AF265" s="1" t="s">
         <v>31</v>
@@ -15884,8 +15884,8 @@
       <c r="S266" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="AE266" s="1" t="s">
-        <v>36</v>
+      <c r="AE266" s="1">
+        <v>0</v>
       </c>
       <c r="AF266" s="1" t="s">
         <v>31</v>
@@ -15928,8 +15928,8 @@
       <c r="S267" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="AE267" s="1" t="s">
-        <v>36</v>
+      <c r="AE267" s="1">
+        <v>0</v>
       </c>
       <c r="AF267" s="1" t="s">
         <v>31</v>
@@ -15975,8 +15975,8 @@
       <c r="S268" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="AE268" s="1" t="s">
-        <v>36</v>
+      <c r="AE268" s="1">
+        <v>0</v>
       </c>
       <c r="AF268" s="1" t="s">
         <v>31</v>
@@ -16019,8 +16019,8 @@
       <c r="S269" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="AE269" s="1" t="s">
-        <v>36</v>
+      <c r="AE269" s="1">
+        <v>0</v>
       </c>
       <c r="AF269" s="1" t="s">
         <v>31</v>
@@ -16066,8 +16066,8 @@
       <c r="S270" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="AE270" s="1" t="s">
-        <v>36</v>
+      <c r="AE270" s="1">
+        <v>0</v>
       </c>
       <c r="AF270" s="1" t="s">
         <v>31</v>
@@ -16110,8 +16110,8 @@
       <c r="S271" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="AE271" s="1" t="s">
-        <v>36</v>
+      <c r="AE271" s="1">
+        <v>0</v>
       </c>
       <c r="AF271" s="1" t="s">
         <v>31</v>
@@ -16154,8 +16154,8 @@
       <c r="S272" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="AE272" s="1" t="s">
-        <v>36</v>
+      <c r="AE272" s="1">
+        <v>0</v>
       </c>
       <c r="AF272" s="1" t="s">
         <v>31</v>
@@ -16198,8 +16198,8 @@
       <c r="S273" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="AE273" s="1" t="s">
-        <v>36</v>
+      <c r="AE273" s="1">
+        <v>0</v>
       </c>
       <c r="AF273" s="1" t="s">
         <v>31</v>
@@ -16242,8 +16242,8 @@
       <c r="S274" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="AE274" s="1" t="s">
-        <v>36</v>
+      <c r="AE274" s="1">
+        <v>0</v>
       </c>
       <c r="AF274" s="1" t="s">
         <v>31</v>
@@ -16286,8 +16286,8 @@
       <c r="S275" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="AE275" s="1" t="s">
-        <v>36</v>
+      <c r="AE275" s="1">
+        <v>0</v>
       </c>
       <c r="AF275" s="1" t="s">
         <v>31</v>
@@ -16330,8 +16330,8 @@
       <c r="S276" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="AE276" s="1" t="s">
-        <v>36</v>
+      <c r="AE276" s="1">
+        <v>0</v>
       </c>
       <c r="AF276" s="1" t="s">
         <v>31</v>
@@ -16371,8 +16371,8 @@
       <c r="S277" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="AE277" s="1" t="s">
-        <v>36</v>
+      <c r="AE277" s="1">
+        <v>0</v>
       </c>
       <c r="AF277" s="1" t="s">
         <v>31</v>
@@ -16412,8 +16412,8 @@
       <c r="S278" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="AE278" s="1" t="s">
-        <v>36</v>
+      <c r="AE278" s="1">
+        <v>0</v>
       </c>
       <c r="AF278" s="1" t="s">
         <v>31</v>
@@ -16456,8 +16456,8 @@
       <c r="S279" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="AE279" s="1" t="s">
-        <v>36</v>
+      <c r="AE279" s="1">
+        <v>0</v>
       </c>
       <c r="AF279" s="1" t="s">
         <v>31</v>
@@ -16500,8 +16500,8 @@
       <c r="S280" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="AE280" s="1" t="s">
-        <v>36</v>
+      <c r="AE280" s="1">
+        <v>0</v>
       </c>
       <c r="AF280" s="1" t="s">
         <v>31</v>
@@ -16544,8 +16544,8 @@
       <c r="S281" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="AE281" s="1" t="s">
-        <v>36</v>
+      <c r="AE281" s="1">
+        <v>0</v>
       </c>
       <c r="AF281" s="1" t="s">
         <v>31</v>
@@ -16588,8 +16588,8 @@
       <c r="S282" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="AE282" s="1" t="s">
-        <v>36</v>
+      <c r="AE282" s="1">
+        <v>0</v>
       </c>
       <c r="AF282" s="1" t="s">
         <v>31</v>
@@ -16635,8 +16635,8 @@
       <c r="S283" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="AE283" s="1" t="s">
-        <v>36</v>
+      <c r="AE283" s="1">
+        <v>0</v>
       </c>
       <c r="AF283" s="1" t="s">
         <v>31</v>
@@ -16676,8 +16676,8 @@
       <c r="S284" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="AE284" s="1" t="s">
-        <v>36</v>
+      <c r="AE284" s="1">
+        <v>0</v>
       </c>
       <c r="AF284" s="1" t="s">
         <v>31</v>
@@ -16717,8 +16717,8 @@
       <c r="S285" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="AE285" s="1" t="s">
-        <v>36</v>
+      <c r="AE285" s="1">
+        <v>0</v>
       </c>
       <c r="AF285" s="1" t="s">
         <v>31</v>
@@ -16758,8 +16758,8 @@
       <c r="S286" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="AE286" s="1" t="s">
-        <v>36</v>
+      <c r="AE286" s="1">
+        <v>0</v>
       </c>
       <c r="AF286" s="1" t="s">
         <v>31</v>
@@ -16799,8 +16799,8 @@
       <c r="S287" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="AE287" s="1" t="s">
-        <v>36</v>
+      <c r="AE287" s="1">
+        <v>0</v>
       </c>
       <c r="AF287" s="1" t="s">
         <v>31</v>
@@ -16840,8 +16840,8 @@
       <c r="S288" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="AE288" s="1" t="s">
-        <v>36</v>
+      <c r="AE288" s="1">
+        <v>0</v>
       </c>
       <c r="AF288" s="1" t="s">
         <v>31</v>
@@ -16881,8 +16881,8 @@
       <c r="S289" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="AE289" s="1" t="s">
-        <v>36</v>
+      <c r="AE289" s="1">
+        <v>0</v>
       </c>
       <c r="AF289" s="1" t="s">
         <v>31</v>
@@ -16928,8 +16928,8 @@
       <c r="S290" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="AE290" s="1" t="s">
-        <v>36</v>
+      <c r="AE290" s="1">
+        <v>0</v>
       </c>
       <c r="AF290" s="1" t="s">
         <v>31</v>
@@ -16972,8 +16972,8 @@
       <c r="S291" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="AE291" s="1" t="s">
-        <v>36</v>
+      <c r="AE291" s="1">
+        <v>0</v>
       </c>
       <c r="AF291" s="1" t="s">
         <v>31</v>
@@ -17010,8 +17010,8 @@
       <c r="S292" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="AE292" s="1" t="s">
-        <v>36</v>
+      <c r="AE292" s="1">
+        <v>0</v>
       </c>
       <c r="AF292" s="1" t="s">
         <v>31</v>
@@ -17051,8 +17051,8 @@
       <c r="S293" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="AE293" s="1" t="s">
-        <v>36</v>
+      <c r="AE293" s="1">
+        <v>0</v>
       </c>
       <c r="AF293" s="1" t="s">
         <v>31</v>
@@ -17092,8 +17092,8 @@
       <c r="S294" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="AE294" s="1" t="s">
-        <v>36</v>
+      <c r="AE294" s="1">
+        <v>0</v>
       </c>
       <c r="AF294" s="1" t="s">
         <v>31</v>
@@ -17136,8 +17136,8 @@
       <c r="S295" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="AE295" s="1" t="s">
-        <v>36</v>
+      <c r="AE295" s="1">
+        <v>0</v>
       </c>
       <c r="AF295" s="1" t="s">
         <v>31</v>
@@ -17183,8 +17183,8 @@
       <c r="S296" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="AE296" s="1" t="s">
-        <v>36</v>
+      <c r="AE296" s="1">
+        <v>0</v>
       </c>
       <c r="AF296" s="1" t="s">
         <v>31</v>
@@ -17218,8 +17218,8 @@
       <c r="S297" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="AE297" s="1" t="s">
-        <v>36</v>
+      <c r="AE297" s="1">
+        <v>0</v>
       </c>
       <c r="AF297" s="1" t="s">
         <v>31</v>
@@ -17256,8 +17256,8 @@
       <c r="S298" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="AE298" s="1" t="s">
-        <v>36</v>
+      <c r="AE298" s="1">
+        <v>0</v>
       </c>
       <c r="AF298" s="1" t="s">
         <v>31</v>
@@ -17294,8 +17294,8 @@
       <c r="S299" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="AE299" s="1" t="s">
-        <v>36</v>
+      <c r="AE299" s="1">
+        <v>0</v>
       </c>
       <c r="AF299" s="1" t="s">
         <v>31</v>
@@ -17332,8 +17332,8 @@
       <c r="S300" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="AE300" s="1" t="s">
-        <v>36</v>
+      <c r="AE300" s="1">
+        <v>0</v>
       </c>
       <c r="AF300" s="1" t="s">
         <v>31</v>
@@ -17376,8 +17376,8 @@
       <c r="S301" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="AE301" s="1" t="s">
-        <v>36</v>
+      <c r="AE301" s="1">
+        <v>0</v>
       </c>
       <c r="AF301" s="1" t="s">
         <v>31</v>
@@ -17420,8 +17420,8 @@
       <c r="S302" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="AE302" s="1" t="s">
-        <v>36</v>
+      <c r="AE302" s="1">
+        <v>0</v>
       </c>
       <c r="AF302" s="1" t="s">
         <v>31</v>
@@ -17464,8 +17464,8 @@
       <c r="S303" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="AE303" s="1" t="s">
-        <v>36</v>
+      <c r="AE303" s="1">
+        <v>0</v>
       </c>
       <c r="AF303" s="1" t="s">
         <v>31</v>
@@ -17508,8 +17508,8 @@
       <c r="S304" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="AE304" s="1" t="s">
-        <v>36</v>
+      <c r="AE304" s="1">
+        <v>0</v>
       </c>
       <c r="AF304" s="1" t="s">
         <v>31</v>
@@ -17552,8 +17552,8 @@
       <c r="S305" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="AE305" s="1" t="s">
-        <v>36</v>
+      <c r="AE305" s="1">
+        <v>0</v>
       </c>
       <c r="AF305" s="1" t="s">
         <v>31</v>
@@ -17596,8 +17596,8 @@
       <c r="S306" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="AE306" s="1" t="s">
-        <v>36</v>
+      <c r="AE306" s="1">
+        <v>0</v>
       </c>
       <c r="AF306" s="1" t="s">
         <v>31</v>
@@ -17637,8 +17637,8 @@
       <c r="S307" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="AE307" s="1" t="s">
-        <v>36</v>
+      <c r="AE307" s="1">
+        <v>0</v>
       </c>
       <c r="AF307" s="1" t="s">
         <v>31</v>
@@ -17678,8 +17678,8 @@
       <c r="S308" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="AE308" s="1" t="s">
-        <v>36</v>
+      <c r="AE308" s="1">
+        <v>0</v>
       </c>
       <c r="AF308" s="1" t="s">
         <v>31</v>
@@ -17713,8 +17713,8 @@
       <c r="S309" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="AE309" s="1" t="s">
-        <v>36</v>
+      <c r="AE309" s="1">
+        <v>0</v>
       </c>
       <c r="AF309" s="1" t="s">
         <v>31</v>
@@ -17748,8 +17748,8 @@
       <c r="S310" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="AE310" s="1" t="s">
-        <v>36</v>
+      <c r="AE310" s="1">
+        <v>0</v>
       </c>
       <c r="AF310" s="1" t="s">
         <v>31</v>
@@ -17789,8 +17789,8 @@
       <c r="S311" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="AE311" s="1" t="s">
-        <v>36</v>
+      <c r="AE311" s="1">
+        <v>0</v>
       </c>
       <c r="AF311" s="1" t="s">
         <v>31</v>
@@ -17830,8 +17830,8 @@
       <c r="S312" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="AE312" s="1" t="s">
-        <v>36</v>
+      <c r="AE312" s="1">
+        <v>0</v>
       </c>
       <c r="AF312" s="1" t="s">
         <v>31</v>
@@ -17871,8 +17871,8 @@
       <c r="S313" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="AE313" s="1" t="s">
-        <v>36</v>
+      <c r="AE313" s="1">
+        <v>0</v>
       </c>
       <c r="AF313" s="1" t="s">
         <v>31</v>
@@ -17912,8 +17912,8 @@
       <c r="S314" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="AE314" s="1" t="s">
-        <v>36</v>
+      <c r="AE314" s="1">
+        <v>0</v>
       </c>
       <c r="AF314" s="1" t="s">
         <v>31</v>
@@ -17956,8 +17956,8 @@
       <c r="S315" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="AE315" s="1" t="s">
-        <v>36</v>
+      <c r="AE315" s="1">
+        <v>0</v>
       </c>
       <c r="AF315" s="1" t="s">
         <v>31</v>
@@ -18000,8 +18000,8 @@
       <c r="S316" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="AE316" s="1" t="s">
-        <v>36</v>
+      <c r="AE316" s="1">
+        <v>0</v>
       </c>
       <c r="AF316" s="1" t="s">
         <v>31</v>
@@ -18044,8 +18044,8 @@
       <c r="S317" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="AE317" s="1" t="s">
-        <v>36</v>
+      <c r="AE317" s="1">
+        <v>0</v>
       </c>
       <c r="AF317" s="1" t="s">
         <v>31</v>
@@ -18088,8 +18088,8 @@
       <c r="S318" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="AE318" s="1" t="s">
-        <v>36</v>
+      <c r="AE318" s="1">
+        <v>0</v>
       </c>
       <c r="AF318" s="1" t="s">
         <v>31</v>
@@ -18129,8 +18129,8 @@
       <c r="S319" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="AE319" s="1" t="s">
-        <v>36</v>
+      <c r="AE319" s="1">
+        <v>0</v>
       </c>
       <c r="AF319" s="1" t="s">
         <v>31</v>
@@ -18170,8 +18170,8 @@
       <c r="S320" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="AE320" s="1" t="s">
-        <v>36</v>
+      <c r="AE320" s="1">
+        <v>0</v>
       </c>
       <c r="AF320" s="1" t="s">
         <v>31</v>
@@ -18211,8 +18211,8 @@
       <c r="S321" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="AE321" s="1" t="s">
-        <v>36</v>
+      <c r="AE321" s="1">
+        <v>0</v>
       </c>
       <c r="AF321" s="1" t="s">
         <v>31</v>
@@ -18261,8 +18261,8 @@
       <c r="S322" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="AE322" s="1" t="s">
-        <v>36</v>
+      <c r="AE322" s="1">
+        <v>0</v>
       </c>
       <c r="AF322" s="1" t="s">
         <v>31</v>
@@ -18299,8 +18299,8 @@
       <c r="S323" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="AE323" s="1" t="s">
-        <v>36</v>
+      <c r="AE323" s="1">
+        <v>0</v>
       </c>
       <c r="AF323" s="1" t="s">
         <v>31</v>
@@ -18340,8 +18340,8 @@
       <c r="S324" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="AE324" s="1" t="s">
-        <v>36</v>
+      <c r="AE324" s="1">
+        <v>0</v>
       </c>
       <c r="AF324" s="1" t="s">
         <v>31</v>
@@ -18381,8 +18381,8 @@
       <c r="S325" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="AE325" s="1" t="s">
-        <v>36</v>
+      <c r="AE325" s="1">
+        <v>0</v>
       </c>
       <c r="AF325" s="1" t="s">
         <v>31</v>
@@ -18416,8 +18416,8 @@
       <c r="S326" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="AE326" s="1" t="s">
-        <v>36</v>
+      <c r="AE326" s="1">
+        <v>0</v>
       </c>
       <c r="AF326" s="1" t="s">
         <v>31</v>
@@ -18451,8 +18451,8 @@
       <c r="S327" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="AE327" s="1" t="s">
-        <v>36</v>
+      <c r="AE327" s="1">
+        <v>0</v>
       </c>
       <c r="AF327" s="1" t="s">
         <v>31</v>
@@ -18492,8 +18492,8 @@
       <c r="S328" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="AE328" s="1" t="s">
-        <v>36</v>
+      <c r="AE328" s="1">
+        <v>0</v>
       </c>
       <c r="AF328" s="1" t="s">
         <v>31</v>
@@ -18527,8 +18527,8 @@
       <c r="S329" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="AE329" s="1" t="s">
-        <v>36</v>
+      <c r="AE329" s="1">
+        <v>0</v>
       </c>
       <c r="AF329" s="1" t="s">
         <v>31</v>
@@ -18562,8 +18562,8 @@
       <c r="S330" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="AE330" s="1" t="s">
-        <v>36</v>
+      <c r="AE330" s="1">
+        <v>0</v>
       </c>
       <c r="AF330" s="1" t="s">
         <v>31</v>
@@ -18597,8 +18597,8 @@
       <c r="S331" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="AE331" s="1" t="s">
-        <v>36</v>
+      <c r="AE331" s="1">
+        <v>0</v>
       </c>
       <c r="AF331" s="1" t="s">
         <v>31</v>
@@ -18632,8 +18632,8 @@
       <c r="S332" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="AE332" s="1" t="s">
-        <v>36</v>
+      <c r="AE332" s="1">
+        <v>0</v>
       </c>
       <c r="AF332" s="1" t="s">
         <v>31</v>
@@ -18679,8 +18679,8 @@
       <c r="S333" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="AE333" s="1" t="s">
-        <v>36</v>
+      <c r="AE333" s="1">
+        <v>0</v>
       </c>
       <c r="AF333" s="1" t="s">
         <v>31</v>

--- a/Luban/Config/Datas/#BattleSkillConfig.xlsx
+++ b/Luban/Config/Datas/#BattleSkillConfig.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Project\Return0\Luban\Config\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{479ED86E-8344-4A87-8C3F-A645C957E437}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B5BE8A27-41DC-41C7-A7E7-C5E4F24E6CDE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="38280" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{53B3FBB6-B116-408D-BCC0-737AAAC6C9D0}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{53B3FBB6-B116-408D-BCC0-737AAAC6C9D0}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -74,7 +74,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4059" uniqueCount="889">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4338" uniqueCount="1168">
   <si>
     <t>##var</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -2884,343 +2884,1137 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
+    <t>SkillPreUseData1010</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SkillPreUseData1011</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3093</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>StatusPersists</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>GainStatusPersists</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>是否不影响状态的续存</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>是否不影响增益状态的续存</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>行动期间不受异常状态的影响</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>NotBeAbnormalBuffEffect</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3024</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SkillWellyEffect</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>20341,2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>4014</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>破防增加比率</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>BreakDefendAddRate</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>IsPctCost</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>炁拶</t>
+  </si>
+  <si>
+    <t>IsNeedTarget</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>是否需要目标</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Faction</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>派系</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2070</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>72008,20061,0.25</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.15,20,20</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>20081,3</t>
+  </si>
+  <si>
+    <t>0.5,50</t>
+  </si>
+  <si>
+    <t>20081,30381</t>
+  </si>
+  <si>
+    <t>5,1,1,5,1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>160,32</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1,35,2,35</t>
+  </si>
+  <si>
+    <t>3046</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3056</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3079</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>4021</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>4074</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>WellyRateBase</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>脚本</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>预先使用数据脚本</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Skill1011</t>
+  </si>
+  <si>
+    <t>Skill1001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Skill1002</t>
+  </si>
+  <si>
+    <t>Skill1003</t>
+  </si>
+  <si>
+    <t>Skill1004</t>
+  </si>
+  <si>
+    <t>Skill1005</t>
+  </si>
+  <si>
+    <t>Skill1006</t>
+  </si>
+  <si>
+    <t>Skill1007</t>
+  </si>
+  <si>
+    <t>Skill1008</t>
+  </si>
+  <si>
+    <t>Skill1009</t>
+  </si>
+  <si>
+    <t>Skill1012</t>
+  </si>
+  <si>
+    <t>Skill1013</t>
+  </si>
+  <si>
+    <t>Skill1014</t>
+  </si>
+  <si>
+    <t>Skill1015</t>
+  </si>
+  <si>
+    <t>Skill1016</t>
+  </si>
+  <si>
+    <t>Skill1017</t>
+  </si>
+  <si>
+    <t>Skill1018</t>
+  </si>
+  <si>
+    <t>Skill1019</t>
+  </si>
+  <si>
+    <t>Skill1020</t>
+  </si>
+  <si>
+    <t>Skill1021</t>
+  </si>
+  <si>
+    <t>Skill1022</t>
+  </si>
+  <si>
+    <t>Skill1023</t>
+  </si>
+  <si>
+    <t>Skill1024</t>
+  </si>
+  <si>
+    <t>Skill1025</t>
+  </si>
+  <si>
+    <t>Skill1026</t>
+  </si>
+  <si>
+    <t>Skill1027</t>
+  </si>
+  <si>
+    <t>Skill1028</t>
+  </si>
+  <si>
+    <t>Skill1029</t>
+  </si>
+  <si>
+    <t>Skill1030</t>
+  </si>
+  <si>
+    <t>Skill1031</t>
+  </si>
+  <si>
+    <t>Skill1032</t>
+  </si>
+  <si>
+    <t>Skill1033</t>
+  </si>
+  <si>
+    <t>Skill1034</t>
+  </si>
+  <si>
+    <t>Skill1035</t>
+  </si>
+  <si>
+    <t>Skill1036</t>
+  </si>
+  <si>
+    <t>Skill1038</t>
+  </si>
+  <si>
+    <t>Skill1040</t>
+  </si>
+  <si>
+    <t>Skill1041</t>
+  </si>
+  <si>
+    <t>Skill1042</t>
+  </si>
+  <si>
+    <t>Skill1043</t>
+  </si>
+  <si>
+    <t>Skill1044</t>
+  </si>
+  <si>
+    <t>Skill1045</t>
+  </si>
+  <si>
+    <t>Skill1046</t>
+  </si>
+  <si>
+    <t>Skill1010</t>
+  </si>
+  <si>
+    <t>Skill1037</t>
+  </si>
+  <si>
+    <t>Skill1039</t>
+  </si>
+  <si>
+    <t>Skill1047</t>
+  </si>
+  <si>
+    <t>Skill1048</t>
+  </si>
+  <si>
+    <t>Skill1049</t>
+  </si>
+  <si>
+    <t>Skill1050</t>
+  </si>
+  <si>
+    <t>Skill1051</t>
+  </si>
+  <si>
+    <t>Skill1052</t>
+  </si>
+  <si>
+    <t>Skill1053</t>
+  </si>
+  <si>
+    <t>Skill2001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Skill2002</t>
+  </si>
+  <si>
+    <t>Skill2003</t>
+  </si>
+  <si>
+    <t>Skill2004</t>
+  </si>
+  <si>
+    <t>Skill2005</t>
+  </si>
+  <si>
+    <t>Skill2006</t>
+  </si>
+  <si>
+    <t>Skill2007</t>
+  </si>
+  <si>
+    <t>Skill2008</t>
+  </si>
+  <si>
+    <t>Skill2009</t>
+  </si>
+  <si>
+    <t>Skill2010</t>
+  </si>
+  <si>
+    <t>Skill2011</t>
+  </si>
+  <si>
+    <t>Skill2012</t>
+  </si>
+  <si>
+    <t>Skill2013</t>
+  </si>
+  <si>
+    <t>Skill2014</t>
+  </si>
+  <si>
+    <t>Skill2015</t>
+  </si>
+  <si>
+    <t>Skill2016</t>
+  </si>
+  <si>
+    <t>Skill2017</t>
+  </si>
+  <si>
+    <t>Skill2018</t>
+  </si>
+  <si>
+    <t>Skill2019</t>
+  </si>
+  <si>
+    <t>Skill2020</t>
+  </si>
+  <si>
+    <t>Skill2021</t>
+  </si>
+  <si>
+    <t>Skill2022</t>
+  </si>
+  <si>
+    <t>Skill2023</t>
+  </si>
+  <si>
+    <t>Skill2024</t>
+  </si>
+  <si>
+    <t>Skill2025</t>
+  </si>
+  <si>
+    <t>Skill2026</t>
+  </si>
+  <si>
+    <t>Skill2027</t>
+  </si>
+  <si>
+    <t>Skill2028</t>
+  </si>
+  <si>
+    <t>Skill2029</t>
+  </si>
+  <si>
+    <t>Skill2030</t>
+  </si>
+  <si>
+    <t>Skill2031</t>
+  </si>
+  <si>
     <t>Skill2032</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>Skill2033</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>Skill2034</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Skill1010</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Skill1011</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Skill2009</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>SkillPreUseData1010</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>SkillPreUseData1011</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Skill2028</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Skill2030</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Skill2035</t>
+  </si>
+  <si>
+    <t>Skill2036</t>
+  </si>
+  <si>
+    <t>Skill2037</t>
+  </si>
+  <si>
+    <t>Skill2038</t>
+  </si>
+  <si>
+    <t>Skill2039</t>
+  </si>
+  <si>
+    <t>Skill2040</t>
+  </si>
+  <si>
+    <t>Skill2041</t>
+  </si>
+  <si>
+    <t>Skill2042</t>
+  </si>
+  <si>
+    <t>Skill2043</t>
+  </si>
+  <si>
+    <t>Skill2044</t>
+  </si>
+  <si>
+    <t>Skill2045</t>
+  </si>
+  <si>
+    <t>Skill2046</t>
+  </si>
+  <si>
+    <t>Skill2047</t>
+  </si>
+  <si>
+    <t>Skill2048</t>
+  </si>
+  <si>
+    <t>Skill2049</t>
+  </si>
+  <si>
+    <t>Skill2050</t>
+  </si>
+  <si>
+    <t>Skill2051</t>
+  </si>
+  <si>
+    <t>Skill2052</t>
+  </si>
+  <si>
+    <t>Skill2053</t>
+  </si>
+  <si>
+    <t>Skill2054</t>
+  </si>
+  <si>
+    <t>Skill2055</t>
+  </si>
+  <si>
+    <t>Skill2056</t>
+  </si>
+  <si>
+    <t>Skill2057</t>
+  </si>
+  <si>
+    <t>Skill2058</t>
+  </si>
+  <si>
+    <t>Skill2059</t>
+  </si>
+  <si>
+    <t>Skill2060</t>
+  </si>
+  <si>
+    <t>Skill2061</t>
+  </si>
+  <si>
+    <t>Skill2062</t>
+  </si>
+  <si>
+    <t>Skill2063</t>
+  </si>
+  <si>
+    <t>Skill2064</t>
+  </si>
+  <si>
+    <t>Skill2065</t>
+  </si>
+  <si>
+    <t>Skill2066</t>
+  </si>
+  <si>
+    <t>Skill2067</t>
+  </si>
+  <si>
+    <t>Skill2068</t>
+  </si>
+  <si>
+    <t>Skill2069</t>
+  </si>
+  <si>
+    <t>Skill2070</t>
+  </si>
+  <si>
+    <t>Skill2071</t>
+  </si>
+  <si>
+    <t>Skill2072</t>
+  </si>
+  <si>
+    <t>Skill2073</t>
+  </si>
+  <si>
+    <t>Skill2074</t>
+  </si>
+  <si>
+    <t>Skill2075</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Skill3001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Skill3002</t>
+  </si>
+  <si>
+    <t>Skill3003</t>
+  </si>
+  <si>
+    <t>Skill3004</t>
+  </si>
+  <si>
+    <t>Skill3005</t>
+  </si>
+  <si>
+    <t>Skill3006</t>
+  </si>
+  <si>
+    <t>Skill3007</t>
+  </si>
+  <si>
+    <t>Skill3008</t>
+  </si>
+  <si>
+    <t>Skill3009</t>
+  </si>
+  <si>
+    <t>Skill3010</t>
+  </si>
+  <si>
+    <t>Skill3011</t>
+  </si>
+  <si>
+    <t>Skill3012</t>
+  </si>
+  <si>
+    <t>Skill3013</t>
+  </si>
+  <si>
+    <t>Skill3014</t>
+  </si>
+  <si>
+    <t>Skill3015</t>
+  </si>
+  <si>
+    <t>Skill3016</t>
+  </si>
+  <si>
+    <t>Skill3017</t>
+  </si>
+  <si>
+    <t>Skill3018</t>
+  </si>
+  <si>
+    <t>Skill3019</t>
+  </si>
+  <si>
+    <t>Skill3020</t>
+  </si>
+  <si>
+    <t>Skill3021</t>
+  </si>
+  <si>
+    <t>Skill3022</t>
+  </si>
+  <si>
+    <t>Skill3023</t>
+  </si>
+  <si>
+    <t>Skill3024</t>
+  </si>
+  <si>
+    <t>Skill3025</t>
+  </si>
+  <si>
+    <t>Skill3026</t>
+  </si>
+  <si>
+    <t>Skill3027</t>
+  </si>
+  <si>
+    <t>Skill3028</t>
+  </si>
+  <si>
+    <t>Skill3029</t>
+  </si>
+  <si>
+    <t>Skill3030</t>
+  </si>
+  <si>
+    <t>Skill3031</t>
+  </si>
+  <si>
+    <t>Skill3032</t>
+  </si>
+  <si>
+    <t>Skill3033</t>
+  </si>
+  <si>
+    <t>Skill3034</t>
+  </si>
+  <si>
+    <t>Skill3035</t>
+  </si>
+  <si>
+    <t>Skill3036</t>
+  </si>
+  <si>
+    <t>Skill3037</t>
+  </si>
+  <si>
+    <t>Skill3038</t>
+  </si>
+  <si>
+    <t>Skill3039</t>
+  </si>
+  <si>
+    <t>Skill3040</t>
+  </si>
+  <si>
+    <t>Skill3041</t>
+  </si>
+  <si>
+    <t>Skill3042</t>
+  </si>
+  <si>
+    <t>Skill3043</t>
+  </si>
+  <si>
+    <t>Skill3044</t>
+  </si>
+  <si>
+    <t>Skill3045</t>
+  </si>
+  <si>
+    <t>Skill3046</t>
+  </si>
+  <si>
+    <t>Skill3047</t>
+  </si>
+  <si>
+    <t>Skill3048</t>
+  </si>
+  <si>
+    <t>Skill3049</t>
+  </si>
+  <si>
+    <t>Skill3050</t>
+  </si>
+  <si>
+    <t>Skill3051</t>
+  </si>
+  <si>
+    <t>Skill3052</t>
+  </si>
+  <si>
+    <t>Skill3053</t>
+  </si>
+  <si>
+    <t>Skill3054</t>
+  </si>
+  <si>
+    <t>Skill3055</t>
+  </si>
+  <si>
+    <t>Skill3056</t>
+  </si>
+  <si>
+    <t>Skill3057</t>
+  </si>
+  <si>
+    <t>Skill3058</t>
+  </si>
+  <si>
+    <t>Skill3059</t>
+  </si>
+  <si>
+    <t>Skill3060</t>
+  </si>
+  <si>
+    <t>Skill3061</t>
+  </si>
+  <si>
+    <t>Skill3062</t>
+  </si>
+  <si>
+    <t>Skill3063</t>
+  </si>
+  <si>
+    <t>Skill3064</t>
+  </si>
+  <si>
+    <t>Skill3065</t>
+  </si>
+  <si>
+    <t>Skill3066</t>
+  </si>
+  <si>
+    <t>Skill3067</t>
+  </si>
+  <si>
+    <t>Skill3068</t>
+  </si>
+  <si>
+    <t>Skill3069</t>
+  </si>
+  <si>
+    <t>Skill3070</t>
+  </si>
+  <si>
+    <t>Skill3071</t>
+  </si>
+  <si>
+    <t>Skill3072</t>
+  </si>
+  <si>
+    <t>Skill3073</t>
+  </si>
+  <si>
+    <t>Skill3074</t>
+  </si>
+  <si>
+    <t>Skill3075</t>
+  </si>
+  <si>
+    <t>Skill3076</t>
+  </si>
+  <si>
+    <t>Skill3077</t>
+  </si>
+  <si>
+    <t>Skill3078</t>
+  </si>
+  <si>
+    <t>Skill3079</t>
+  </si>
+  <si>
+    <t>Skill3080</t>
+  </si>
+  <si>
+    <t>Skill3081</t>
+  </si>
+  <si>
+    <t>Skill3082</t>
+  </si>
+  <si>
+    <t>Skill3083</t>
   </si>
   <si>
     <t>Skill3084</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Skill3085</t>
+  </si>
+  <si>
+    <t>Skill3086</t>
+  </si>
+  <si>
+    <t>Skill3087</t>
+  </si>
+  <si>
+    <t>Skill3088</t>
   </si>
   <si>
     <t>Skill3089</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Skill3090</t>
+  </si>
+  <si>
+    <t>Skill3091</t>
+  </si>
+  <si>
+    <t>Skill3092</t>
   </si>
   <si>
     <t>Skill3093</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>3093</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Skill3094</t>
+  </si>
+  <si>
+    <t>Skill3095</t>
+  </si>
+  <si>
+    <t>Skill3096</t>
+  </si>
+  <si>
+    <t>Skill3097</t>
+  </si>
+  <si>
+    <t>Skill3098</t>
+  </si>
+  <si>
+    <t>Skill3099</t>
+  </si>
+  <si>
+    <t>Skill3100</t>
+  </si>
+  <si>
+    <t>Skill3101</t>
+  </si>
+  <si>
+    <t>Skill3102</t>
+  </si>
+  <si>
+    <t>Skill3103</t>
+  </si>
+  <si>
+    <t>Skill3104</t>
   </si>
   <si>
     <t>Skill3105</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Skill3021</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Skill3020</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>StatusPersists</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>GainStatusPersists</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>是否不影响状态的续存</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>是否不影响增益状态的续存</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>行动期间不受异常状态的影响</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>NotBeAbnormalBuffEffect</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Skill3044</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Skill3045</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Skill2067</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Skill3094</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Skill1037</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Skill1047</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Skill2026</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Skill2027</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Skill2029</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Skill3009</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Skill3034</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Skill3040</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Skill3051</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Skill3064</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Skill3086</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Skill3088</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Skill3101</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Skill3103</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>Skill3106</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Skill3107</t>
   </si>
   <si>
     <t>Skill3108</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Skill3109</t>
+  </si>
+  <si>
+    <t>Skill3110</t>
+  </si>
+  <si>
+    <t>Skill3111</t>
+  </si>
+  <si>
+    <t>Skill3112</t>
+  </si>
+  <si>
+    <t>Skill3113</t>
+  </si>
+  <si>
+    <t>Skill3114</t>
+  </si>
+  <si>
+    <t>Skill3115</t>
+  </si>
+  <si>
+    <t>Skill4001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Skill4002</t>
+  </si>
+  <si>
+    <t>Skill4003</t>
+  </si>
+  <si>
+    <t>Skill4004</t>
+  </si>
+  <si>
+    <t>Skill4005</t>
+  </si>
+  <si>
+    <t>Skill4006</t>
+  </si>
+  <si>
+    <t>Skill4007</t>
+  </si>
+  <si>
+    <t>Skill4008</t>
+  </si>
+  <si>
+    <t>Skill4009</t>
+  </si>
+  <si>
+    <t>Skill4010</t>
+  </si>
+  <si>
+    <t>Skill4011</t>
+  </si>
+  <si>
+    <t>Skill4012</t>
+  </si>
+  <si>
+    <t>Skill4013</t>
+  </si>
+  <si>
+    <t>Skill4014</t>
+  </si>
+  <si>
+    <t>Skill4015</t>
+  </si>
+  <si>
+    <t>Skill4016</t>
+  </si>
+  <si>
+    <t>Skill4017</t>
+  </si>
+  <si>
+    <t>Skill4018</t>
+  </si>
+  <si>
+    <t>Skill4019</t>
+  </si>
+  <si>
+    <t>Skill4020</t>
+  </si>
+  <si>
+    <t>Skill4021</t>
+  </si>
+  <si>
+    <t>Skill4022</t>
+  </si>
+  <si>
+    <t>Skill4023</t>
+  </si>
+  <si>
+    <t>Skill4024</t>
+  </si>
+  <si>
+    <t>Skill4025</t>
+  </si>
+  <si>
+    <t>Skill4026</t>
+  </si>
+  <si>
+    <t>Skill4027</t>
+  </si>
+  <si>
+    <t>Skill4028</t>
+  </si>
+  <si>
+    <t>Skill4029</t>
+  </si>
+  <si>
+    <t>Skill4030</t>
+  </si>
+  <si>
+    <t>Skill4031</t>
+  </si>
+  <si>
+    <t>Skill4032</t>
+  </si>
+  <si>
+    <t>Skill4033</t>
   </si>
   <si>
     <t>Skill4034</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Skill4035</t>
+  </si>
+  <si>
+    <t>Skill4036</t>
+  </si>
+  <si>
+    <t>Skill4037</t>
+  </si>
+  <si>
+    <t>Skill4038</t>
+  </si>
+  <si>
+    <t>Skill4039</t>
+  </si>
+  <si>
+    <t>Skill4040</t>
+  </si>
+  <si>
+    <t>Skill4041</t>
+  </si>
+  <si>
+    <t>Skill4042</t>
+  </si>
+  <si>
+    <t>Skill4043</t>
+  </si>
+  <si>
+    <t>Skill4044</t>
+  </si>
+  <si>
+    <t>Skill4045</t>
+  </si>
+  <si>
+    <t>Skill4046</t>
   </si>
   <si>
     <t>Skill4047</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>3024</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>SkillWellyEffect</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Skill1039</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>20341,2</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>4014</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>破防增加比率</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>BreakDefendAddRate</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>IsPctCost</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>炁拶</t>
-  </si>
-  <si>
-    <t>IsNeedTarget</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>是否需要目标</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Faction</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>派系</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>2070</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>72008,20061,0.25</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Skill2008</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Skill2057</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>0.15,20,20</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Skill2066</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Skill3065</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>20081,3</t>
-  </si>
-  <si>
-    <t>Skill3072</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>0.5,50</t>
-  </si>
-  <si>
-    <t>Skill3076</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>20081,30381</t>
-  </si>
-  <si>
-    <t>Skill4014</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Skill4019</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>5,1,1,5,1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Skill4041</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Skill4046</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Skill4048</t>
+  </si>
+  <si>
+    <t>Skill4049</t>
+  </si>
+  <si>
+    <t>Skill4050</t>
+  </si>
+  <si>
+    <t>Skill4051</t>
+  </si>
+  <si>
+    <t>Skill4052</t>
+  </si>
+  <si>
+    <t>Skill4053</t>
+  </si>
+  <si>
+    <t>Skill4054</t>
   </si>
   <si>
     <t>Skill4055</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>160,32</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Skill4056</t>
+  </si>
+  <si>
+    <t>Skill4057</t>
+  </si>
+  <si>
+    <t>Skill4058</t>
+  </si>
+  <si>
+    <t>Skill4059</t>
+  </si>
+  <si>
+    <t>Skill4060</t>
+  </si>
+  <si>
+    <t>Skill4061</t>
+  </si>
+  <si>
+    <t>Skill4062</t>
+  </si>
+  <si>
+    <t>Skill4063</t>
+  </si>
+  <si>
+    <t>Skill4064</t>
+  </si>
+  <si>
+    <t>Skill4065</t>
+  </si>
+  <si>
+    <t>Skill4066</t>
+  </si>
+  <si>
+    <t>Skill4067</t>
+  </si>
+  <si>
+    <t>Skill4068</t>
+  </si>
+  <si>
+    <t>Skill4069</t>
+  </si>
+  <si>
+    <t>Skill4070</t>
+  </si>
+  <si>
+    <t>Skill4071</t>
+  </si>
+  <si>
+    <t>Skill4072</t>
   </si>
   <si>
     <t>Skill4073</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1,35,2,35</t>
-  </si>
-  <si>
-    <t>Skill1050</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>3046</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>3056</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>3079</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>4021</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>4074</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>WellyRateBase</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Skill4074</t>
+  </si>
+  <si>
+    <t>Skill4075</t>
+  </si>
+  <si>
+    <t>Skill4076</t>
+  </si>
+  <si>
+    <t>Skill4077</t>
+  </si>
+  <si>
+    <t>Skill4078</t>
+  </si>
+  <si>
+    <t>Skill4079</t>
+  </si>
+  <si>
+    <t>Skill4080</t>
+  </si>
+  <si>
+    <t>Skill4081</t>
+  </si>
+  <si>
+    <t>Skill4082</t>
+  </si>
+  <si>
+    <t>Skill4083</t>
+  </si>
+  <si>
+    <t>Skill4084</t>
   </si>
 </sst>
 </file>
@@ -3690,16 +4484,16 @@
         <v>3</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>854</v>
+        <v>817</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>855</v>
+        <v>818</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>857</v>
+        <v>820</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>859</v>
+        <v>822</v>
       </c>
       <c r="I1" s="1" t="s">
         <v>385</v>
@@ -3729,25 +4523,25 @@
         <v>15</v>
       </c>
       <c r="R1" s="1" t="s">
-        <v>888</v>
+        <v>838</v>
       </c>
       <c r="S1" s="1" t="s">
         <v>52</v>
       </c>
       <c r="T1" s="1" t="s">
-        <v>849</v>
+        <v>813</v>
       </c>
       <c r="U1" s="1" t="s">
         <v>802</v>
       </c>
       <c r="V1" s="1" t="s">
-        <v>820</v>
+        <v>806</v>
       </c>
       <c r="W1" s="1" t="s">
-        <v>821</v>
+        <v>807</v>
       </c>
       <c r="X1" s="1" t="s">
-        <v>825</v>
+        <v>811</v>
       </c>
     </row>
     <row r="2" spans="1:24" x14ac:dyDescent="0.2">
@@ -3838,16 +4632,22 @@
         <v>9</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>853</v>
+        <v>816</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>856</v>
+        <v>819</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>858</v>
+        <v>821</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>860</v>
+        <v>823</v>
+      </c>
+      <c r="I3" s="1" t="s">
+        <v>839</v>
+      </c>
+      <c r="J3" s="1" t="s">
+        <v>840</v>
       </c>
       <c r="K3" s="1" t="s">
         <v>384</v>
@@ -3883,13 +4683,13 @@
         <v>801</v>
       </c>
       <c r="V3" s="1" t="s">
-        <v>822</v>
+        <v>808</v>
       </c>
       <c r="W3" s="1" t="s">
-        <v>823</v>
+        <v>809</v>
       </c>
       <c r="X3" s="1" t="s">
-        <v>824</v>
+        <v>810</v>
       </c>
     </row>
     <row r="4" spans="1:24" x14ac:dyDescent="0.2">
@@ -3908,6 +4708,9 @@
       <c r="E4" s="1" t="s">
         <v>36</v>
       </c>
+      <c r="I4" s="1" t="s">
+        <v>842</v>
+      </c>
       <c r="L4" s="1" t="s">
         <v>25</v>
       </c>
@@ -3952,6 +4755,9 @@
       <c r="D5" s="1" t="s">
         <v>35</v>
       </c>
+      <c r="I5" s="1" t="s">
+        <v>843</v>
+      </c>
       <c r="L5" s="1" t="s">
         <v>26</v>
       </c>
@@ -3999,6 +4805,9 @@
       <c r="E6" s="1" t="s">
         <v>36</v>
       </c>
+      <c r="I6" s="1" t="s">
+        <v>844</v>
+      </c>
       <c r="L6" s="1" t="s">
         <v>27</v>
       </c>
@@ -4043,6 +4852,9 @@
       <c r="D7" s="1" t="s">
         <v>42</v>
       </c>
+      <c r="I7" s="1" t="s">
+        <v>845</v>
+      </c>
       <c r="L7" s="1" t="s">
         <v>25</v>
       </c>
@@ -4090,6 +4902,9 @@
       <c r="E8" s="1" t="s">
         <v>36</v>
       </c>
+      <c r="I8" s="1" t="s">
+        <v>846</v>
+      </c>
       <c r="L8" s="1" t="s">
         <v>25</v>
       </c>
@@ -4134,6 +4949,9 @@
       <c r="D9" s="1" t="s">
         <v>47</v>
       </c>
+      <c r="I9" s="1" t="s">
+        <v>847</v>
+      </c>
       <c r="L9" s="1" t="s">
         <v>25</v>
       </c>
@@ -4178,6 +4996,9 @@
       <c r="D10" s="1" t="s">
         <v>54</v>
       </c>
+      <c r="I10" s="1" t="s">
+        <v>848</v>
+      </c>
       <c r="L10" s="1" t="s">
         <v>25</v>
       </c>
@@ -4222,6 +5043,9 @@
       <c r="D11" s="1" t="s">
         <v>57</v>
       </c>
+      <c r="I11" s="1" t="s">
+        <v>849</v>
+      </c>
       <c r="L11" s="1" t="s">
         <v>25</v>
       </c>
@@ -4266,6 +5090,9 @@
       <c r="D12" s="1" t="s">
         <v>60</v>
       </c>
+      <c r="I12" s="1" t="s">
+        <v>850</v>
+      </c>
       <c r="L12" s="1" t="s">
         <v>25</v>
       </c>
@@ -4311,10 +5138,10 @@
         <v>64</v>
       </c>
       <c r="I13" s="1" t="s">
-        <v>806</v>
+        <v>884</v>
       </c>
       <c r="J13" s="1" t="s">
-        <v>809</v>
+        <v>803</v>
       </c>
       <c r="K13" s="1" t="s">
         <v>284</v>
@@ -4364,10 +5191,10 @@
         <v>65</v>
       </c>
       <c r="I14" s="1" t="s">
-        <v>807</v>
+        <v>841</v>
       </c>
       <c r="J14" s="1" t="s">
-        <v>810</v>
+        <v>804</v>
       </c>
       <c r="K14" s="1" t="s">
         <v>284</v>
@@ -4416,6 +5243,9 @@
       <c r="D15" s="1" t="s">
         <v>71</v>
       </c>
+      <c r="I15" s="1" t="s">
+        <v>851</v>
+      </c>
       <c r="L15" s="1" t="s">
         <v>25</v>
       </c>
@@ -4460,6 +5290,9 @@
       <c r="D16" s="1" t="s">
         <v>76</v>
       </c>
+      <c r="I16" s="1" t="s">
+        <v>852</v>
+      </c>
       <c r="L16" s="1" t="s">
         <v>25</v>
       </c>
@@ -4504,6 +5337,9 @@
       <c r="D17" s="1" t="s">
         <v>78</v>
       </c>
+      <c r="I17" s="1" t="s">
+        <v>853</v>
+      </c>
       <c r="L17" s="1" t="s">
         <v>25</v>
       </c>
@@ -4548,6 +5384,9 @@
       <c r="D18" s="1" t="s">
         <v>81</v>
       </c>
+      <c r="I18" s="1" t="s">
+        <v>854</v>
+      </c>
       <c r="L18" s="1" t="s">
         <v>25</v>
       </c>
@@ -4592,6 +5431,9 @@
       <c r="D19" s="1" t="s">
         <v>85</v>
       </c>
+      <c r="I19" s="1" t="s">
+        <v>855</v>
+      </c>
       <c r="L19" s="1" t="s">
         <v>25</v>
       </c>
@@ -4636,6 +5478,9 @@
       <c r="D20" s="1" t="s">
         <v>89</v>
       </c>
+      <c r="I20" s="1" t="s">
+        <v>856</v>
+      </c>
       <c r="L20" s="1" t="s">
         <v>25</v>
       </c>
@@ -4680,6 +5525,9 @@
       <c r="D21" s="1" t="s">
         <v>92</v>
       </c>
+      <c r="I21" s="1" t="s">
+        <v>857</v>
+      </c>
       <c r="L21" s="1" t="s">
         <v>25</v>
       </c>
@@ -4724,6 +5572,9 @@
       <c r="D22" s="1" t="s">
         <v>92</v>
       </c>
+      <c r="I22" s="1" t="s">
+        <v>858</v>
+      </c>
       <c r="L22" s="1" t="s">
         <v>25</v>
       </c>
@@ -4768,6 +5619,9 @@
       <c r="D23" s="1" t="s">
         <v>96</v>
       </c>
+      <c r="I23" s="1" t="s">
+        <v>859</v>
+      </c>
       <c r="L23" s="1" t="s">
         <v>25</v>
       </c>
@@ -4812,6 +5666,9 @@
       <c r="D24" s="1" t="s">
         <v>100</v>
       </c>
+      <c r="I24" s="1" t="s">
+        <v>860</v>
+      </c>
       <c r="L24" s="1" t="s">
         <v>25</v>
       </c>
@@ -4856,6 +5713,9 @@
       <c r="D25" s="1" t="s">
         <v>96</v>
       </c>
+      <c r="I25" s="1" t="s">
+        <v>861</v>
+      </c>
       <c r="L25" s="1" t="s">
         <v>25</v>
       </c>
@@ -4903,6 +5763,9 @@
       <c r="E26" s="1" t="s">
         <v>36</v>
       </c>
+      <c r="I26" s="1" t="s">
+        <v>862</v>
+      </c>
       <c r="L26" s="1" t="s">
         <v>25</v>
       </c>
@@ -4947,6 +5810,9 @@
       <c r="D27" s="1" t="s">
         <v>107</v>
       </c>
+      <c r="I27" s="1" t="s">
+        <v>863</v>
+      </c>
       <c r="L27" s="1" t="s">
         <v>25</v>
       </c>
@@ -4991,6 +5857,9 @@
       <c r="D28" s="1" t="s">
         <v>110</v>
       </c>
+      <c r="I28" s="1" t="s">
+        <v>864</v>
+      </c>
       <c r="L28" s="1" t="s">
         <v>25</v>
       </c>
@@ -5032,6 +5901,9 @@
       <c r="D29" s="1" t="s">
         <v>114</v>
       </c>
+      <c r="I29" s="1" t="s">
+        <v>865</v>
+      </c>
       <c r="L29" s="1" t="s">
         <v>25</v>
       </c>
@@ -5076,6 +5948,9 @@
       <c r="D30" s="1" t="s">
         <v>115</v>
       </c>
+      <c r="I30" s="1" t="s">
+        <v>866</v>
+      </c>
       <c r="L30" s="1" t="s">
         <v>25</v>
       </c>
@@ -5120,6 +5995,9 @@
       <c r="D31" s="1" t="s">
         <v>120</v>
       </c>
+      <c r="I31" s="1" t="s">
+        <v>867</v>
+      </c>
       <c r="L31" s="1" t="s">
         <v>25</v>
       </c>
@@ -5161,6 +6039,9 @@
       <c r="D32" s="1" t="s">
         <v>122</v>
       </c>
+      <c r="I32" s="1" t="s">
+        <v>868</v>
+      </c>
       <c r="L32" s="1" t="s">
         <v>25</v>
       </c>
@@ -5205,6 +6086,9 @@
       <c r="D33" s="1" t="s">
         <v>125</v>
       </c>
+      <c r="I33" s="1" t="s">
+        <v>869</v>
+      </c>
       <c r="L33" s="1" t="s">
         <v>25</v>
       </c>
@@ -5249,6 +6133,9 @@
       <c r="D34" s="1" t="s">
         <v>127</v>
       </c>
+      <c r="I34" s="1" t="s">
+        <v>870</v>
+      </c>
       <c r="L34" s="1" t="s">
         <v>25</v>
       </c>
@@ -5293,6 +6180,9 @@
       <c r="E35" s="1" t="s">
         <v>36</v>
       </c>
+      <c r="I35" s="1" t="s">
+        <v>871</v>
+      </c>
       <c r="L35" s="1" t="s">
         <v>25</v>
       </c>
@@ -5337,6 +6227,9 @@
       <c r="D36" s="1" t="s">
         <v>132</v>
       </c>
+      <c r="I36" s="1" t="s">
+        <v>872</v>
+      </c>
       <c r="L36" s="1" t="s">
         <v>25</v>
       </c>
@@ -5381,6 +6274,9 @@
       <c r="D37" s="1" t="s">
         <v>136</v>
       </c>
+      <c r="I37" s="1" t="s">
+        <v>873</v>
+      </c>
       <c r="L37" s="1" t="s">
         <v>25</v>
       </c>
@@ -5422,6 +6318,9 @@
       <c r="D38" s="1" t="s">
         <v>138</v>
       </c>
+      <c r="I38" s="1" t="s">
+        <v>874</v>
+      </c>
       <c r="L38" s="1" t="s">
         <v>25</v>
       </c>
@@ -5463,6 +6362,9 @@
       <c r="D39" s="1" t="s">
         <v>140</v>
       </c>
+      <c r="I39" s="1" t="s">
+        <v>875</v>
+      </c>
       <c r="L39" s="1" t="s">
         <v>25</v>
       </c>
@@ -5505,7 +6407,7 @@
         <v>142</v>
       </c>
       <c r="I40" s="1" t="s">
-        <v>830</v>
+        <v>885</v>
       </c>
       <c r="L40" s="1" t="s">
         <v>25</v>
@@ -5551,6 +6453,9 @@
       <c r="E41" s="1" t="s">
         <v>36</v>
       </c>
+      <c r="I41" s="1" t="s">
+        <v>876</v>
+      </c>
       <c r="L41" s="1" t="s">
         <v>25</v>
       </c>
@@ -5593,10 +6498,10 @@
         <v>146</v>
       </c>
       <c r="I42" s="1" t="s">
-        <v>850</v>
+        <v>886</v>
       </c>
       <c r="K42" s="1" t="s">
-        <v>851</v>
+        <v>814</v>
       </c>
       <c r="L42" s="1" t="s">
         <v>25</v>
@@ -5639,6 +6544,9 @@
       <c r="D43" s="1" t="s">
         <v>140</v>
       </c>
+      <c r="I43" s="1" t="s">
+        <v>877</v>
+      </c>
       <c r="L43" s="1" t="s">
         <v>25</v>
       </c>
@@ -5680,6 +6588,9 @@
       <c r="D44" s="1" t="s">
         <v>92</v>
       </c>
+      <c r="I44" s="1" t="s">
+        <v>878</v>
+      </c>
       <c r="L44" s="1" t="s">
         <v>25</v>
       </c>
@@ -5724,6 +6635,9 @@
       <c r="D45" s="1" t="s">
         <v>92</v>
       </c>
+      <c r="I45" s="1" t="s">
+        <v>879</v>
+      </c>
       <c r="L45" s="1" t="s">
         <v>25</v>
       </c>
@@ -5768,6 +6682,9 @@
       <c r="D46" s="1" t="s">
         <v>96</v>
       </c>
+      <c r="I46" s="1" t="s">
+        <v>880</v>
+      </c>
       <c r="L46" s="1" t="s">
         <v>25</v>
       </c>
@@ -5812,6 +6729,9 @@
       <c r="D47" s="1" t="s">
         <v>96</v>
       </c>
+      <c r="I47" s="1" t="s">
+        <v>881</v>
+      </c>
       <c r="L47" s="1" t="s">
         <v>25</v>
       </c>
@@ -5856,6 +6776,9 @@
       <c r="D48" s="1" t="s">
         <v>138</v>
       </c>
+      <c r="I48" s="1" t="s">
+        <v>882</v>
+      </c>
       <c r="L48" s="1" t="s">
         <v>25</v>
       </c>
@@ -5897,6 +6820,9 @@
       <c r="D49" s="1" t="s">
         <v>140</v>
       </c>
+      <c r="I49" s="1" t="s">
+        <v>883</v>
+      </c>
       <c r="L49" s="1" t="s">
         <v>25</v>
       </c>
@@ -5939,7 +6865,7 @@
         <v>142</v>
       </c>
       <c r="I50" s="1" t="s">
-        <v>831</v>
+        <v>887</v>
       </c>
       <c r="L50" s="1" t="s">
         <v>25</v>
@@ -5982,6 +6908,9 @@
       <c r="D51" s="1" t="s">
         <v>155</v>
       </c>
+      <c r="I51" s="1" t="s">
+        <v>888</v>
+      </c>
       <c r="L51" s="1" t="s">
         <v>25</v>
       </c>
@@ -6023,6 +6952,9 @@
       <c r="D52" s="1" t="s">
         <v>156</v>
       </c>
+      <c r="I52" s="1" t="s">
+        <v>889</v>
+      </c>
       <c r="L52" s="1" t="s">
         <v>25</v>
       </c>
@@ -6065,7 +6997,7 @@
         <v>157</v>
       </c>
       <c r="I53" s="1" t="s">
-        <v>882</v>
+        <v>890</v>
       </c>
       <c r="K53" s="1" t="s">
         <v>618</v>
@@ -6117,6 +7049,9 @@
       <c r="E54" s="1" t="s">
         <v>36</v>
       </c>
+      <c r="I54" s="1" t="s">
+        <v>891</v>
+      </c>
       <c r="L54" s="1" t="s">
         <v>25</v>
       </c>
@@ -6161,6 +7096,9 @@
       <c r="D55" s="1" t="s">
         <v>162</v>
       </c>
+      <c r="I55" s="1" t="s">
+        <v>892</v>
+      </c>
       <c r="L55" s="1" t="s">
         <v>25</v>
       </c>
@@ -6204,6 +7142,9 @@
       </c>
       <c r="D56" s="1" t="s">
         <v>165</v>
+      </c>
+      <c r="I56" s="1" t="s">
+        <v>893</v>
       </c>
       <c r="L56" s="1" t="s">
         <v>25</v>
@@ -6250,6 +7191,9 @@
       <c r="D58" s="1" t="s">
         <v>167</v>
       </c>
+      <c r="I58" s="1" t="s">
+        <v>894</v>
+      </c>
       <c r="L58" s="1" t="s">
         <v>25</v>
       </c>
@@ -6294,6 +7238,9 @@
       <c r="D59" s="1" t="s">
         <v>172</v>
       </c>
+      <c r="I59" s="1" t="s">
+        <v>895</v>
+      </c>
       <c r="L59" s="1" t="s">
         <v>25</v>
       </c>
@@ -6338,6 +7285,9 @@
       <c r="D60" s="1" t="s">
         <v>173</v>
       </c>
+      <c r="I60" s="1" t="s">
+        <v>896</v>
+      </c>
       <c r="L60" s="1" t="s">
         <v>25</v>
       </c>
@@ -6382,6 +7332,9 @@
       <c r="D61" s="1" t="s">
         <v>182</v>
       </c>
+      <c r="I61" s="1" t="s">
+        <v>897</v>
+      </c>
       <c r="L61" s="1" t="s">
         <v>25</v>
       </c>
@@ -6426,6 +7379,9 @@
       <c r="D62" s="1" t="s">
         <v>183</v>
       </c>
+      <c r="I62" s="1" t="s">
+        <v>898</v>
+      </c>
       <c r="L62" s="1" t="s">
         <v>25</v>
       </c>
@@ -6470,6 +7426,9 @@
       <c r="D63" s="1" t="s">
         <v>184</v>
       </c>
+      <c r="I63" s="1" t="s">
+        <v>899</v>
+      </c>
       <c r="L63" s="1" t="s">
         <v>25</v>
       </c>
@@ -6514,6 +7473,9 @@
       <c r="D64" s="1" t="s">
         <v>193</v>
       </c>
+      <c r="I64" s="1" t="s">
+        <v>900</v>
+      </c>
       <c r="L64" s="1" t="s">
         <v>25</v>
       </c>
@@ -6559,10 +7521,10 @@
         <v>197</v>
       </c>
       <c r="I65" s="1" t="s">
-        <v>863</v>
+        <v>901</v>
       </c>
       <c r="K65" s="1" t="s">
-        <v>862</v>
+        <v>825</v>
       </c>
       <c r="L65" s="1" t="s">
         <v>25</v>
@@ -6609,7 +7571,7 @@
         <v>199</v>
       </c>
       <c r="I66" s="1" t="s">
-        <v>808</v>
+        <v>902</v>
       </c>
       <c r="L66" s="1" t="s">
         <v>25</v>
@@ -6655,6 +7617,9 @@
       <c r="D67" s="1" t="s">
         <v>203</v>
       </c>
+      <c r="I67" s="1" t="s">
+        <v>903</v>
+      </c>
       <c r="L67" s="1" t="s">
         <v>25</v>
       </c>
@@ -6690,6 +7655,9 @@
       <c r="D68" s="1" t="s">
         <v>214</v>
       </c>
+      <c r="I68" s="1" t="s">
+        <v>904</v>
+      </c>
       <c r="L68" s="1" t="s">
         <v>25</v>
       </c>
@@ -6725,6 +7693,9 @@
       <c r="D69" s="1" t="s">
         <v>215</v>
       </c>
+      <c r="I69" s="1" t="s">
+        <v>905</v>
+      </c>
       <c r="L69" s="1" t="s">
         <v>25</v>
       </c>
@@ -6760,6 +7731,9 @@
       <c r="D70" s="1" t="s">
         <v>216</v>
       </c>
+      <c r="I70" s="1" t="s">
+        <v>906</v>
+      </c>
       <c r="L70" s="1" t="s">
         <v>25</v>
       </c>
@@ -6804,6 +7778,9 @@
       <c r="D71" s="1" t="s">
         <v>217</v>
       </c>
+      <c r="I71" s="1" t="s">
+        <v>907</v>
+      </c>
       <c r="L71" s="1" t="s">
         <v>25</v>
       </c>
@@ -6848,6 +7825,9 @@
       <c r="D72" s="1" t="s">
         <v>218</v>
       </c>
+      <c r="I72" s="1" t="s">
+        <v>908</v>
+      </c>
       <c r="L72" s="1" t="s">
         <v>25</v>
       </c>
@@ -6892,6 +7872,9 @@
       <c r="D73" s="1" t="s">
         <v>219</v>
       </c>
+      <c r="I73" s="1" t="s">
+        <v>909</v>
+      </c>
       <c r="L73" s="1" t="s">
         <v>25</v>
       </c>
@@ -6936,6 +7919,9 @@
       <c r="D74" s="1" t="s">
         <v>220</v>
       </c>
+      <c r="I74" s="1" t="s">
+        <v>910</v>
+      </c>
       <c r="L74" s="1" t="s">
         <v>25</v>
       </c>
@@ -6980,6 +7966,9 @@
       <c r="D75" s="1" t="s">
         <v>221</v>
       </c>
+      <c r="I75" s="1" t="s">
+        <v>911</v>
+      </c>
       <c r="L75" s="1" t="s">
         <v>25</v>
       </c>
@@ -7024,6 +8013,9 @@
       <c r="D76" s="1" t="s">
         <v>222</v>
       </c>
+      <c r="I76" s="1" t="s">
+        <v>912</v>
+      </c>
       <c r="L76" s="1" t="s">
         <v>25</v>
       </c>
@@ -7068,6 +8060,9 @@
       <c r="D77" s="1" t="s">
         <v>223</v>
       </c>
+      <c r="I77" s="1" t="s">
+        <v>913</v>
+      </c>
       <c r="L77" s="1" t="s">
         <v>25</v>
       </c>
@@ -7112,6 +8107,9 @@
       <c r="D78" s="1" t="s">
         <v>232</v>
       </c>
+      <c r="I78" s="1" t="s">
+        <v>914</v>
+      </c>
       <c r="L78" s="1" t="s">
         <v>25</v>
       </c>
@@ -7156,6 +8154,9 @@
       <c r="D79" s="1" t="s">
         <v>235</v>
       </c>
+      <c r="I79" s="1" t="s">
+        <v>915</v>
+      </c>
       <c r="L79" s="1" t="s">
         <v>25</v>
       </c>
@@ -7191,6 +8192,9 @@
       <c r="D80" s="1" t="s">
         <v>237</v>
       </c>
+      <c r="I80" s="1" t="s">
+        <v>916</v>
+      </c>
       <c r="L80" s="1" t="s">
         <v>25</v>
       </c>
@@ -7226,6 +8230,9 @@
       <c r="D81" s="1" t="s">
         <v>242</v>
       </c>
+      <c r="I81" s="1" t="s">
+        <v>917</v>
+      </c>
       <c r="L81" s="1" t="s">
         <v>25</v>
       </c>
@@ -7270,6 +8277,9 @@
       <c r="D82" s="1" t="s">
         <v>242</v>
       </c>
+      <c r="I82" s="1" t="s">
+        <v>918</v>
+      </c>
       <c r="L82" s="1" t="s">
         <v>25</v>
       </c>
@@ -7315,7 +8325,7 @@
         <v>247</v>
       </c>
       <c r="I83" s="1" t="s">
-        <v>832</v>
+        <v>919</v>
       </c>
       <c r="L83" s="1" t="s">
         <v>25</v>
@@ -7362,7 +8372,7 @@
         <v>250</v>
       </c>
       <c r="I84" s="1" t="s">
-        <v>833</v>
+        <v>920</v>
       </c>
       <c r="L84" s="1" t="s">
         <v>25</v>
@@ -7409,7 +8419,7 @@
         <v>254</v>
       </c>
       <c r="I85" s="1" t="s">
-        <v>811</v>
+        <v>921</v>
       </c>
       <c r="L85" s="1" t="s">
         <v>25</v>
@@ -7456,7 +8466,7 @@
         <v>250</v>
       </c>
       <c r="I86" s="1" t="s">
-        <v>834</v>
+        <v>922</v>
       </c>
       <c r="L86" s="1" t="s">
         <v>25</v>
@@ -7503,7 +8513,7 @@
         <v>254</v>
       </c>
       <c r="I87" s="1" t="s">
-        <v>812</v>
+        <v>923</v>
       </c>
       <c r="L87" s="1" t="s">
         <v>25</v>
@@ -7549,6 +8559,9 @@
       <c r="D88" s="1" t="s">
         <v>259</v>
       </c>
+      <c r="I88" s="1" t="s">
+        <v>924</v>
+      </c>
       <c r="L88" s="1" t="s">
         <v>25</v>
       </c>
@@ -7594,7 +8607,7 @@
         <v>266</v>
       </c>
       <c r="I89" s="1" t="s">
-        <v>803</v>
+        <v>925</v>
       </c>
       <c r="K89" s="1" t="s">
         <v>29</v>
@@ -7635,7 +8648,7 @@
         <v>267</v>
       </c>
       <c r="I90" s="1" t="s">
-        <v>804</v>
+        <v>926</v>
       </c>
       <c r="L90" s="1" t="s">
         <v>25</v>
@@ -7673,7 +8686,7 @@
         <v>268</v>
       </c>
       <c r="I91" s="1" t="s">
-        <v>805</v>
+        <v>927</v>
       </c>
       <c r="L91" s="1" t="s">
         <v>25</v>
@@ -7710,6 +8723,9 @@
       <c r="D92" s="1" t="s">
         <v>270</v>
       </c>
+      <c r="I92" s="1" t="s">
+        <v>928</v>
+      </c>
       <c r="L92" s="1" t="s">
         <v>25</v>
       </c>
@@ -7751,6 +8767,9 @@
       <c r="D93" s="1" t="s">
         <v>272</v>
       </c>
+      <c r="I93" s="1" t="s">
+        <v>929</v>
+      </c>
       <c r="L93" s="1" t="s">
         <v>25</v>
       </c>
@@ -7792,6 +8811,9 @@
       <c r="D94" s="1" t="s">
         <v>275</v>
       </c>
+      <c r="I94" s="1" t="s">
+        <v>930</v>
+      </c>
       <c r="L94" s="1" t="s">
         <v>25</v>
       </c>
@@ -7833,6 +8855,9 @@
       <c r="D95" s="1" t="s">
         <v>277</v>
       </c>
+      <c r="I95" s="1" t="s">
+        <v>931</v>
+      </c>
       <c r="L95" s="1" t="s">
         <v>25</v>
       </c>
@@ -7865,6 +8890,9 @@
       <c r="D96" s="1" t="s">
         <v>279</v>
       </c>
+      <c r="I96" s="1" t="s">
+        <v>932</v>
+      </c>
       <c r="L96" s="1" t="s">
         <v>25</v>
       </c>
@@ -7909,6 +8937,9 @@
       <c r="D97" s="1" t="s">
         <v>283</v>
       </c>
+      <c r="I97" s="1" t="s">
+        <v>933</v>
+      </c>
       <c r="L97" s="1" t="s">
         <v>25</v>
       </c>
@@ -7950,6 +8981,9 @@
       <c r="D98" s="1" t="s">
         <v>287</v>
       </c>
+      <c r="I98" s="1" t="s">
+        <v>934</v>
+      </c>
       <c r="L98" s="1" t="s">
         <v>25</v>
       </c>
@@ -7991,6 +9025,9 @@
       <c r="D99" s="1" t="s">
         <v>289</v>
       </c>
+      <c r="I99" s="1" t="s">
+        <v>935</v>
+      </c>
       <c r="L99" s="1" t="s">
         <v>25</v>
       </c>
@@ -8032,6 +9069,9 @@
       <c r="D100" s="1" t="s">
         <v>291</v>
       </c>
+      <c r="I100" s="1" t="s">
+        <v>936</v>
+      </c>
       <c r="L100" s="1" t="s">
         <v>25</v>
       </c>
@@ -8073,6 +9113,9 @@
       <c r="D101" s="1" t="s">
         <v>293</v>
       </c>
+      <c r="I101" s="1" t="s">
+        <v>937</v>
+      </c>
       <c r="L101" s="1" t="s">
         <v>25</v>
       </c>
@@ -8117,6 +9160,9 @@
       <c r="D102" s="1" t="s">
         <v>296</v>
       </c>
+      <c r="I102" s="1" t="s">
+        <v>938</v>
+      </c>
       <c r="L102" s="1" t="s">
         <v>25</v>
       </c>
@@ -8161,6 +9207,9 @@
       <c r="D103" s="1" t="s">
         <v>299</v>
       </c>
+      <c r="I103" s="1" t="s">
+        <v>939</v>
+      </c>
       <c r="L103" s="1" t="s">
         <v>25</v>
       </c>
@@ -8205,6 +9254,9 @@
       <c r="D104" s="1" t="s">
         <v>303</v>
       </c>
+      <c r="I104" s="1" t="s">
+        <v>940</v>
+      </c>
       <c r="L104" s="1" t="s">
         <v>25</v>
       </c>
@@ -8249,6 +9301,9 @@
       <c r="D105" s="1" t="s">
         <v>305</v>
       </c>
+      <c r="I105" s="1" t="s">
+        <v>941</v>
+      </c>
       <c r="L105" s="1" t="s">
         <v>25</v>
       </c>
@@ -8293,6 +9348,9 @@
       <c r="D106" s="1" t="s">
         <v>308</v>
       </c>
+      <c r="I106" s="1" t="s">
+        <v>942</v>
+      </c>
       <c r="L106" s="1" t="s">
         <v>25</v>
       </c>
@@ -8337,6 +9395,9 @@
       <c r="D107" s="1" t="s">
         <v>311</v>
       </c>
+      <c r="I107" s="1" t="s">
+        <v>943</v>
+      </c>
       <c r="L107" s="1" t="s">
         <v>25</v>
       </c>
@@ -8381,6 +9442,9 @@
       <c r="D108" s="1" t="s">
         <v>314</v>
       </c>
+      <c r="I108" s="1" t="s">
+        <v>944</v>
+      </c>
       <c r="L108" s="1" t="s">
         <v>25</v>
       </c>
@@ -8425,6 +9489,9 @@
       <c r="D109" s="1" t="s">
         <v>317</v>
       </c>
+      <c r="I109" s="1" t="s">
+        <v>945</v>
+      </c>
       <c r="L109" s="1" t="s">
         <v>25</v>
       </c>
@@ -8469,6 +9536,9 @@
       <c r="D110" s="1" t="s">
         <v>320</v>
       </c>
+      <c r="I110" s="1" t="s">
+        <v>946</v>
+      </c>
       <c r="L110" s="1" t="s">
         <v>25</v>
       </c>
@@ -8513,6 +9583,9 @@
       <c r="D111" s="1" t="s">
         <v>322</v>
       </c>
+      <c r="I111" s="1" t="s">
+        <v>947</v>
+      </c>
       <c r="L111" s="1" t="s">
         <v>25</v>
       </c>
@@ -8557,6 +9630,9 @@
       <c r="D112" s="1" t="s">
         <v>323</v>
       </c>
+      <c r="I112" s="1" t="s">
+        <v>948</v>
+      </c>
       <c r="L112" s="1" t="s">
         <v>25</v>
       </c>
@@ -8601,6 +9677,9 @@
       <c r="D113" s="1" t="s">
         <v>327</v>
       </c>
+      <c r="I113" s="1" t="s">
+        <v>949</v>
+      </c>
       <c r="L113" s="1" t="s">
         <v>25</v>
       </c>
@@ -8646,10 +9725,10 @@
         <v>346</v>
       </c>
       <c r="I114" s="1" t="s">
-        <v>864</v>
+        <v>950</v>
       </c>
       <c r="K114" s="1" t="s">
-        <v>865</v>
+        <v>826</v>
       </c>
       <c r="L114" s="1" t="s">
         <v>25</v>
@@ -8692,6 +9771,9 @@
       <c r="D115" s="1" t="s">
         <v>347</v>
       </c>
+      <c r="I115" s="1" t="s">
+        <v>951</v>
+      </c>
       <c r="L115" s="1" t="s">
         <v>25</v>
       </c>
@@ -8733,6 +9815,9 @@
       <c r="D116" s="1" t="s">
         <v>348</v>
       </c>
+      <c r="I116" s="1" t="s">
+        <v>952</v>
+      </c>
       <c r="L116" s="1" t="s">
         <v>25</v>
       </c>
@@ -8774,6 +9859,9 @@
       <c r="D117" s="1" t="s">
         <v>349</v>
       </c>
+      <c r="I117" s="1" t="s">
+        <v>953</v>
+      </c>
       <c r="J117" s="4" t="s">
         <v>369</v>
       </c>
@@ -8822,6 +9910,9 @@
       <c r="D118" s="1" t="s">
         <v>350</v>
       </c>
+      <c r="I118" s="1" t="s">
+        <v>954</v>
+      </c>
       <c r="L118" s="1" t="s">
         <v>25</v>
       </c>
@@ -8866,6 +9957,9 @@
       <c r="D119" s="1" t="s">
         <v>350</v>
       </c>
+      <c r="I119" s="1" t="s">
+        <v>955</v>
+      </c>
       <c r="L119" s="1" t="s">
         <v>25</v>
       </c>
@@ -8910,6 +10004,9 @@
       <c r="D120" s="1" t="s">
         <v>351</v>
       </c>
+      <c r="I120" s="1" t="s">
+        <v>956</v>
+      </c>
       <c r="L120" s="1" t="s">
         <v>25</v>
       </c>
@@ -8954,6 +10051,9 @@
       <c r="D121" s="1" t="s">
         <v>351</v>
       </c>
+      <c r="I121" s="1" t="s">
+        <v>957</v>
+      </c>
       <c r="L121" s="1" t="s">
         <v>25</v>
       </c>
@@ -8998,6 +10098,9 @@
       <c r="D122" s="1" t="s">
         <v>352</v>
       </c>
+      <c r="I122" s="1" t="s">
+        <v>958</v>
+      </c>
       <c r="J122" s="4" t="s">
         <v>372</v>
       </c>
@@ -9047,7 +10150,7 @@
         <v>353</v>
       </c>
       <c r="I123" s="1" t="s">
-        <v>866</v>
+        <v>959</v>
       </c>
       <c r="L123" s="1" t="s">
         <v>25</v>
@@ -9094,7 +10197,7 @@
         <v>354</v>
       </c>
       <c r="I124" s="1" t="s">
-        <v>828</v>
+        <v>960</v>
       </c>
       <c r="L124" s="1" t="s">
         <v>25</v>
@@ -9137,6 +10240,9 @@
       <c r="D125" s="1" t="s">
         <v>355</v>
       </c>
+      <c r="I125" s="1" t="s">
+        <v>961</v>
+      </c>
       <c r="L125" s="1" t="s">
         <v>25</v>
       </c>
@@ -9178,6 +10284,9 @@
       <c r="D126" s="1" t="s">
         <v>356</v>
       </c>
+      <c r="I126" s="1" t="s">
+        <v>962</v>
+      </c>
       <c r="L126" s="1" t="s">
         <v>25</v>
       </c>
@@ -9211,7 +10320,7 @@
     </row>
     <row r="127" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A127" s="4" t="s">
-        <v>861</v>
+        <v>824</v>
       </c>
       <c r="B127" s="4" t="s">
         <v>341</v>
@@ -9221,6 +10330,9 @@
       </c>
       <c r="D127" s="1" t="s">
         <v>357</v>
+      </c>
+      <c r="I127" s="1" t="s">
+        <v>963</v>
       </c>
       <c r="L127" s="1" t="s">
         <v>25</v>
@@ -9266,6 +10378,9 @@
       <c r="D128" s="1" t="s">
         <v>358</v>
       </c>
+      <c r="I128" s="1" t="s">
+        <v>964</v>
+      </c>
       <c r="L128" s="1" t="s">
         <v>25</v>
       </c>
@@ -9307,6 +10422,9 @@
       <c r="D129" s="1" t="s">
         <v>361</v>
       </c>
+      <c r="I129" s="1" t="s">
+        <v>965</v>
+      </c>
       <c r="L129" s="1" t="s">
         <v>25</v>
       </c>
@@ -9348,6 +10466,9 @@
       <c r="D130" s="1" t="s">
         <v>362</v>
       </c>
+      <c r="I130" s="1" t="s">
+        <v>966</v>
+      </c>
       <c r="L130" s="1" t="s">
         <v>25</v>
       </c>
@@ -9389,6 +10510,9 @@
       <c r="D131" s="1" t="s">
         <v>359</v>
       </c>
+      <c r="I131" s="1" t="s">
+        <v>967</v>
+      </c>
       <c r="L131" s="1" t="s">
         <v>25</v>
       </c>
@@ -9429,6 +10553,9 @@
       </c>
       <c r="D132" s="1" t="s">
         <v>360</v>
+      </c>
+      <c r="I132" s="1" t="s">
+        <v>968</v>
       </c>
       <c r="L132" s="1" t="s">
         <v>25</v>
@@ -9472,6 +10599,9 @@
       <c r="D134" s="1" t="s">
         <v>396</v>
       </c>
+      <c r="I134" s="1" t="s">
+        <v>969</v>
+      </c>
       <c r="L134" s="1" t="s">
         <v>25</v>
       </c>
@@ -9516,6 +10646,9 @@
       <c r="D135" s="1" t="s">
         <v>397</v>
       </c>
+      <c r="I135" s="1" t="s">
+        <v>970</v>
+      </c>
       <c r="L135" s="1" t="s">
         <v>25</v>
       </c>
@@ -9560,6 +10693,9 @@
       <c r="D136" s="1" t="s">
         <v>398</v>
       </c>
+      <c r="I136" s="1" t="s">
+        <v>971</v>
+      </c>
       <c r="L136" s="1" t="s">
         <v>25</v>
       </c>
@@ -9604,6 +10740,9 @@
       <c r="D137" s="1" t="s">
         <v>399</v>
       </c>
+      <c r="I137" s="1" t="s">
+        <v>972</v>
+      </c>
       <c r="L137" s="1" t="s">
         <v>25</v>
       </c>
@@ -9648,6 +10787,9 @@
       <c r="D138" s="1" t="s">
         <v>400</v>
       </c>
+      <c r="I138" s="1" t="s">
+        <v>973</v>
+      </c>
       <c r="L138" s="1" t="s">
         <v>25</v>
       </c>
@@ -9692,6 +10834,9 @@
       <c r="D139" s="1" t="s">
         <v>401</v>
       </c>
+      <c r="I139" s="1" t="s">
+        <v>974</v>
+      </c>
       <c r="L139" s="1" t="s">
         <v>25</v>
       </c>
@@ -9736,6 +10881,9 @@
       <c r="D140" s="1" t="s">
         <v>402</v>
       </c>
+      <c r="I140" s="1" t="s">
+        <v>975</v>
+      </c>
       <c r="L140" s="1" t="s">
         <v>25</v>
       </c>
@@ -9780,6 +10928,9 @@
       <c r="D141" s="1" t="s">
         <v>403</v>
       </c>
+      <c r="I141" s="1" t="s">
+        <v>976</v>
+      </c>
       <c r="L141" s="1" t="s">
         <v>25</v>
       </c>
@@ -9825,7 +10976,7 @@
         <v>404</v>
       </c>
       <c r="I142" s="1" t="s">
-        <v>835</v>
+        <v>977</v>
       </c>
       <c r="L142" s="1" t="s">
         <v>25</v>
@@ -9871,6 +11022,9 @@
       <c r="D143" s="1" t="s">
         <v>405</v>
       </c>
+      <c r="I143" s="1" t="s">
+        <v>978</v>
+      </c>
       <c r="L143" s="1" t="s">
         <v>25</v>
       </c>
@@ -9915,6 +11069,9 @@
       <c r="D144" s="1" t="s">
         <v>511</v>
       </c>
+      <c r="I144" s="1" t="s">
+        <v>979</v>
+      </c>
       <c r="L144" s="1" t="s">
         <v>25</v>
       </c>
@@ -9956,6 +11113,9 @@
       <c r="D145" s="1" t="s">
         <v>512</v>
       </c>
+      <c r="I145" s="1" t="s">
+        <v>980</v>
+      </c>
       <c r="L145" s="1" t="s">
         <v>25</v>
       </c>
@@ -9997,6 +11157,9 @@
       <c r="D146" s="1" t="s">
         <v>513</v>
       </c>
+      <c r="I146" s="1" t="s">
+        <v>981</v>
+      </c>
       <c r="L146" s="1" t="s">
         <v>25</v>
       </c>
@@ -10041,6 +11204,9 @@
       <c r="D147" s="1" t="s">
         <v>514</v>
       </c>
+      <c r="I147" s="1" t="s">
+        <v>982</v>
+      </c>
       <c r="L147" s="1" t="s">
         <v>25</v>
       </c>
@@ -10082,6 +11248,9 @@
       <c r="D148" s="1" t="s">
         <v>515</v>
       </c>
+      <c r="I148" s="1" t="s">
+        <v>983</v>
+      </c>
       <c r="L148" s="1" t="s">
         <v>25</v>
       </c>
@@ -10126,6 +11295,9 @@
       <c r="D149" s="1" t="s">
         <v>516</v>
       </c>
+      <c r="I149" s="1" t="s">
+        <v>984</v>
+      </c>
       <c r="L149" s="1" t="s">
         <v>25</v>
       </c>
@@ -10170,6 +11342,9 @@
       <c r="D150" s="1" t="s">
         <v>517</v>
       </c>
+      <c r="I150" s="1" t="s">
+        <v>985</v>
+      </c>
       <c r="L150" s="1" t="s">
         <v>25</v>
       </c>
@@ -10211,6 +11386,9 @@
       <c r="D151" s="1" t="s">
         <v>518</v>
       </c>
+      <c r="I151" s="1" t="s">
+        <v>986</v>
+      </c>
       <c r="L151" s="1" t="s">
         <v>25</v>
       </c>
@@ -10252,6 +11430,9 @@
       <c r="D152" s="1" t="s">
         <v>519</v>
       </c>
+      <c r="I152" s="1" t="s">
+        <v>987</v>
+      </c>
       <c r="L152" s="1" t="s">
         <v>25</v>
       </c>
@@ -10294,7 +11475,7 @@
         <v>520</v>
       </c>
       <c r="I153" s="1" t="s">
-        <v>819</v>
+        <v>988</v>
       </c>
       <c r="L153" s="1" t="s">
         <v>25</v>
@@ -10338,7 +11519,7 @@
         <v>521</v>
       </c>
       <c r="I154" s="1" t="s">
-        <v>818</v>
+        <v>989</v>
       </c>
       <c r="L154" s="1" t="s">
         <v>25</v>
@@ -10381,6 +11562,9 @@
       <c r="D155" s="1" t="s">
         <v>522</v>
       </c>
+      <c r="I155" s="1" t="s">
+        <v>990</v>
+      </c>
       <c r="L155" s="1" t="s">
         <v>25</v>
       </c>
@@ -10425,6 +11609,9 @@
       <c r="D156" s="1" t="s">
         <v>523</v>
       </c>
+      <c r="I156" s="1" t="s">
+        <v>991</v>
+      </c>
       <c r="L156" s="1" t="s">
         <v>25</v>
       </c>
@@ -10452,7 +11639,7 @@
     </row>
     <row r="157" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A157" s="1" t="s">
-        <v>848</v>
+        <v>812</v>
       </c>
       <c r="B157" s="1" t="s">
         <v>419</v>
@@ -10462,6 +11649,9 @@
       </c>
       <c r="D157" s="1" t="s">
         <v>524</v>
+      </c>
+      <c r="I157" s="1" t="s">
+        <v>992</v>
       </c>
       <c r="L157" s="1" t="s">
         <v>25</v>
@@ -10504,6 +11694,9 @@
       <c r="D158" s="1" t="s">
         <v>525</v>
       </c>
+      <c r="I158" s="1" t="s">
+        <v>993</v>
+      </c>
       <c r="L158" s="1" t="s">
         <v>25</v>
       </c>
@@ -10545,6 +11738,9 @@
       <c r="D159" s="1" t="s">
         <v>526</v>
       </c>
+      <c r="I159" s="1" t="s">
+        <v>994</v>
+      </c>
       <c r="L159" s="1" t="s">
         <v>25</v>
       </c>
@@ -10583,6 +11779,9 @@
       <c r="D160" s="1" t="s">
         <v>527</v>
       </c>
+      <c r="I160" s="1" t="s">
+        <v>995</v>
+      </c>
       <c r="L160" s="1" t="s">
         <v>25</v>
       </c>
@@ -10627,6 +11826,9 @@
       <c r="D161" s="1" t="s">
         <v>528</v>
       </c>
+      <c r="I161" s="1" t="s">
+        <v>996</v>
+      </c>
       <c r="L161" s="1" t="s">
         <v>25</v>
       </c>
@@ -10671,6 +11873,9 @@
       <c r="D162" s="1" t="s">
         <v>529</v>
       </c>
+      <c r="I162" s="1" t="s">
+        <v>997</v>
+      </c>
       <c r="L162" s="1" t="s">
         <v>25</v>
       </c>
@@ -10715,6 +11920,9 @@
       <c r="D163" s="1" t="s">
         <v>530</v>
       </c>
+      <c r="I163" s="1" t="s">
+        <v>998</v>
+      </c>
       <c r="L163" s="1" t="s">
         <v>25</v>
       </c>
@@ -10759,6 +11967,9 @@
       <c r="D164" s="1" t="s">
         <v>531</v>
       </c>
+      <c r="I164" s="1" t="s">
+        <v>999</v>
+      </c>
       <c r="L164" s="1" t="s">
         <v>25</v>
       </c>
@@ -10803,6 +12014,9 @@
       <c r="D165" s="1" t="s">
         <v>532</v>
       </c>
+      <c r="I165" s="1" t="s">
+        <v>1000</v>
+      </c>
       <c r="L165" s="1" t="s">
         <v>25</v>
       </c>
@@ -10844,6 +12058,9 @@
       <c r="D166" s="1" t="s">
         <v>533</v>
       </c>
+      <c r="I166" s="1" t="s">
+        <v>1001</v>
+      </c>
       <c r="L166" s="1" t="s">
         <v>25</v>
       </c>
@@ -10883,7 +12100,7 @@
         <v>429</v>
       </c>
       <c r="I167" s="1" t="s">
-        <v>836</v>
+        <v>1002</v>
       </c>
       <c r="K167" s="1" t="s">
         <v>74</v>
@@ -10923,6 +12140,9 @@
       <c r="B168" s="1" t="s">
         <v>430</v>
       </c>
+      <c r="I168" s="1" t="s">
+        <v>1003</v>
+      </c>
       <c r="L168" s="1" t="s">
         <v>25</v>
       </c>
@@ -10964,6 +12184,9 @@
       <c r="D169" s="1" t="s">
         <v>534</v>
       </c>
+      <c r="I169" s="1" t="s">
+        <v>1004</v>
+      </c>
       <c r="L169" s="1" t="s">
         <v>25</v>
       </c>
@@ -11002,6 +12225,9 @@
       <c r="B170" s="1" t="s">
         <v>432</v>
       </c>
+      <c r="I170" s="1" t="s">
+        <v>1005</v>
+      </c>
       <c r="L170" s="1" t="s">
         <v>25</v>
       </c>
@@ -11043,6 +12269,9 @@
       <c r="D171" s="1" t="s">
         <v>535</v>
       </c>
+      <c r="I171" s="1" t="s">
+        <v>1006</v>
+      </c>
       <c r="L171" s="1" t="s">
         <v>25</v>
       </c>
@@ -11087,6 +12316,9 @@
       <c r="D172" s="1" t="s">
         <v>536</v>
       </c>
+      <c r="I172" s="1" t="s">
+        <v>1007</v>
+      </c>
       <c r="L172" s="1" t="s">
         <v>25</v>
       </c>
@@ -11129,7 +12361,7 @@
         <v>537</v>
       </c>
       <c r="I173" s="1" t="s">
-        <v>837</v>
+        <v>1008</v>
       </c>
       <c r="L173" s="1" t="s">
         <v>25</v>
@@ -11172,6 +12404,9 @@
       <c r="D174" s="1" t="s">
         <v>538</v>
       </c>
+      <c r="I174" s="1" t="s">
+        <v>1009</v>
+      </c>
       <c r="L174" s="1" t="s">
         <v>25</v>
       </c>
@@ -11216,6 +12451,9 @@
       <c r="D175" s="1" t="s">
         <v>539</v>
       </c>
+      <c r="I175" s="1" t="s">
+        <v>1010</v>
+      </c>
       <c r="L175" s="1" t="s">
         <v>25</v>
       </c>
@@ -11260,6 +12498,9 @@
       <c r="D176" s="1" t="s">
         <v>535</v>
       </c>
+      <c r="I176" s="1" t="s">
+        <v>1011</v>
+      </c>
       <c r="L176" s="1" t="s">
         <v>25</v>
       </c>
@@ -11305,7 +12546,7 @@
         <v>540</v>
       </c>
       <c r="I177" s="1" t="s">
-        <v>826</v>
+        <v>1012</v>
       </c>
       <c r="L177" s="1" t="s">
         <v>25</v>
@@ -11352,7 +12593,7 @@
         <v>540</v>
       </c>
       <c r="I178" s="1" t="s">
-        <v>827</v>
+        <v>1013</v>
       </c>
       <c r="L178" s="1" t="s">
         <v>25</v>
@@ -11387,7 +12628,7 @@
     </row>
     <row r="179" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A179" s="1" t="s">
-        <v>883</v>
+        <v>833</v>
       </c>
       <c r="B179" s="1" t="s">
         <v>441</v>
@@ -11397,6 +12638,9 @@
       </c>
       <c r="D179" s="1" t="s">
         <v>541</v>
+      </c>
+      <c r="I179" s="1" t="s">
+        <v>1014</v>
       </c>
       <c r="L179" s="1" t="s">
         <v>25</v>
@@ -11442,6 +12686,9 @@
       <c r="D180" s="1" t="s">
         <v>542</v>
       </c>
+      <c r="I180" s="1" t="s">
+        <v>1015</v>
+      </c>
       <c r="L180" s="1" t="s">
         <v>25</v>
       </c>
@@ -11486,6 +12733,9 @@
       <c r="D181" s="1" t="s">
         <v>543</v>
       </c>
+      <c r="I181" s="1" t="s">
+        <v>1016</v>
+      </c>
       <c r="L181" s="1" t="s">
         <v>25</v>
       </c>
@@ -11530,6 +12780,9 @@
       <c r="D182" s="1" t="s">
         <v>544</v>
       </c>
+      <c r="I182" s="1" t="s">
+        <v>1017</v>
+      </c>
       <c r="L182" s="1" t="s">
         <v>25</v>
       </c>
@@ -11571,6 +12824,9 @@
       <c r="D183" s="1" t="s">
         <v>545</v>
       </c>
+      <c r="I183" s="1" t="s">
+        <v>1018</v>
+      </c>
       <c r="L183" s="1" t="s">
         <v>25</v>
       </c>
@@ -11613,7 +12869,7 @@
         <v>546</v>
       </c>
       <c r="I184" s="1" t="s">
-        <v>838</v>
+        <v>1019</v>
       </c>
       <c r="K184" s="1" t="s">
         <v>618</v>
@@ -11659,6 +12915,9 @@
       <c r="D185" s="1" t="s">
         <v>547</v>
       </c>
+      <c r="I185" s="1" t="s">
+        <v>1020</v>
+      </c>
       <c r="L185" s="1" t="s">
         <v>25</v>
       </c>
@@ -11700,6 +12959,9 @@
       <c r="D186" s="1" t="s">
         <v>548</v>
       </c>
+      <c r="I186" s="1" t="s">
+        <v>1021</v>
+      </c>
       <c r="L186" s="1" t="s">
         <v>25</v>
       </c>
@@ -11744,6 +13006,9 @@
       <c r="D187" s="1" t="s">
         <v>549</v>
       </c>
+      <c r="I187" s="1" t="s">
+        <v>1022</v>
+      </c>
       <c r="L187" s="1" t="s">
         <v>25</v>
       </c>
@@ -11788,6 +13053,9 @@
       <c r="D188" s="1" t="s">
         <v>550</v>
       </c>
+      <c r="I188" s="1" t="s">
+        <v>1023</v>
+      </c>
       <c r="L188" s="1" t="s">
         <v>25</v>
       </c>
@@ -11818,7 +13086,7 @@
     </row>
     <row r="189" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A189" s="1" t="s">
-        <v>884</v>
+        <v>834</v>
       </c>
       <c r="B189" s="1" t="s">
         <v>451</v>
@@ -11828,6 +13096,9 @@
       </c>
       <c r="D189" s="1" t="s">
         <v>551</v>
+      </c>
+      <c r="I189" s="1" t="s">
+        <v>1024</v>
       </c>
       <c r="L189" s="1" t="s">
         <v>25</v>
@@ -11873,6 +13144,9 @@
       <c r="D190" s="1" t="s">
         <v>797</v>
       </c>
+      <c r="I190" s="1" t="s">
+        <v>1025</v>
+      </c>
       <c r="L190" s="1" t="s">
         <v>25</v>
       </c>
@@ -11914,6 +13188,9 @@
       <c r="D191" s="1" t="s">
         <v>552</v>
       </c>
+      <c r="I191" s="1" t="s">
+        <v>1026</v>
+      </c>
       <c r="L191" s="1" t="s">
         <v>25</v>
       </c>
@@ -11958,6 +13235,9 @@
       <c r="D192" s="1" t="s">
         <v>553</v>
       </c>
+      <c r="I192" s="1" t="s">
+        <v>1027</v>
+      </c>
       <c r="L192" s="1" t="s">
         <v>25</v>
       </c>
@@ -12002,6 +13282,9 @@
       <c r="D193" s="1" t="s">
         <v>554</v>
       </c>
+      <c r="I193" s="1" t="s">
+        <v>1028</v>
+      </c>
       <c r="L193" s="1" t="s">
         <v>25</v>
       </c>
@@ -12043,6 +13326,9 @@
       <c r="D194" s="1" t="s">
         <v>555</v>
       </c>
+      <c r="I194" s="1" t="s">
+        <v>1029</v>
+      </c>
       <c r="L194" s="1" t="s">
         <v>25</v>
       </c>
@@ -12087,6 +13373,9 @@
       <c r="D195" s="1" t="s">
         <v>556</v>
       </c>
+      <c r="I195" s="1" t="s">
+        <v>1030</v>
+      </c>
       <c r="L195" s="1" t="s">
         <v>25</v>
       </c>
@@ -12131,6 +13420,9 @@
       <c r="D196" s="1" t="s">
         <v>557</v>
       </c>
+      <c r="I196" s="1" t="s">
+        <v>1031</v>
+      </c>
       <c r="L196" s="1" t="s">
         <v>25</v>
       </c>
@@ -12176,7 +13468,7 @@
         <v>558</v>
       </c>
       <c r="I197" s="1" t="s">
-        <v>839</v>
+        <v>1032</v>
       </c>
       <c r="L197" s="1" t="s">
         <v>25</v>
@@ -12223,10 +13515,10 @@
         <v>559</v>
       </c>
       <c r="I198" s="1" t="s">
-        <v>867</v>
+        <v>1033</v>
       </c>
       <c r="K198" s="1" t="s">
-        <v>868</v>
+        <v>827</v>
       </c>
       <c r="L198" s="1" t="s">
         <v>25</v>
@@ -12272,6 +13564,9 @@
       <c r="D199" s="1" t="s">
         <v>560</v>
       </c>
+      <c r="I199" s="1" t="s">
+        <v>1034</v>
+      </c>
       <c r="L199" s="1" t="s">
         <v>25</v>
       </c>
@@ -12316,6 +13611,9 @@
       <c r="D200" s="1" t="s">
         <v>561</v>
       </c>
+      <c r="I200" s="1" t="s">
+        <v>1035</v>
+      </c>
       <c r="L200" s="1" t="s">
         <v>25</v>
       </c>
@@ -12360,6 +13658,9 @@
       <c r="D201" s="1" t="s">
         <v>562</v>
       </c>
+      <c r="I201" s="1" t="s">
+        <v>1036</v>
+      </c>
       <c r="L201" s="1" t="s">
         <v>25</v>
       </c>
@@ -12404,6 +13705,9 @@
       <c r="D202" s="1" t="s">
         <v>563</v>
       </c>
+      <c r="I202" s="1" t="s">
+        <v>1037</v>
+      </c>
       <c r="L202" s="1" t="s">
         <v>25</v>
       </c>
@@ -12448,6 +13752,9 @@
       <c r="D203" s="1" t="s">
         <v>564</v>
       </c>
+      <c r="I203" s="1" t="s">
+        <v>1038</v>
+      </c>
       <c r="L203" s="1" t="s">
         <v>25</v>
       </c>
@@ -12492,6 +13799,9 @@
       <c r="D204" s="1" t="s">
         <v>565</v>
       </c>
+      <c r="I204" s="1" t="s">
+        <v>1039</v>
+      </c>
       <c r="L204" s="1" t="s">
         <v>25</v>
       </c>
@@ -12531,10 +13841,10 @@
         <v>566</v>
       </c>
       <c r="I205" s="1" t="s">
-        <v>869</v>
+        <v>1040</v>
       </c>
       <c r="K205" s="1" t="s">
-        <v>870</v>
+        <v>828</v>
       </c>
       <c r="L205" s="1" t="s">
         <v>25</v>
@@ -12571,6 +13881,9 @@
       <c r="B206" s="1" t="s">
         <v>468</v>
       </c>
+      <c r="I206" s="1" t="s">
+        <v>1041</v>
+      </c>
       <c r="L206" s="1" t="s">
         <v>25</v>
       </c>
@@ -12612,6 +13925,9 @@
       <c r="B207" s="1" t="s">
         <v>469</v>
       </c>
+      <c r="I207" s="1" t="s">
+        <v>1042</v>
+      </c>
       <c r="L207" s="1" t="s">
         <v>25</v>
       </c>
@@ -12656,6 +13972,9 @@
       <c r="D208" s="1" t="s">
         <v>567</v>
       </c>
+      <c r="I208" s="1" t="s">
+        <v>1043</v>
+      </c>
       <c r="L208" s="1" t="s">
         <v>25</v>
       </c>
@@ -12695,10 +14014,10 @@
         <v>471</v>
       </c>
       <c r="I209" s="1" t="s">
-        <v>871</v>
+        <v>1044</v>
       </c>
       <c r="K209" s="1" t="s">
-        <v>872</v>
+        <v>829</v>
       </c>
       <c r="L209" s="1" t="s">
         <v>25</v>
@@ -12738,6 +14057,9 @@
       <c r="B210" s="1" t="s">
         <v>472</v>
       </c>
+      <c r="I210" s="1" t="s">
+        <v>1045</v>
+      </c>
       <c r="L210" s="1" t="s">
         <v>25</v>
       </c>
@@ -12776,6 +14098,9 @@
       <c r="B211" s="1" t="s">
         <v>473</v>
       </c>
+      <c r="I211" s="1" t="s">
+        <v>1046</v>
+      </c>
       <c r="L211" s="1" t="s">
         <v>25</v>
       </c>
@@ -12809,10 +14134,13 @@
     </row>
     <row r="212" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A212" s="1" t="s">
-        <v>885</v>
+        <v>835</v>
       </c>
       <c r="B212" s="1" t="s">
         <v>474</v>
+      </c>
+      <c r="I212" s="1" t="s">
+        <v>1047</v>
       </c>
       <c r="L212" s="1" t="s">
         <v>25</v>
@@ -12849,6 +14177,9 @@
       <c r="B213" s="1" t="s">
         <v>475</v>
       </c>
+      <c r="I213" s="1" t="s">
+        <v>1048</v>
+      </c>
       <c r="L213" s="1" t="s">
         <v>25</v>
       </c>
@@ -12890,6 +14221,9 @@
       <c r="D214" s="1" t="s">
         <v>568</v>
       </c>
+      <c r="I214" s="1" t="s">
+        <v>1049</v>
+      </c>
       <c r="L214" s="1" t="s">
         <v>25</v>
       </c>
@@ -12928,6 +14262,9 @@
       <c r="B215" s="1" t="s">
         <v>477</v>
       </c>
+      <c r="I215" s="1" t="s">
+        <v>1050</v>
+      </c>
       <c r="L215" s="1" t="s">
         <v>25</v>
       </c>
@@ -12972,6 +14309,9 @@
       <c r="D216" s="1" t="s">
         <v>569</v>
       </c>
+      <c r="I216" s="1" t="s">
+        <v>1051</v>
+      </c>
       <c r="L216" s="1" t="s">
         <v>25</v>
       </c>
@@ -13014,7 +14354,7 @@
         <v>570</v>
       </c>
       <c r="I217" s="1" t="s">
-        <v>813</v>
+        <v>1052</v>
       </c>
       <c r="L217" s="1" t="s">
         <v>25</v>
@@ -13057,6 +14397,9 @@
       <c r="D218" s="1" t="s">
         <v>571</v>
       </c>
+      <c r="I218" s="1" t="s">
+        <v>1053</v>
+      </c>
       <c r="L218" s="1" t="s">
         <v>25</v>
       </c>
@@ -13099,7 +14442,7 @@
         <v>572</v>
       </c>
       <c r="I219" s="1" t="s">
-        <v>840</v>
+        <v>1054</v>
       </c>
       <c r="L219" s="1" t="s">
         <v>25</v>
@@ -13142,6 +14485,9 @@
       <c r="D220" s="1" t="s">
         <v>573</v>
       </c>
+      <c r="I220" s="1" t="s">
+        <v>1055</v>
+      </c>
       <c r="L220" s="1" t="s">
         <v>25</v>
       </c>
@@ -13184,7 +14530,7 @@
         <v>574</v>
       </c>
       <c r="I221" s="1" t="s">
-        <v>841</v>
+        <v>1056</v>
       </c>
       <c r="L221" s="1" t="s">
         <v>25</v>
@@ -13228,7 +14574,7 @@
         <v>575</v>
       </c>
       <c r="I222" s="1" t="s">
-        <v>814</v>
+        <v>1057</v>
       </c>
       <c r="L222" s="1" t="s">
         <v>25</v>
@@ -13271,6 +14617,9 @@
       <c r="D223" s="1" t="s">
         <v>576</v>
       </c>
+      <c r="I223" s="1" t="s">
+        <v>1058</v>
+      </c>
       <c r="L223" s="1" t="s">
         <v>25</v>
       </c>
@@ -13315,6 +14664,9 @@
       <c r="D224" s="1" t="s">
         <v>577</v>
       </c>
+      <c r="I224" s="1" t="s">
+        <v>1059</v>
+      </c>
       <c r="L224" s="1" t="s">
         <v>25</v>
       </c>
@@ -13356,6 +14708,9 @@
       <c r="D225" s="1" t="s">
         <v>578</v>
       </c>
+      <c r="I225" s="1" t="s">
+        <v>1060</v>
+      </c>
       <c r="L225" s="1" t="s">
         <v>25</v>
       </c>
@@ -13389,7 +14744,7 @@
         <v>488</v>
       </c>
       <c r="B226" s="1" t="s">
-        <v>816</v>
+        <v>805</v>
       </c>
       <c r="C226" s="1" t="s">
         <v>579</v>
@@ -13398,7 +14753,7 @@
         <v>579</v>
       </c>
       <c r="I226" s="1" t="s">
-        <v>815</v>
+        <v>1061</v>
       </c>
       <c r="L226" s="1" t="s">
         <v>25</v>
@@ -13442,7 +14797,7 @@
         <v>580</v>
       </c>
       <c r="I227" s="1" t="s">
-        <v>829</v>
+        <v>1062</v>
       </c>
       <c r="L227" s="1" t="s">
         <v>25</v>
@@ -13488,6 +14843,9 @@
       <c r="D228" s="1" t="s">
         <v>535</v>
       </c>
+      <c r="I228" s="1" t="s">
+        <v>1063</v>
+      </c>
       <c r="L228" s="1" t="s">
         <v>25</v>
       </c>
@@ -13532,6 +14890,9 @@
       <c r="D229" s="1" t="s">
         <v>535</v>
       </c>
+      <c r="I229" s="1" t="s">
+        <v>1064</v>
+      </c>
       <c r="L229" s="1" t="s">
         <v>25</v>
       </c>
@@ -13576,6 +14937,9 @@
       <c r="D230" s="1" t="s">
         <v>540</v>
       </c>
+      <c r="I230" s="1" t="s">
+        <v>1065</v>
+      </c>
       <c r="L230" s="1" t="s">
         <v>25</v>
       </c>
@@ -13620,6 +14984,9 @@
       <c r="D231" s="1" t="s">
         <v>540</v>
       </c>
+      <c r="I231" s="1" t="s">
+        <v>1066</v>
+      </c>
       <c r="L231" s="1" t="s">
         <v>25</v>
       </c>
@@ -13661,6 +15028,9 @@
       <c r="D232" s="1" t="s">
         <v>569</v>
       </c>
+      <c r="I232" s="1" t="s">
+        <v>1067</v>
+      </c>
       <c r="L232" s="1" t="s">
         <v>25</v>
       </c>
@@ -13702,6 +15072,9 @@
       <c r="D233" s="1" t="s">
         <v>570</v>
       </c>
+      <c r="I233" s="1" t="s">
+        <v>1068</v>
+      </c>
       <c r="L233" s="1" t="s">
         <v>25</v>
       </c>
@@ -13744,7 +15117,7 @@
         <v>572</v>
       </c>
       <c r="I234" s="1" t="s">
-        <v>842</v>
+        <v>1069</v>
       </c>
       <c r="L234" s="1" t="s">
         <v>25</v>
@@ -13787,6 +15160,9 @@
       <c r="D235" s="1" t="s">
         <v>573</v>
       </c>
+      <c r="I235" s="1" t="s">
+        <v>1070</v>
+      </c>
       <c r="L235" s="1" t="s">
         <v>25</v>
       </c>
@@ -13829,7 +15205,7 @@
         <v>574</v>
       </c>
       <c r="I236" s="1" t="s">
-        <v>843</v>
+        <v>1071</v>
       </c>
       <c r="L236" s="1" t="s">
         <v>25</v>
@@ -13872,6 +15248,9 @@
       <c r="D237" s="1" t="s">
         <v>569</v>
       </c>
+      <c r="I237" s="1" t="s">
+        <v>1072</v>
+      </c>
       <c r="L237" s="1" t="s">
         <v>25</v>
       </c>
@@ -13914,7 +15293,7 @@
         <v>570</v>
       </c>
       <c r="I238" s="1" t="s">
-        <v>817</v>
+        <v>1073</v>
       </c>
       <c r="L238" s="1" t="s">
         <v>25</v>
@@ -13958,7 +15337,7 @@
         <v>572</v>
       </c>
       <c r="I239" s="1" t="s">
-        <v>844</v>
+        <v>1074</v>
       </c>
       <c r="L239" s="1" t="s">
         <v>25</v>
@@ -14001,6 +15380,9 @@
       <c r="D240" s="1" t="s">
         <v>573</v>
       </c>
+      <c r="I240" s="1" t="s">
+        <v>1075</v>
+      </c>
       <c r="L240" s="1" t="s">
         <v>25</v>
       </c>
@@ -14043,7 +15425,7 @@
         <v>574</v>
       </c>
       <c r="I241" s="1" t="s">
-        <v>845</v>
+        <v>1076</v>
       </c>
       <c r="L241" s="1" t="s">
         <v>25</v>
@@ -14086,6 +15468,9 @@
       <c r="D242" s="1" t="s">
         <v>581</v>
       </c>
+      <c r="I242" s="1" t="s">
+        <v>1077</v>
+      </c>
       <c r="L242" s="1" t="s">
         <v>25</v>
       </c>
@@ -14118,6 +15503,9 @@
       <c r="B243" s="1" t="s">
         <v>505</v>
       </c>
+      <c r="I243" s="1" t="s">
+        <v>1078</v>
+      </c>
       <c r="L243" s="1" t="s">
         <v>25</v>
       </c>
@@ -14153,6 +15541,9 @@
       <c r="B244" s="1" t="s">
         <v>506</v>
       </c>
+      <c r="I244" s="1" t="s">
+        <v>1079</v>
+      </c>
       <c r="L244" s="1" t="s">
         <v>25</v>
       </c>
@@ -14185,6 +15576,9 @@
       <c r="B245" s="1" t="s">
         <v>507</v>
       </c>
+      <c r="I245" s="1" t="s">
+        <v>1080</v>
+      </c>
       <c r="L245" s="1" t="s">
         <v>25</v>
       </c>
@@ -14217,6 +15611,9 @@
       <c r="B246" s="1" t="s">
         <v>508</v>
       </c>
+      <c r="I246" s="1" t="s">
+        <v>1081</v>
+      </c>
       <c r="L246" s="1" t="s">
         <v>25</v>
       </c>
@@ -14249,6 +15646,9 @@
       <c r="B247" s="1" t="s">
         <v>509</v>
       </c>
+      <c r="I247" s="1" t="s">
+        <v>1082</v>
+      </c>
       <c r="L247" s="1" t="s">
         <v>25</v>
       </c>
@@ -14289,6 +15689,9 @@
       </c>
       <c r="D248" s="1" t="s">
         <v>582</v>
+      </c>
+      <c r="I248" s="1" t="s">
+        <v>1083</v>
       </c>
       <c r="L248" s="1" t="s">
         <v>25</v>
@@ -14332,6 +15735,9 @@
       <c r="D250" s="1" t="s">
         <v>709</v>
       </c>
+      <c r="I250" s="1" t="s">
+        <v>1084</v>
+      </c>
       <c r="L250" s="1" t="s">
         <v>25</v>
       </c>
@@ -14376,6 +15782,9 @@
       <c r="D251" s="1" t="s">
         <v>710</v>
       </c>
+      <c r="I251" s="1" t="s">
+        <v>1085</v>
+      </c>
       <c r="L251" s="1" t="s">
         <v>25</v>
       </c>
@@ -14420,6 +15829,9 @@
       <c r="D252" s="1" t="s">
         <v>711</v>
       </c>
+      <c r="I252" s="1" t="s">
+        <v>1086</v>
+      </c>
       <c r="L252" s="1" t="s">
         <v>25</v>
       </c>
@@ -14467,6 +15879,9 @@
       <c r="D253" s="1" t="s">
         <v>712</v>
       </c>
+      <c r="I253" s="1" t="s">
+        <v>1087</v>
+      </c>
       <c r="L253" s="1" t="s">
         <v>25</v>
       </c>
@@ -14511,6 +15926,9 @@
       <c r="D254" s="1" t="s">
         <v>713</v>
       </c>
+      <c r="I254" s="1" t="s">
+        <v>1088</v>
+      </c>
       <c r="L254" s="1" t="s">
         <v>25</v>
       </c>
@@ -14555,6 +15973,9 @@
       <c r="D255" s="1" t="s">
         <v>714</v>
       </c>
+      <c r="I255" s="1" t="s">
+        <v>1089</v>
+      </c>
       <c r="L255" s="1" t="s">
         <v>25</v>
       </c>
@@ -14596,6 +16017,9 @@
       <c r="D256" s="1" t="s">
         <v>715</v>
       </c>
+      <c r="I256" s="1" t="s">
+        <v>1090</v>
+      </c>
       <c r="L256" s="1" t="s">
         <v>25</v>
       </c>
@@ -14640,6 +16064,9 @@
       <c r="D257" s="1" t="s">
         <v>716</v>
       </c>
+      <c r="I257" s="1" t="s">
+        <v>1091</v>
+      </c>
       <c r="L257" s="1" t="s">
         <v>25</v>
       </c>
@@ -14684,6 +16111,9 @@
       <c r="D258" s="1" t="s">
         <v>717</v>
       </c>
+      <c r="I258" s="1" t="s">
+        <v>1092</v>
+      </c>
       <c r="L258" s="1" t="s">
         <v>25</v>
       </c>
@@ -14728,6 +16158,9 @@
       <c r="D259" s="1" t="s">
         <v>718</v>
       </c>
+      <c r="I259" s="1" t="s">
+        <v>1093</v>
+      </c>
       <c r="L259" s="1" t="s">
         <v>25</v>
       </c>
@@ -14769,6 +16202,9 @@
       <c r="D260" s="1" t="s">
         <v>719</v>
       </c>
+      <c r="I260" s="1" t="s">
+        <v>1094</v>
+      </c>
       <c r="L260" s="1" t="s">
         <v>25</v>
       </c>
@@ -14810,6 +16246,9 @@
       <c r="D261" s="1" t="s">
         <v>720</v>
       </c>
+      <c r="I261" s="1" t="s">
+        <v>1095</v>
+      </c>
       <c r="L261" s="1" t="s">
         <v>25</v>
       </c>
@@ -14851,6 +16290,9 @@
       <c r="D262" s="1" t="s">
         <v>721</v>
       </c>
+      <c r="I262" s="1" t="s">
+        <v>1096</v>
+      </c>
       <c r="L262" s="1" t="s">
         <v>25</v>
       </c>
@@ -14887,7 +16329,7 @@
         <v>638</v>
       </c>
       <c r="B263" s="1" t="s">
-        <v>852</v>
+        <v>815</v>
       </c>
       <c r="C263" s="1" t="s">
         <v>722</v>
@@ -14896,7 +16338,7 @@
         <v>722</v>
       </c>
       <c r="I263" s="1" t="s">
-        <v>873</v>
+        <v>1097</v>
       </c>
       <c r="L263" s="1" t="s">
         <v>25</v>
@@ -14942,6 +16384,9 @@
       <c r="D264" s="1" t="s">
         <v>723</v>
       </c>
+      <c r="I264" s="1" t="s">
+        <v>1098</v>
+      </c>
       <c r="L264" s="1" t="s">
         <v>25</v>
       </c>
@@ -14986,6 +16431,9 @@
       <c r="D265" s="1" t="s">
         <v>724</v>
       </c>
+      <c r="I265" s="1" t="s">
+        <v>1099</v>
+      </c>
       <c r="L265" s="1" t="s">
         <v>25</v>
       </c>
@@ -15030,6 +16478,9 @@
       <c r="D266" s="1" t="s">
         <v>725</v>
       </c>
+      <c r="I266" s="1" t="s">
+        <v>1100</v>
+      </c>
       <c r="L266" s="1" t="s">
         <v>25</v>
       </c>
@@ -15074,6 +16525,9 @@
       <c r="D267" s="1" t="s">
         <v>726</v>
       </c>
+      <c r="I267" s="1" t="s">
+        <v>1101</v>
+      </c>
       <c r="L267" s="1" t="s">
         <v>25</v>
       </c>
@@ -15119,10 +16573,10 @@
         <v>727</v>
       </c>
       <c r="I268" s="1" t="s">
-        <v>874</v>
+        <v>1102</v>
       </c>
       <c r="K268" s="1" t="s">
-        <v>875</v>
+        <v>830</v>
       </c>
       <c r="L268" s="1" t="s">
         <v>25</v>
@@ -15165,6 +16619,9 @@
       <c r="D269" s="1" t="s">
         <v>728</v>
       </c>
+      <c r="I269" s="1" t="s">
+        <v>1103</v>
+      </c>
       <c r="L269" s="1" t="s">
         <v>25</v>
       </c>
@@ -15201,7 +16658,7 @@
     </row>
     <row r="270" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A270" s="1" t="s">
-        <v>886</v>
+        <v>836</v>
       </c>
       <c r="B270" s="1" t="s">
         <v>645</v>
@@ -15211,6 +16668,9 @@
       </c>
       <c r="D270" s="1" t="s">
         <v>729</v>
+      </c>
+      <c r="I270" s="1" t="s">
+        <v>1104</v>
       </c>
       <c r="L270" s="1" t="s">
         <v>25</v>
@@ -15256,6 +16716,9 @@
       <c r="D271" s="1" t="s">
         <v>729</v>
       </c>
+      <c r="I271" s="1" t="s">
+        <v>1105</v>
+      </c>
       <c r="L271" s="1" t="s">
         <v>25</v>
       </c>
@@ -15300,6 +16763,9 @@
       <c r="D272" s="1" t="s">
         <v>730</v>
       </c>
+      <c r="I272" s="1" t="s">
+        <v>1106</v>
+      </c>
       <c r="L272" s="1" t="s">
         <v>25</v>
       </c>
@@ -15344,6 +16810,9 @@
       <c r="D273" s="1" t="s">
         <v>730</v>
       </c>
+      <c r="I273" s="1" t="s">
+        <v>1107</v>
+      </c>
       <c r="L273" s="1" t="s">
         <v>25</v>
       </c>
@@ -15388,6 +16857,9 @@
       <c r="D274" s="1" t="s">
         <v>731</v>
       </c>
+      <c r="I274" s="1" t="s">
+        <v>1108</v>
+      </c>
       <c r="L274" s="1" t="s">
         <v>25</v>
       </c>
@@ -15432,6 +16904,9 @@
       <c r="D275" s="1" t="s">
         <v>731</v>
       </c>
+      <c r="I275" s="1" t="s">
+        <v>1109</v>
+      </c>
       <c r="L275" s="1" t="s">
         <v>25</v>
       </c>
@@ -15476,6 +16951,9 @@
       <c r="D276" s="1" t="s">
         <v>732</v>
       </c>
+      <c r="I276" s="1" t="s">
+        <v>1110</v>
+      </c>
       <c r="L276" s="1" t="s">
         <v>25</v>
       </c>
@@ -15520,6 +16998,9 @@
       <c r="D277" s="1" t="s">
         <v>733</v>
       </c>
+      <c r="I277" s="1" t="s">
+        <v>1111</v>
+      </c>
       <c r="L277" s="1" t="s">
         <v>25</v>
       </c>
@@ -15561,6 +17042,9 @@
       <c r="D278" s="1" t="s">
         <v>734</v>
       </c>
+      <c r="I278" s="1" t="s">
+        <v>1112</v>
+      </c>
       <c r="L278" s="1" t="s">
         <v>25</v>
       </c>
@@ -15602,6 +17086,9 @@
       <c r="D279" s="1" t="s">
         <v>735</v>
       </c>
+      <c r="I279" s="1" t="s">
+        <v>1113</v>
+      </c>
       <c r="L279" s="1" t="s">
         <v>25</v>
       </c>
@@ -15646,6 +17133,9 @@
       <c r="D280" s="1" t="s">
         <v>736</v>
       </c>
+      <c r="I280" s="1" t="s">
+        <v>1114</v>
+      </c>
       <c r="L280" s="1" t="s">
         <v>25</v>
       </c>
@@ -15690,6 +17180,9 @@
       <c r="D281" s="1" t="s">
         <v>737</v>
       </c>
+      <c r="I281" s="1" t="s">
+        <v>1115</v>
+      </c>
       <c r="L281" s="1" t="s">
         <v>25</v>
       </c>
@@ -15737,6 +17230,9 @@
       <c r="D282" s="1" t="s">
         <v>738</v>
       </c>
+      <c r="I282" s="1" t="s">
+        <v>1116</v>
+      </c>
       <c r="L282" s="1" t="s">
         <v>25</v>
       </c>
@@ -15779,7 +17275,7 @@
         <v>739</v>
       </c>
       <c r="I283" s="1" t="s">
-        <v>846</v>
+        <v>1117</v>
       </c>
       <c r="L283" s="1" t="s">
         <v>25</v>
@@ -15825,6 +17321,9 @@
       <c r="D284" s="1" t="s">
         <v>740</v>
       </c>
+      <c r="I284" s="1" t="s">
+        <v>1118</v>
+      </c>
       <c r="L284" s="1" t="s">
         <v>25</v>
       </c>
@@ -15866,6 +17365,9 @@
       <c r="D285" s="1" t="s">
         <v>741</v>
       </c>
+      <c r="I285" s="1" t="s">
+        <v>1119</v>
+      </c>
       <c r="L285" s="1" t="s">
         <v>25</v>
       </c>
@@ -15907,6 +17409,9 @@
       <c r="D286" s="1" t="s">
         <v>742</v>
       </c>
+      <c r="I286" s="1" t="s">
+        <v>1120</v>
+      </c>
       <c r="L286" s="1" t="s">
         <v>25</v>
       </c>
@@ -15948,6 +17453,9 @@
       <c r="D287" s="1" t="s">
         <v>743</v>
       </c>
+      <c r="I287" s="1" t="s">
+        <v>1121</v>
+      </c>
       <c r="L287" s="1" t="s">
         <v>25</v>
       </c>
@@ -15989,6 +17497,9 @@
       <c r="D288" s="1" t="s">
         <v>744</v>
       </c>
+      <c r="I288" s="1" t="s">
+        <v>1122</v>
+      </c>
       <c r="L288" s="1" t="s">
         <v>25</v>
       </c>
@@ -16030,6 +17541,9 @@
       <c r="D289" s="1" t="s">
         <v>745</v>
       </c>
+      <c r="I289" s="1" t="s">
+        <v>1123</v>
+      </c>
       <c r="L289" s="1" t="s">
         <v>25</v>
       </c>
@@ -16072,7 +17586,7 @@
         <v>746</v>
       </c>
       <c r="I290" s="1" t="s">
-        <v>876</v>
+        <v>1124</v>
       </c>
       <c r="L290" s="1" t="s">
         <v>25</v>
@@ -16118,6 +17632,9 @@
       <c r="D291" s="1" t="s">
         <v>747</v>
       </c>
+      <c r="I291" s="1" t="s">
+        <v>1125</v>
+      </c>
       <c r="L291" s="1" t="s">
         <v>25</v>
       </c>
@@ -16156,6 +17673,9 @@
       <c r="B292" s="1" t="s">
         <v>667</v>
       </c>
+      <c r="I292" s="1" t="s">
+        <v>1126</v>
+      </c>
       <c r="L292" s="1" t="s">
         <v>25</v>
       </c>
@@ -16200,6 +17720,9 @@
       <c r="D293" s="1" t="s">
         <v>748</v>
       </c>
+      <c r="I293" s="1" t="s">
+        <v>1127</v>
+      </c>
       <c r="L293" s="1" t="s">
         <v>25</v>
       </c>
@@ -16241,6 +17764,9 @@
       <c r="D294" s="1" t="s">
         <v>749</v>
       </c>
+      <c r="I294" s="1" t="s">
+        <v>1128</v>
+      </c>
       <c r="L294" s="1" t="s">
         <v>25</v>
       </c>
@@ -16283,7 +17809,7 @@
         <v>750</v>
       </c>
       <c r="I295" s="1" t="s">
-        <v>877</v>
+        <v>1129</v>
       </c>
       <c r="L295" s="1" t="s">
         <v>25</v>
@@ -16327,7 +17853,7 @@
         <v>751</v>
       </c>
       <c r="I296" s="1" t="s">
-        <v>847</v>
+        <v>1130</v>
       </c>
       <c r="L296" s="1" t="s">
         <v>25</v>
@@ -16367,6 +17893,9 @@
       <c r="B297" s="1" t="s">
         <v>672</v>
       </c>
+      <c r="I297" s="1" t="s">
+        <v>1131</v>
+      </c>
       <c r="L297" s="1" t="s">
         <v>25</v>
       </c>
@@ -16402,6 +17931,9 @@
       <c r="B298" s="1" t="s">
         <v>673</v>
       </c>
+      <c r="I298" s="1" t="s">
+        <v>1132</v>
+      </c>
       <c r="L298" s="1" t="s">
         <v>25</v>
       </c>
@@ -16440,6 +17972,9 @@
       <c r="B299" s="1" t="s">
         <v>674</v>
       </c>
+      <c r="I299" s="1" t="s">
+        <v>1133</v>
+      </c>
       <c r="L299" s="1" t="s">
         <v>25</v>
       </c>
@@ -16478,6 +18013,9 @@
       <c r="B300" s="1" t="s">
         <v>675</v>
       </c>
+      <c r="I300" s="1" t="s">
+        <v>1134</v>
+      </c>
       <c r="L300" s="1" t="s">
         <v>25</v>
       </c>
@@ -16522,6 +18060,9 @@
       <c r="D301" s="1" t="s">
         <v>752</v>
       </c>
+      <c r="I301" s="1" t="s">
+        <v>1135</v>
+      </c>
       <c r="L301" s="1" t="s">
         <v>25</v>
       </c>
@@ -16566,6 +18107,9 @@
       <c r="D302" s="1" t="s">
         <v>753</v>
       </c>
+      <c r="I302" s="1" t="s">
+        <v>1136</v>
+      </c>
       <c r="L302" s="1" t="s">
         <v>25</v>
       </c>
@@ -16610,6 +18154,9 @@
       <c r="D303" s="1" t="s">
         <v>754</v>
       </c>
+      <c r="I303" s="1" t="s">
+        <v>1137</v>
+      </c>
       <c r="L303" s="1" t="s">
         <v>25</v>
       </c>
@@ -16649,10 +18196,10 @@
         <v>679</v>
       </c>
       <c r="I304" s="1" t="s">
-        <v>878</v>
+        <v>1138</v>
       </c>
       <c r="K304" s="1" t="s">
-        <v>879</v>
+        <v>831</v>
       </c>
       <c r="L304" s="1" t="s">
         <v>25</v>
@@ -16698,6 +18245,9 @@
       <c r="D305" s="1" t="s">
         <v>755</v>
       </c>
+      <c r="I305" s="1" t="s">
+        <v>1139</v>
+      </c>
       <c r="L305" s="1" t="s">
         <v>25</v>
       </c>
@@ -16742,6 +18292,9 @@
       <c r="D306" s="1" t="s">
         <v>756</v>
       </c>
+      <c r="I306" s="1" t="s">
+        <v>1140</v>
+      </c>
       <c r="L306" s="1" t="s">
         <v>25</v>
       </c>
@@ -16786,6 +18339,9 @@
       <c r="D307" s="1" t="s">
         <v>757</v>
       </c>
+      <c r="I307" s="1" t="s">
+        <v>1141</v>
+      </c>
       <c r="L307" s="1" t="s">
         <v>25</v>
       </c>
@@ -16827,6 +18383,9 @@
       <c r="D308" s="1" t="s">
         <v>758</v>
       </c>
+      <c r="I308" s="1" t="s">
+        <v>1142</v>
+      </c>
       <c r="L308" s="1" t="s">
         <v>25</v>
       </c>
@@ -16862,6 +18421,9 @@
       <c r="B309" s="1" t="s">
         <v>684</v>
       </c>
+      <c r="I309" s="1" t="s">
+        <v>1143</v>
+      </c>
       <c r="L309" s="1" t="s">
         <v>25</v>
       </c>
@@ -16897,6 +18459,9 @@
       <c r="B310" s="1" t="s">
         <v>685</v>
       </c>
+      <c r="I310" s="1" t="s">
+        <v>1144</v>
+      </c>
       <c r="L310" s="1" t="s">
         <v>25</v>
       </c>
@@ -16938,6 +18503,9 @@
       <c r="D311" s="1" t="s">
         <v>759</v>
       </c>
+      <c r="I311" s="1" t="s">
+        <v>1145</v>
+      </c>
       <c r="L311" s="1" t="s">
         <v>25</v>
       </c>
@@ -16979,6 +18547,9 @@
       <c r="D312" s="1" t="s">
         <v>760</v>
       </c>
+      <c r="I312" s="1" t="s">
+        <v>1146</v>
+      </c>
       <c r="L312" s="1" t="s">
         <v>25</v>
       </c>
@@ -17020,6 +18591,9 @@
       <c r="D313" s="1" t="s">
         <v>761</v>
       </c>
+      <c r="I313" s="1" t="s">
+        <v>1147</v>
+      </c>
       <c r="L313" s="1" t="s">
         <v>25</v>
       </c>
@@ -17061,6 +18635,9 @@
       <c r="D314" s="1" t="s">
         <v>762</v>
       </c>
+      <c r="I314" s="1" t="s">
+        <v>1148</v>
+      </c>
       <c r="L314" s="1" t="s">
         <v>25</v>
       </c>
@@ -17102,6 +18679,9 @@
       <c r="D315" s="1" t="s">
         <v>729</v>
       </c>
+      <c r="I315" s="1" t="s">
+        <v>1149</v>
+      </c>
       <c r="L315" s="1" t="s">
         <v>25</v>
       </c>
@@ -17146,6 +18726,9 @@
       <c r="D316" s="1" t="s">
         <v>729</v>
       </c>
+      <c r="I316" s="1" t="s">
+        <v>1150</v>
+      </c>
       <c r="L316" s="1" t="s">
         <v>25</v>
       </c>
@@ -17190,6 +18773,9 @@
       <c r="D317" s="1" t="s">
         <v>730</v>
       </c>
+      <c r="I317" s="1" t="s">
+        <v>1151</v>
+      </c>
       <c r="L317" s="1" t="s">
         <v>25</v>
       </c>
@@ -17234,6 +18820,9 @@
       <c r="D318" s="1" t="s">
         <v>730</v>
       </c>
+      <c r="I318" s="1" t="s">
+        <v>1152</v>
+      </c>
       <c r="L318" s="1" t="s">
         <v>25</v>
       </c>
@@ -17278,6 +18867,9 @@
       <c r="D319" s="1" t="s">
         <v>759</v>
       </c>
+      <c r="I319" s="1" t="s">
+        <v>1153</v>
+      </c>
       <c r="L319" s="1" t="s">
         <v>25</v>
       </c>
@@ -17319,6 +18911,9 @@
       <c r="D320" s="1" t="s">
         <v>759</v>
       </c>
+      <c r="I320" s="1" t="s">
+        <v>1154</v>
+      </c>
       <c r="L320" s="1" t="s">
         <v>25</v>
       </c>
@@ -17360,6 +18955,9 @@
       <c r="D321" s="1" t="s">
         <v>763</v>
       </c>
+      <c r="I321" s="1" t="s">
+        <v>1155</v>
+      </c>
       <c r="L321" s="1" t="s">
         <v>25</v>
       </c>
@@ -17402,10 +19000,10 @@
         <v>764</v>
       </c>
       <c r="I322" s="1" t="s">
-        <v>880</v>
+        <v>1156</v>
       </c>
       <c r="K322" s="1" t="s">
-        <v>881</v>
+        <v>832</v>
       </c>
       <c r="L322" s="1" t="s">
         <v>25</v>
@@ -17440,10 +19038,13 @@
     </row>
     <row r="323" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A323" s="1" t="s">
-        <v>887</v>
+        <v>837</v>
       </c>
       <c r="B323" s="1" t="s">
         <v>698</v>
+      </c>
+      <c r="I323" s="1" t="s">
+        <v>1157</v>
       </c>
       <c r="L323" s="1" t="s">
         <v>25</v>
@@ -17489,6 +19090,9 @@
       <c r="D324" s="1" t="s">
         <v>765</v>
       </c>
+      <c r="I324" s="1" t="s">
+        <v>1158</v>
+      </c>
       <c r="L324" s="1" t="s">
         <v>25</v>
       </c>
@@ -17530,6 +19134,9 @@
       <c r="D325" s="1" t="s">
         <v>766</v>
       </c>
+      <c r="I325" s="1" t="s">
+        <v>1159</v>
+      </c>
       <c r="L325" s="1" t="s">
         <v>25</v>
       </c>
@@ -17565,6 +19172,9 @@
       <c r="B326" s="1" t="s">
         <v>701</v>
       </c>
+      <c r="I326" s="1" t="s">
+        <v>1160</v>
+      </c>
       <c r="L326" s="1" t="s">
         <v>25</v>
       </c>
@@ -17600,6 +19210,9 @@
       <c r="B327" s="1" t="s">
         <v>702</v>
       </c>
+      <c r="I327" s="1" t="s">
+        <v>1161</v>
+      </c>
       <c r="L327" s="1" t="s">
         <v>25</v>
       </c>
@@ -17641,6 +19254,9 @@
       <c r="D328" s="1" t="s">
         <v>767</v>
       </c>
+      <c r="I328" s="1" t="s">
+        <v>1162</v>
+      </c>
       <c r="L328" s="1" t="s">
         <v>25</v>
       </c>
@@ -17676,6 +19292,9 @@
       <c r="B329" s="1" t="s">
         <v>704</v>
       </c>
+      <c r="I329" s="1" t="s">
+        <v>1163</v>
+      </c>
       <c r="L329" s="1" t="s">
         <v>25</v>
       </c>
@@ -17711,6 +19330,9 @@
       <c r="B330" s="1" t="s">
         <v>705</v>
       </c>
+      <c r="I330" s="1" t="s">
+        <v>1164</v>
+      </c>
       <c r="L330" s="1" t="s">
         <v>25</v>
       </c>
@@ -17746,6 +19368,9 @@
       <c r="B331" s="1" t="s">
         <v>706</v>
       </c>
+      <c r="I331" s="1" t="s">
+        <v>1165</v>
+      </c>
       <c r="L331" s="1" t="s">
         <v>25</v>
       </c>
@@ -17781,6 +19406,9 @@
       <c r="B332" s="1" t="s">
         <v>707</v>
       </c>
+      <c r="I332" s="1" t="s">
+        <v>1166</v>
+      </c>
       <c r="L332" s="1" t="s">
         <v>25</v>
       </c>
@@ -17824,6 +19452,9 @@
       </c>
       <c r="D333" s="1" t="s">
         <v>768</v>
+      </c>
+      <c r="I333" s="1" t="s">
+        <v>1167</v>
       </c>
       <c r="L333" s="1" t="s">
         <v>25</v>
